--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>391091</v>
+        <v>122649804</v>
       </c>
       <c r="B4" t="n">
-        <v>81235</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,37 +925,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810860.7270867341</v>
+        <v>810465</v>
       </c>
       <c r="R4" t="n">
-        <v>7171669.623737417</v>
+        <v>7171522</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +986,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,6 +1000,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1021,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2055139</v>
+        <v>122645698</v>
       </c>
       <c r="B5" t="n">
-        <v>78097</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,37 +1035,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810860.7270867341</v>
+        <v>810288</v>
       </c>
       <c r="R5" t="n">
-        <v>7171669.623737417</v>
+        <v>7171439</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,22 +1097,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>barksprätt på senvuxen gammelgran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,7 +1119,6 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AR5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>292476</v>
+        <v>122649813</v>
       </c>
       <c r="B6" t="n">
-        <v>79432</v>
+        <v>78690</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,37 +1150,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tallskog Storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810917.5546458759</v>
+        <v>810503</v>
       </c>
       <c r="R6" t="n">
-        <v>7171682.39060352</v>
+        <v>7171478</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,27 +1211,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2007-10-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>rapport från Patrik Nygren, SNF</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,28 +1225,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Jonas F Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>292265</v>
+        <v>122645725</v>
       </c>
       <c r="B7" t="n">
-        <v>79432</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,37 +1260,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810860.7270867341</v>
+        <v>810444</v>
       </c>
       <c r="R7" t="n">
-        <v>7171669.623737417</v>
+        <v>7171408</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1321,22 +1321,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,10 +1335,10 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1361,6 +1351,3353 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122645881</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>810380</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7171534</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122649797</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56585</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>810426</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7171539</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122645747</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57383</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>810444</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7171459</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>barksprätt på gammelgran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122645768</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57383</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>810402</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7171498</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>påbörjat bohål?</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122645753</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>810433</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7171480</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122650377</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90798</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>810600</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7171604</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122649880</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57352</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100136</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lappuggla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Strix nebulosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>810599</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7171453</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2014-10-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2014-10-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>satt i en gran längs vägen</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122645804</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57399</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>810405</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7171515</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122645708</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>810319</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7171477</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122645789</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>810427</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7171501</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122645713</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>810368</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7171378</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122649837</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>810545</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7171458</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122645893</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57383</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>810397</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7171536</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>födosök på gran men kan vara från en annan hackspett</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122645705</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>810319</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7171499</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>391091</v>
+      </c>
+      <c r="B22" t="n">
+        <v>81235</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>810860.7270867341</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7171669.623737417</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2007-12-31</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2055139</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78097</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>810860.7270867341</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7171669.623737417</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2007-12-31</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>292476</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79432</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tallskog Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>810917.5546458759</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7171682.39060352</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2007-06-01</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2007-10-31</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>rapport från Patrik Nygren, SNF</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Via Jonas F Grahn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>292265</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79432</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>810860.7270867341</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7171669.623737417</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2007-12-31</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122650292</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>810931</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7171669</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122650270</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>811036</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7171698</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122650339</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57383</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>810833</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7171605</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal senvuxen gran</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122650264</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>811045</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7171680</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122650350</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>810833</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7171605</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122650329</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>810886</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7171642</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122650066</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>810939</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7171504</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122649988</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>810939</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7171498</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122649892</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>810633</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7171420</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122649934</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57383</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>810828</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7171441</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122649921</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78656</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>810786</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7171426</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122650277</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57399</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>811014</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7171734</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>hack i gran, både äldre och färska hack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122649804</v>
+        <v>122645713</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810465</v>
+        <v>810368</v>
       </c>
       <c r="R4" t="n">
-        <v>7171522</v>
+        <v>7171378</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1019,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645698</v>
+        <v>122645893</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810288</v>
+        <v>810397</v>
       </c>
       <c r="R5" t="n">
-        <v>7171439</v>
+        <v>7171536</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>barksprätt på senvuxen gammelgran</t>
+          <t>födosök på gran men kan vara från en annan hackspett</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122649813</v>
+        <v>122649804</v>
       </c>
       <c r="B6" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,21 +1150,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810503</v>
+        <v>810465</v>
       </c>
       <c r="R6" t="n">
-        <v>7171478</v>
+        <v>7171522</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122645725</v>
+        <v>122645768</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,30 +1260,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1291,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810444</v>
+        <v>810402</v>
       </c>
       <c r="R7" t="n">
-        <v>7171408</v>
+        <v>7171498</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,13 +1330,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>påbörjat bohål?</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1354,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122645881</v>
+        <v>122650377</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>90798</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,31 +1371,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1401,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810380</v>
+        <v>810600</v>
       </c>
       <c r="R8" t="n">
-        <v>7171534</v>
+        <v>7171604</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122649797</v>
+        <v>122645747</v>
       </c>
       <c r="B9" t="n">
-        <v>56585</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,16 +1485,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1502,7 +1507,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1512,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>810426</v>
+        <v>810444</v>
       </c>
       <c r="R9" t="n">
-        <v>7171539</v>
+        <v>7171459</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,6 +1553,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>barksprätt på gammelgran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122645747</v>
+        <v>122649797</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>56585</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,16 +1600,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1612,7 +1622,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1622,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>810444</v>
+        <v>810426</v>
       </c>
       <c r="R10" t="n">
-        <v>7171459</v>
+        <v>7171539</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,11 +1668,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>barksprätt på gammelgran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,10 +1694,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122645768</v>
+        <v>122645705</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,31 +1710,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1737,10 +1741,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810402</v>
+        <v>810319</v>
       </c>
       <c r="R11" t="n">
-        <v>7171498</v>
+        <v>7171499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,17 +1779,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>påbörjat bohål?</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1804,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122645753</v>
+        <v>122645698</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,30 +1820,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1851,10 +1852,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810433</v>
+        <v>810288</v>
       </c>
       <c r="R12" t="n">
-        <v>7171480</v>
+        <v>7171439</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,13 +1890,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>barksprätt på senvuxen gammelgran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1914,10 +1919,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122650377</v>
+        <v>122649813</v>
       </c>
       <c r="B13" t="n">
-        <v>90798</v>
+        <v>78690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,31 +1931,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1961,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810600</v>
+        <v>810503</v>
       </c>
       <c r="R13" t="n">
-        <v>7171604</v>
+        <v>7171478</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122649880</v>
+        <v>122645789</v>
       </c>
       <c r="B14" t="n">
-        <v>57352</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,31 +2041,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100136</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2068,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810599</v>
+        <v>810427</v>
       </c>
       <c r="R14" t="n">
-        <v>7171453</v>
+        <v>7171501</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,17 +2106,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>satt i en gran längs vägen</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,6 +2120,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2135,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122645804</v>
+        <v>122645708</v>
       </c>
       <c r="B15" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,31 +2155,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2183,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810405</v>
+        <v>810319</v>
       </c>
       <c r="R15" t="n">
-        <v>7171515</v>
+        <v>7171477</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2221,17 +2224,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2250,7 +2249,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122645708</v>
+        <v>122645753</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2297,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>810319</v>
+        <v>810433</v>
       </c>
       <c r="R16" t="n">
-        <v>7171477</v>
+        <v>7171480</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122645789</v>
+        <v>122649880</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>57352</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2372,34 +2371,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100136</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2407,10 +2403,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>810427</v>
+        <v>810599</v>
       </c>
       <c r="R17" t="n">
-        <v>7171501</v>
+        <v>7171453</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,12 +2433,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>satt i en gran längs vägen</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,7 +2452,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2470,10 +2470,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122645713</v>
+        <v>122645804</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2486,30 +2486,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2517,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810368</v>
+        <v>810405</v>
       </c>
       <c r="R18" t="n">
-        <v>7171378</v>
+        <v>7171515</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2555,13 +2556,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2690,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122645893</v>
+        <v>122645881</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2706,31 +2711,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2738,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>810397</v>
+        <v>810380</v>
       </c>
       <c r="R20" t="n">
-        <v>7171536</v>
+        <v>7171534</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,17 +2780,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>födosök på gran men kan vara från en annan hackspett</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122645705</v>
+        <v>122645725</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810319</v>
+        <v>810444</v>
       </c>
       <c r="R21" t="n">
-        <v>7171499</v>
+        <v>7171408</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3370,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122650292</v>
+        <v>122649934</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3386,30 +3386,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3417,10 +3418,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810931</v>
+        <v>810828</v>
       </c>
       <c r="R26" t="n">
-        <v>7171669</v>
+        <v>7171441</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,13 +3456,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3480,7 +3485,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122650270</v>
+        <v>122649988</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -3527,10 +3532,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811036</v>
+        <v>810939</v>
       </c>
       <c r="R27" t="n">
-        <v>7171698</v>
+        <v>7171498</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3590,10 +3595,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122650339</v>
+        <v>122650264</v>
       </c>
       <c r="B28" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3606,27 +3611,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3634,10 +3642,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810833</v>
+        <v>811045</v>
       </c>
       <c r="R28" t="n">
-        <v>7171605</v>
+        <v>7171680</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3672,17 +3680,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3701,10 +3705,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122650264</v>
+        <v>122650339</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3717,30 +3721,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3748,10 +3749,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811045</v>
+        <v>810833</v>
       </c>
       <c r="R29" t="n">
-        <v>7171680</v>
+        <v>7171605</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3786,13 +3787,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal senvuxen gran</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3811,7 +3816,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122650350</v>
+        <v>122649921</v>
       </c>
       <c r="B30" t="n">
         <v>78656</v>
@@ -3858,10 +3863,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810833</v>
+        <v>810786</v>
       </c>
       <c r="R30" t="n">
-        <v>7171605</v>
+        <v>7171426</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3921,7 +3926,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122650329</v>
+        <v>122650292</v>
       </c>
       <c r="B31" t="n">
         <v>78656</v>
@@ -3968,10 +3973,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810886</v>
+        <v>810931</v>
       </c>
       <c r="R31" t="n">
-        <v>7171642</v>
+        <v>7171669</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4031,7 +4036,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122650066</v>
+        <v>122650270</v>
       </c>
       <c r="B32" t="n">
         <v>78656</v>
@@ -4078,10 +4083,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810939</v>
+        <v>811036</v>
       </c>
       <c r="R32" t="n">
-        <v>7171504</v>
+        <v>7171698</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4141,10 +4146,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122649988</v>
+        <v>122650277</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4157,30 +4162,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4188,10 +4194,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810939</v>
+        <v>811014</v>
       </c>
       <c r="R33" t="n">
-        <v>7171498</v>
+        <v>7171734</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4226,13 +4232,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>hack i gran, både äldre och färska hack</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4251,7 +4261,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122649892</v>
+        <v>122650066</v>
       </c>
       <c r="B34" t="n">
         <v>78656</v>
@@ -4298,10 +4308,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>810633</v>
+        <v>810939</v>
       </c>
       <c r="R34" t="n">
-        <v>7171420</v>
+        <v>7171504</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4361,10 +4371,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122649934</v>
+        <v>122649892</v>
       </c>
       <c r="B35" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4377,31 +4387,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4409,10 +4418,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810828</v>
+        <v>810633</v>
       </c>
       <c r="R35" t="n">
-        <v>7171441</v>
+        <v>7171420</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4447,17 +4456,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>äldre ringhack i gran</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4476,7 +4481,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122649921</v>
+        <v>122650329</v>
       </c>
       <c r="B36" t="n">
         <v>78656</v>
@@ -4523,10 +4528,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>810786</v>
+        <v>810886</v>
       </c>
       <c r="R36" t="n">
-        <v>7171426</v>
+        <v>7171642</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4586,10 +4591,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122650277</v>
+        <v>122650350</v>
       </c>
       <c r="B37" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4602,31 +4607,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4634,10 +4638,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811014</v>
+        <v>810833</v>
       </c>
       <c r="R37" t="n">
-        <v>7171734</v>
+        <v>7171605</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4672,17 +4676,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>hack i gran, både äldre och färska hack</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645713</v>
+        <v>122645768</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,30 +925,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810368</v>
+        <v>810402</v>
       </c>
       <c r="R4" t="n">
-        <v>7171378</v>
+        <v>7171498</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,13 +995,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>påbörjat bohål?</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1019,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645893</v>
+        <v>122645753</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,31 +1040,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810397</v>
+        <v>810433</v>
       </c>
       <c r="R5" t="n">
-        <v>7171536</v>
+        <v>7171480</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,17 +1109,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>födosök på gran men kan vara från en annan hackspett</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122649804</v>
+        <v>122649880</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>57353</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,34 +1146,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100136</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1181,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810465</v>
+        <v>810599</v>
       </c>
       <c r="R6" t="n">
-        <v>7171522</v>
+        <v>7171453</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,12 +1208,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>satt i en gran längs vägen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,7 +1227,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1244,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122645768</v>
+        <v>122650377</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>90799</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,35 +1257,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810402</v>
+        <v>810600</v>
       </c>
       <c r="R7" t="n">
-        <v>7171498</v>
+        <v>7171604</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,17 +1330,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>påbörjat bohål?</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1359,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122650377</v>
+        <v>122645725</v>
       </c>
       <c r="B8" t="n">
-        <v>90798</v>
+        <v>78657</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,31 +1367,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1406,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810600</v>
+        <v>810444</v>
       </c>
       <c r="R8" t="n">
-        <v>7171604</v>
+        <v>7171408</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122645747</v>
+        <v>122649797</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>56586</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,16 +1481,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1507,7 +1503,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1517,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>810444</v>
+        <v>810426</v>
       </c>
       <c r="R9" t="n">
-        <v>7171459</v>
+        <v>7171539</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,11 +1549,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>barksprätt på gammelgran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122649797</v>
+        <v>122649804</v>
       </c>
       <c r="B10" t="n">
-        <v>56585</v>
+        <v>78657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,31 +1591,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1632,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>810426</v>
+        <v>810465</v>
       </c>
       <c r="R10" t="n">
-        <v>7171539</v>
+        <v>7171522</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,6 +1666,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1694,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122645705</v>
+        <v>122649813</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>78691</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,21 +1701,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810319</v>
+        <v>810503</v>
       </c>
       <c r="R11" t="n">
-        <v>7171499</v>
+        <v>7171478</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122645698</v>
+        <v>122645713</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,31 +1811,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1852,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810288</v>
+        <v>810368</v>
       </c>
       <c r="R12" t="n">
-        <v>7171439</v>
+        <v>7171378</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,17 +1880,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>barksprätt på senvuxen gammelgran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1919,10 +1905,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122649813</v>
+        <v>122645789</v>
       </c>
       <c r="B13" t="n">
-        <v>78690</v>
+        <v>78657</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,21 +1921,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1966,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810503</v>
+        <v>810427</v>
       </c>
       <c r="R13" t="n">
-        <v>7171478</v>
+        <v>7171501</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2029,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122645789</v>
+        <v>122645747</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,30 +2031,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2076,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810427</v>
+        <v>810444</v>
       </c>
       <c r="R14" t="n">
-        <v>7171501</v>
+        <v>7171459</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2114,13 +2101,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>barksprätt på gammelgran</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2139,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122645708</v>
+        <v>122645698</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,30 +2146,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2186,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810319</v>
+        <v>810288</v>
       </c>
       <c r="R15" t="n">
-        <v>7171477</v>
+        <v>7171439</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2224,13 +2216,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>barksprätt på senvuxen gammelgran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2249,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122645753</v>
+        <v>122645881</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>810433</v>
+        <v>810380</v>
       </c>
       <c r="R16" t="n">
-        <v>7171480</v>
+        <v>7171534</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2359,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122649880</v>
+        <v>122649837</v>
       </c>
       <c r="B17" t="n">
-        <v>57352</v>
+        <v>78657</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,31 +2367,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100136</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2403,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>810599</v>
+        <v>810545</v>
       </c>
       <c r="R17" t="n">
-        <v>7171453</v>
+        <v>7171458</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,17 +2432,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>satt i en gran längs vägen</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,6 +2446,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2470,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122645804</v>
+        <v>122645705</v>
       </c>
       <c r="B18" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2486,31 +2481,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2518,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810405</v>
+        <v>810319</v>
       </c>
       <c r="R18" t="n">
-        <v>7171515</v>
+        <v>7171499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,17 +2550,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2585,10 +2575,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122649837</v>
+        <v>122645893</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,30 +2591,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2632,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810545</v>
+        <v>810397</v>
       </c>
       <c r="R19" t="n">
-        <v>7171458</v>
+        <v>7171536</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2670,13 +2661,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>födosök på gran men kan vara från en annan hackspett</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2695,10 +2690,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122645881</v>
+        <v>122645708</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2742,10 +2737,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>810380</v>
+        <v>810319</v>
       </c>
       <c r="R20" t="n">
-        <v>7171534</v>
+        <v>7171477</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2805,10 +2800,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122645725</v>
+        <v>122645804</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2821,30 +2816,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2852,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810444</v>
+        <v>810405</v>
       </c>
       <c r="R21" t="n">
-        <v>7171408</v>
+        <v>7171515</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2890,13 +2886,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3370,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122649934</v>
+        <v>122649921</v>
       </c>
       <c r="B26" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3386,31 +3386,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3418,10 +3417,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810828</v>
+        <v>810786</v>
       </c>
       <c r="R26" t="n">
-        <v>7171441</v>
+        <v>7171426</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3456,17 +3455,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>äldre ringhack i gran</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3485,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122649988</v>
+        <v>122650339</v>
       </c>
       <c r="B27" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,30 +3496,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3532,10 +3524,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810939</v>
+        <v>810833</v>
       </c>
       <c r="R27" t="n">
-        <v>7171498</v>
+        <v>7171605</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3570,13 +3562,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal senvuxen gran</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3598,7 +3594,7 @@
         <v>122650264</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3705,10 +3701,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122650339</v>
+        <v>122650066</v>
       </c>
       <c r="B29" t="n">
-        <v>57383</v>
+        <v>78657</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3721,27 +3717,30 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3749,10 +3748,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810833</v>
+        <v>810939</v>
       </c>
       <c r="R29" t="n">
-        <v>7171605</v>
+        <v>7171504</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3787,17 +3786,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3816,10 +3811,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122649921</v>
+        <v>122650329</v>
       </c>
       <c r="B30" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3863,10 +3858,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810786</v>
+        <v>810886</v>
       </c>
       <c r="R30" t="n">
-        <v>7171426</v>
+        <v>7171642</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3926,10 +3921,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122650292</v>
+        <v>122649892</v>
       </c>
       <c r="B31" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3973,10 +3968,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810931</v>
+        <v>810633</v>
       </c>
       <c r="R31" t="n">
-        <v>7171669</v>
+        <v>7171420</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4039,7 +4034,7 @@
         <v>122650270</v>
       </c>
       <c r="B32" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4146,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122650277</v>
+        <v>122650350</v>
       </c>
       <c r="B33" t="n">
-        <v>57399</v>
+        <v>78657</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4162,31 +4157,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4194,10 +4188,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811014</v>
+        <v>810833</v>
       </c>
       <c r="R33" t="n">
-        <v>7171734</v>
+        <v>7171605</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,17 +4226,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>hack i gran, både äldre och färska hack</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4261,10 +4251,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122650066</v>
+        <v>122649988</v>
       </c>
       <c r="B34" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4311,7 +4301,7 @@
         <v>810939</v>
       </c>
       <c r="R34" t="n">
-        <v>7171504</v>
+        <v>7171498</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4371,10 +4361,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122649892</v>
+        <v>122650277</v>
       </c>
       <c r="B35" t="n">
-        <v>78656</v>
+        <v>57400</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4387,30 +4377,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4418,10 +4409,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810633</v>
+        <v>811014</v>
       </c>
       <c r="R35" t="n">
-        <v>7171420</v>
+        <v>7171734</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,13 +4447,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>hack i gran, både äldre och färska hack</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4481,10 +4476,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122650329</v>
+        <v>122650292</v>
       </c>
       <c r="B36" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4528,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>810886</v>
+        <v>810931</v>
       </c>
       <c r="R36" t="n">
-        <v>7171642</v>
+        <v>7171669</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4591,10 +4586,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122650350</v>
+        <v>122649934</v>
       </c>
       <c r="B37" t="n">
-        <v>78656</v>
+        <v>57384</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4607,30 +4602,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4638,10 +4634,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810833</v>
+        <v>810828</v>
       </c>
       <c r="R37" t="n">
-        <v>7171605</v>
+        <v>7171441</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4676,13 +4672,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -2015,7 +2015,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122645747</v>
+        <v>122645698</v>
       </c>
       <c r="B14" t="n">
         <v>57384</v>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810444</v>
+        <v>810288</v>
       </c>
       <c r="R14" t="n">
-        <v>7171459</v>
+        <v>7171439</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>barksprätt på gammelgran</t>
+          <t>barksprätt på senvuxen gammelgran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,7 +2130,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122645698</v>
+        <v>122645747</v>
       </c>
       <c r="B15" t="n">
         <v>57384</v>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810288</v>
+        <v>810444</v>
       </c>
       <c r="R15" t="n">
-        <v>7171439</v>
+        <v>7171459</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>barksprätt på senvuxen gammelgran</t>
+          <t>barksprätt på gammelgran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3480,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122650339</v>
+        <v>122650264</v>
       </c>
       <c r="B27" t="n">
-        <v>57384</v>
+        <v>78657</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3496,27 +3496,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3524,10 +3527,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810833</v>
+        <v>811045</v>
       </c>
       <c r="R27" t="n">
-        <v>7171605</v>
+        <v>7171680</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3562,17 +3565,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3591,10 +3590,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122650264</v>
+        <v>122650339</v>
       </c>
       <c r="B28" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3607,30 +3606,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3638,10 +3634,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811045</v>
+        <v>810833</v>
       </c>
       <c r="R28" t="n">
-        <v>7171680</v>
+        <v>7171605</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3676,13 +3672,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal senvuxen gran</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4031,7 +4031,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122650270</v>
+        <v>122649988</v>
       </c>
       <c r="B32" t="n">
         <v>78657</v>
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811036</v>
+        <v>810939</v>
       </c>
       <c r="R32" t="n">
-        <v>7171698</v>
+        <v>7171498</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4141,7 +4141,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122650350</v>
+        <v>122650270</v>
       </c>
       <c r="B33" t="n">
         <v>78657</v>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810833</v>
+        <v>811036</v>
       </c>
       <c r="R33" t="n">
-        <v>7171605</v>
+        <v>7171698</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4251,7 +4251,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122649988</v>
+        <v>122650350</v>
       </c>
       <c r="B34" t="n">
         <v>78657</v>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>810939</v>
+        <v>810833</v>
       </c>
       <c r="R34" t="n">
-        <v>7171498</v>
+        <v>7171605</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645768</v>
+        <v>122645705</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,31 +925,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810402</v>
+        <v>810319</v>
       </c>
       <c r="R4" t="n">
-        <v>7171498</v>
+        <v>7171499</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,17 +994,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>påbörjat bohål?</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1024,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645753</v>
+        <v>122645698</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,30 +1035,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810433</v>
+        <v>810288</v>
       </c>
       <c r="R5" t="n">
-        <v>7171480</v>
+        <v>7171439</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,13 +1105,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>barksprätt på senvuxen gammelgran</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122650377</v>
+        <v>122649797</v>
       </c>
       <c r="B7" t="n">
-        <v>90799</v>
+        <v>56586</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,34 +1257,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1292,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810600</v>
+        <v>810426</v>
       </c>
       <c r="R7" t="n">
-        <v>7171604</v>
+        <v>7171539</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,7 +1337,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122645725</v>
+        <v>122645708</v>
       </c>
       <c r="B8" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810444</v>
+        <v>810319</v>
       </c>
       <c r="R8" t="n">
-        <v>7171408</v>
+        <v>7171477</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122649797</v>
+        <v>122645713</v>
       </c>
       <c r="B9" t="n">
-        <v>56586</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,31 +1481,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1513,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>810426</v>
+        <v>810368</v>
       </c>
       <c r="R9" t="n">
-        <v>7171539</v>
+        <v>7171378</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,6 +1556,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122649804</v>
+        <v>122645804</v>
       </c>
       <c r="B10" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,30 +1591,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1622,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>810465</v>
+        <v>810405</v>
       </c>
       <c r="R10" t="n">
-        <v>7171522</v>
+        <v>7171515</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,13 +1661,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1685,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122649813</v>
+        <v>122650377</v>
       </c>
       <c r="B11" t="n">
-        <v>78691</v>
+        <v>90802</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,31 +1702,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1732,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810503</v>
+        <v>810600</v>
       </c>
       <c r="R11" t="n">
-        <v>7171478</v>
+        <v>7171604</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122645713</v>
+        <v>122645789</v>
       </c>
       <c r="B12" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810368</v>
+        <v>810427</v>
       </c>
       <c r="R12" t="n">
-        <v>7171378</v>
+        <v>7171501</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122645789</v>
+        <v>122649804</v>
       </c>
       <c r="B13" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810427</v>
+        <v>810465</v>
       </c>
       <c r="R13" t="n">
-        <v>7171501</v>
+        <v>7171522</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122645698</v>
+        <v>122645725</v>
       </c>
       <c r="B14" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,31 +2036,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2063,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810288</v>
+        <v>810444</v>
       </c>
       <c r="R14" t="n">
-        <v>7171439</v>
+        <v>7171408</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,17 +2105,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>barksprätt på senvuxen gammelgran</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122645747</v>
+        <v>122645768</v>
       </c>
       <c r="B15" t="n">
         <v>57384</v>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810444</v>
+        <v>810402</v>
       </c>
       <c r="R15" t="n">
-        <v>7171459</v>
+        <v>7171498</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>barksprätt på gammelgran</t>
+          <t>påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2245,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122645881</v>
+        <v>122645893</v>
       </c>
       <c r="B16" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,30 +2261,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2292,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>810380</v>
+        <v>810397</v>
       </c>
       <c r="R16" t="n">
-        <v>7171534</v>
+        <v>7171536</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2330,13 +2331,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>födosök på gran men kan vara från en annan hackspett</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2355,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122649837</v>
+        <v>122645881</v>
       </c>
       <c r="B17" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,10 +2407,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>810545</v>
+        <v>810380</v>
       </c>
       <c r="R17" t="n">
-        <v>7171458</v>
+        <v>7171534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,10 +2470,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122645705</v>
+        <v>122649813</v>
       </c>
       <c r="B18" t="n">
-        <v>78657</v>
+        <v>78694</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2481,21 +2486,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810319</v>
+        <v>810503</v>
       </c>
       <c r="R18" t="n">
-        <v>7171499</v>
+        <v>7171478</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2575,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122645893</v>
+        <v>122645753</v>
       </c>
       <c r="B19" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,31 +2596,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2623,10 +2627,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810397</v>
+        <v>810433</v>
       </c>
       <c r="R19" t="n">
-        <v>7171536</v>
+        <v>7171480</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2661,17 +2665,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>födosök på gran men kan vara från en annan hackspett</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122645708</v>
+        <v>122649837</v>
       </c>
       <c r="B20" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>810319</v>
+        <v>810545</v>
       </c>
       <c r="R20" t="n">
-        <v>7171477</v>
+        <v>7171458</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122645804</v>
+        <v>122645747</v>
       </c>
       <c r="B21" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810405</v>
+        <v>810444</v>
       </c>
       <c r="R21" t="n">
-        <v>7171515</v>
+        <v>7171459</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>hack i gran</t>
+          <t>barksprätt på gammelgran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3370,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122649921</v>
+        <v>122649934</v>
       </c>
       <c r="B26" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3386,30 +3386,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3417,10 +3418,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810786</v>
+        <v>810828</v>
       </c>
       <c r="R26" t="n">
-        <v>7171426</v>
+        <v>7171441</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,13 +3456,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3480,10 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122650264</v>
+        <v>122650270</v>
       </c>
       <c r="B27" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3527,10 +3532,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811045</v>
+        <v>811036</v>
       </c>
       <c r="R27" t="n">
-        <v>7171680</v>
+        <v>7171698</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3590,10 +3595,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122650339</v>
+        <v>122649921</v>
       </c>
       <c r="B28" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3606,27 +3611,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3634,10 +3642,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810833</v>
+        <v>810786</v>
       </c>
       <c r="R28" t="n">
-        <v>7171605</v>
+        <v>7171426</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3672,17 +3680,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3701,10 +3705,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122650066</v>
+        <v>122650292</v>
       </c>
       <c r="B29" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3748,10 +3752,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810939</v>
+        <v>810931</v>
       </c>
       <c r="R29" t="n">
-        <v>7171504</v>
+        <v>7171669</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3811,10 +3815,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122650329</v>
+        <v>122649988</v>
       </c>
       <c r="B30" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3858,10 +3862,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810886</v>
+        <v>810939</v>
       </c>
       <c r="R30" t="n">
-        <v>7171642</v>
+        <v>7171498</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3921,10 +3925,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122649892</v>
+        <v>122650329</v>
       </c>
       <c r="B31" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3968,10 +3972,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810633</v>
+        <v>810886</v>
       </c>
       <c r="R31" t="n">
-        <v>7171420</v>
+        <v>7171642</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4031,10 +4035,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122649988</v>
+        <v>122650339</v>
       </c>
       <c r="B32" t="n">
-        <v>78657</v>
+        <v>57384</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4047,30 +4051,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4078,10 +4079,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810939</v>
+        <v>810833</v>
       </c>
       <c r="R32" t="n">
-        <v>7171498</v>
+        <v>7171605</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4116,13 +4117,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal senvuxen gran</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4141,10 +4146,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122650270</v>
+        <v>122650264</v>
       </c>
       <c r="B33" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4188,10 +4193,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811036</v>
+        <v>811045</v>
       </c>
       <c r="R33" t="n">
-        <v>7171698</v>
+        <v>7171680</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4251,10 +4256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122650350</v>
+        <v>122650277</v>
       </c>
       <c r="B34" t="n">
-        <v>78657</v>
+        <v>57400</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4267,30 +4272,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4298,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>810833</v>
+        <v>811014</v>
       </c>
       <c r="R34" t="n">
-        <v>7171605</v>
+        <v>7171734</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4336,13 +4342,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>hack i gran, både äldre och färska hack</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4361,10 +4371,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122650277</v>
+        <v>122650350</v>
       </c>
       <c r="B35" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4377,31 +4387,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4409,10 +4418,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811014</v>
+        <v>810833</v>
       </c>
       <c r="R35" t="n">
-        <v>7171734</v>
+        <v>7171605</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4447,17 +4456,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>hack i gran, både äldre och färska hack</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4476,10 +4481,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122650292</v>
+        <v>122650066</v>
       </c>
       <c r="B36" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4523,10 +4528,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>810931</v>
+        <v>810939</v>
       </c>
       <c r="R36" t="n">
-        <v>7171669</v>
+        <v>7171504</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4586,10 +4591,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122649934</v>
+        <v>122649892</v>
       </c>
       <c r="B37" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4602,31 +4607,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4634,10 +4638,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810828</v>
+        <v>810633</v>
       </c>
       <c r="R37" t="n">
-        <v>7171441</v>
+        <v>7171420</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4672,17 +4676,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>äldre ringhack i gran</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645705</v>
+        <v>122645804</v>
       </c>
       <c r="B4" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,30 +925,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810319</v>
+        <v>810405</v>
       </c>
       <c r="R4" t="n">
-        <v>7171499</v>
+        <v>7171515</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,13 +995,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1134,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122649880</v>
+        <v>122645789</v>
       </c>
       <c r="B6" t="n">
-        <v>57353</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,31 +1151,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100136</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810599</v>
+        <v>810427</v>
       </c>
       <c r="R6" t="n">
-        <v>7171453</v>
+        <v>7171501</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,17 +1216,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>satt i en gran längs vägen</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,6 +1230,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1245,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122649797</v>
+        <v>122645747</v>
       </c>
       <c r="B7" t="n">
-        <v>56586</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,16 +1265,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1283,7 +1287,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1293,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810426</v>
+        <v>810444</v>
       </c>
       <c r="R7" t="n">
-        <v>7171539</v>
+        <v>7171459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,6 +1333,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>barksprätt på gammelgran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,7 +1364,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122645708</v>
+        <v>122649804</v>
       </c>
       <c r="B8" t="n">
         <v>78660</v>
@@ -1402,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810319</v>
+        <v>810465</v>
       </c>
       <c r="R8" t="n">
-        <v>7171477</v>
+        <v>7171522</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,7 +1474,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122645713</v>
+        <v>122645708</v>
       </c>
       <c r="B9" t="n">
         <v>78660</v>
@@ -1512,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>810368</v>
+        <v>810319</v>
       </c>
       <c r="R9" t="n">
-        <v>7171378</v>
+        <v>7171477</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122645804</v>
+        <v>122645768</v>
       </c>
       <c r="B10" t="n">
-        <v>57400</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,16 +1600,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1623,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>810405</v>
+        <v>810402</v>
       </c>
       <c r="R10" t="n">
-        <v>7171515</v>
+        <v>7171498</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,7 +1672,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>hack i gran</t>
+          <t>påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122645789</v>
+        <v>122649813</v>
       </c>
       <c r="B12" t="n">
-        <v>78660</v>
+        <v>78694</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,21 +1825,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1847,10 +1856,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810427</v>
+        <v>810503</v>
       </c>
       <c r="R12" t="n">
-        <v>7171501</v>
+        <v>7171478</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,10 +1919,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122649804</v>
+        <v>122645893</v>
       </c>
       <c r="B13" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,30 +1935,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1957,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810465</v>
+        <v>810397</v>
       </c>
       <c r="R13" t="n">
-        <v>7171522</v>
+        <v>7171536</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,13 +2005,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>födosök på gran men kan vara från en annan hackspett</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2130,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122645768</v>
+        <v>122645753</v>
       </c>
       <c r="B15" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,31 +2160,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2178,10 +2191,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810402</v>
+        <v>810433</v>
       </c>
       <c r="R15" t="n">
-        <v>7171498</v>
+        <v>7171480</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,17 +2229,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>påbörjat bohål?</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2245,10 +2254,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122645893</v>
+        <v>122649837</v>
       </c>
       <c r="B16" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,31 +2270,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2293,10 +2301,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>810397</v>
+        <v>810545</v>
       </c>
       <c r="R16" t="n">
-        <v>7171536</v>
+        <v>7171458</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,17 +2339,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>födosök på gran men kan vara från en annan hackspett</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2360,7 +2364,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122645881</v>
+        <v>122645705</v>
       </c>
       <c r="B17" t="n">
         <v>78660</v>
@@ -2407,10 +2411,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>810380</v>
+        <v>810319</v>
       </c>
       <c r="R17" t="n">
-        <v>7171534</v>
+        <v>7171499</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2470,10 +2474,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122649813</v>
+        <v>122645881</v>
       </c>
       <c r="B18" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2486,21 +2490,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2517,10 +2521,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810503</v>
+        <v>810380</v>
       </c>
       <c r="R18" t="n">
-        <v>7171478</v>
+        <v>7171534</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2580,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122645753</v>
+        <v>122649880</v>
       </c>
       <c r="B19" t="n">
-        <v>78660</v>
+        <v>57353</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2592,34 +2596,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100136</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2627,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810433</v>
+        <v>810599</v>
       </c>
       <c r="R19" t="n">
-        <v>7171480</v>
+        <v>7171453</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2657,12 +2658,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>satt i en gran längs vägen</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,7 +2677,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2690,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122649837</v>
+        <v>122649797</v>
       </c>
       <c r="B20" t="n">
-        <v>78660</v>
+        <v>56586</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2706,30 +2711,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2737,10 +2743,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>810545</v>
+        <v>810426</v>
       </c>
       <c r="R20" t="n">
-        <v>7171458</v>
+        <v>7171539</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,7 +2787,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2800,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122645747</v>
+        <v>122645713</v>
       </c>
       <c r="B21" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2816,31 +2821,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2848,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810444</v>
+        <v>810368</v>
       </c>
       <c r="R21" t="n">
-        <v>7171459</v>
+        <v>7171378</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2886,17 +2890,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>barksprätt på gammelgran</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3370,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122649934</v>
+        <v>122650270</v>
       </c>
       <c r="B26" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3386,31 +3386,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3418,10 +3417,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810828</v>
+        <v>811036</v>
       </c>
       <c r="R26" t="n">
-        <v>7171441</v>
+        <v>7171698</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3456,17 +3455,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>äldre ringhack i gran</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3485,7 +3480,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122650270</v>
+        <v>122650066</v>
       </c>
       <c r="B27" t="n">
         <v>78660</v>
@@ -3532,10 +3527,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811036</v>
+        <v>810939</v>
       </c>
       <c r="R27" t="n">
-        <v>7171698</v>
+        <v>7171504</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3595,7 +3590,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122649921</v>
+        <v>122650264</v>
       </c>
       <c r="B28" t="n">
         <v>78660</v>
@@ -3642,10 +3637,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810786</v>
+        <v>811045</v>
       </c>
       <c r="R28" t="n">
-        <v>7171426</v>
+        <v>7171680</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3705,10 +3700,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122650292</v>
+        <v>122650339</v>
       </c>
       <c r="B29" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3721,30 +3716,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3752,10 +3744,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810931</v>
+        <v>810833</v>
       </c>
       <c r="R29" t="n">
-        <v>7171669</v>
+        <v>7171605</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3790,13 +3782,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal senvuxen gran</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3815,7 +3811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122649988</v>
+        <v>122649892</v>
       </c>
       <c r="B30" t="n">
         <v>78660</v>
@@ -3862,10 +3858,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810939</v>
+        <v>810633</v>
       </c>
       <c r="R30" t="n">
-        <v>7171498</v>
+        <v>7171420</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3925,7 +3921,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122650329</v>
+        <v>122649988</v>
       </c>
       <c r="B31" t="n">
         <v>78660</v>
@@ -3972,10 +3968,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810886</v>
+        <v>810939</v>
       </c>
       <c r="R31" t="n">
-        <v>7171642</v>
+        <v>7171498</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4035,10 +4031,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122650339</v>
+        <v>122650292</v>
       </c>
       <c r="B32" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4051,27 +4047,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4079,10 +4078,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810833</v>
+        <v>810931</v>
       </c>
       <c r="R32" t="n">
-        <v>7171605</v>
+        <v>7171669</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4117,17 +4116,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4146,10 +4141,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122650264</v>
+        <v>122649934</v>
       </c>
       <c r="B33" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4162,30 +4157,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4193,10 +4189,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811045</v>
+        <v>810828</v>
       </c>
       <c r="R33" t="n">
-        <v>7171680</v>
+        <v>7171441</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4231,13 +4227,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122650277</v>
+        <v>122650329</v>
       </c>
       <c r="B34" t="n">
-        <v>57400</v>
+        <v>78660</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4272,31 +4272,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4304,10 +4303,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811014</v>
+        <v>810886</v>
       </c>
       <c r="R34" t="n">
-        <v>7171734</v>
+        <v>7171642</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4342,17 +4341,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>hack i gran, både äldre och färska hack</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4371,10 +4366,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122650350</v>
+        <v>122650277</v>
       </c>
       <c r="B35" t="n">
-        <v>78660</v>
+        <v>57400</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4387,30 +4382,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4418,10 +4414,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810833</v>
+        <v>811014</v>
       </c>
       <c r="R35" t="n">
-        <v>7171605</v>
+        <v>7171734</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,13 +4452,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>hack i gran, både äldre och färska hack</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4481,7 +4481,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122650066</v>
+        <v>122649921</v>
       </c>
       <c r="B36" t="n">
         <v>78660</v>
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>810939</v>
+        <v>810786</v>
       </c>
       <c r="R36" t="n">
-        <v>7171504</v>
+        <v>7171426</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4591,7 +4591,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122649892</v>
+        <v>122650350</v>
       </c>
       <c r="B37" t="n">
         <v>78660</v>
@@ -4638,10 +4638,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810633</v>
+        <v>810833</v>
       </c>
       <c r="R37" t="n">
-        <v>7171420</v>
+        <v>7171605</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645804</v>
+        <v>122645753</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>78762</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,31 +925,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810405</v>
+        <v>810433</v>
       </c>
       <c r="R4" t="n">
-        <v>7171515</v>
+        <v>7171480</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,17 +994,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1024,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645698</v>
+        <v>122645804</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,16 +1035,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1072,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810288</v>
+        <v>810405</v>
       </c>
       <c r="R5" t="n">
-        <v>7171439</v>
+        <v>7171515</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1107,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>barksprätt på senvuxen gammelgran</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122645789</v>
+        <v>122645747</v>
       </c>
       <c r="B6" t="n">
-        <v>78660</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,30 +1150,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1186,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810427</v>
+        <v>810444</v>
       </c>
       <c r="R6" t="n">
-        <v>7171501</v>
+        <v>7171459</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,13 +1220,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>barksprätt på gammelgran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1249,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122645747</v>
+        <v>122645725</v>
       </c>
       <c r="B7" t="n">
-        <v>57384</v>
+        <v>78762</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,31 +1265,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1300,7 +1299,7 @@
         <v>810444</v>
       </c>
       <c r="R7" t="n">
-        <v>7171459</v>
+        <v>7171408</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,17 +1334,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>barksprätt på gammelgran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1364,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122649804</v>
+        <v>122649837</v>
       </c>
       <c r="B8" t="n">
-        <v>78660</v>
+        <v>78762</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810465</v>
+        <v>810545</v>
       </c>
       <c r="R8" t="n">
-        <v>7171522</v>
+        <v>7171458</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122645708</v>
+        <v>122650377</v>
       </c>
       <c r="B9" t="n">
-        <v>78660</v>
+        <v>90905</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,31 +1481,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1521,10 +1516,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>810319</v>
+        <v>810600</v>
       </c>
       <c r="R9" t="n">
-        <v>7171477</v>
+        <v>7171604</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122645768</v>
+        <v>122649797</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
+        <v>56680</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,16 +1595,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1622,7 +1617,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1632,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>810402</v>
+        <v>810426</v>
       </c>
       <c r="R10" t="n">
-        <v>7171498</v>
+        <v>7171539</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,11 +1663,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122650377</v>
+        <v>122645698</v>
       </c>
       <c r="B11" t="n">
-        <v>90802</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,34 +1701,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1746,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810600</v>
+        <v>810288</v>
       </c>
       <c r="R11" t="n">
-        <v>7171604</v>
+        <v>7171439</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,13 +1775,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>barksprätt på senvuxen gammelgran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1809,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122649813</v>
+        <v>122649804</v>
       </c>
       <c r="B12" t="n">
-        <v>78694</v>
+        <v>78762</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,21 +1820,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1856,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810503</v>
+        <v>810465</v>
       </c>
       <c r="R12" t="n">
-        <v>7171478</v>
+        <v>7171522</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1919,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122645893</v>
+        <v>122649813</v>
       </c>
       <c r="B13" t="n">
-        <v>57384</v>
+        <v>78796</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,31 +1930,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1967,10 +1961,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810397</v>
+        <v>810503</v>
       </c>
       <c r="R13" t="n">
-        <v>7171536</v>
+        <v>7171478</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,17 +1999,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>födosök på gran men kan vara från en annan hackspett</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2034,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122645725</v>
+        <v>122649880</v>
       </c>
       <c r="B14" t="n">
-        <v>78660</v>
+        <v>57447</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,34 +2036,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100136</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2081,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810444</v>
+        <v>810599</v>
       </c>
       <c r="R14" t="n">
-        <v>7171408</v>
+        <v>7171453</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,12 +2098,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>satt i en gran längs vägen</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2125,7 +2117,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2144,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122645753</v>
+        <v>122645789</v>
       </c>
       <c r="B15" t="n">
-        <v>78660</v>
+        <v>78762</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810433</v>
+        <v>810427</v>
       </c>
       <c r="R15" t="n">
-        <v>7171480</v>
+        <v>7171501</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122649837</v>
+        <v>122645768</v>
       </c>
       <c r="B16" t="n">
-        <v>78660</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2270,30 +2261,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2301,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>810545</v>
+        <v>810402</v>
       </c>
       <c r="R16" t="n">
-        <v>7171458</v>
+        <v>7171498</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,13 +2331,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>påbörjat bohål?</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2364,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122645705</v>
+        <v>122645713</v>
       </c>
       <c r="B17" t="n">
-        <v>78660</v>
+        <v>78762</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2411,10 +2407,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>810319</v>
+        <v>810368</v>
       </c>
       <c r="R17" t="n">
-        <v>7171499</v>
+        <v>7171378</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2474,10 +2470,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122645881</v>
+        <v>122645708</v>
       </c>
       <c r="B18" t="n">
-        <v>78660</v>
+        <v>78762</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810380</v>
+        <v>810319</v>
       </c>
       <c r="R18" t="n">
-        <v>7171534</v>
+        <v>7171477</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122649880</v>
+        <v>122645881</v>
       </c>
       <c r="B19" t="n">
-        <v>57353</v>
+        <v>78762</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,31 +2592,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100136</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2628,10 +2627,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810599</v>
+        <v>810380</v>
       </c>
       <c r="R19" t="n">
-        <v>7171453</v>
+        <v>7171534</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,17 +2657,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>satt i en gran längs vägen</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2677,6 +2671,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2695,10 +2690,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122649797</v>
+        <v>122645893</v>
       </c>
       <c r="B20" t="n">
-        <v>56586</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,16 +2706,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2733,7 +2728,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2743,10 +2738,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>810426</v>
+        <v>810397</v>
       </c>
       <c r="R20" t="n">
-        <v>7171539</v>
+        <v>7171536</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2779,6 +2774,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>födosök på gran men kan vara från en annan hackspett</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2805,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122645713</v>
+        <v>122645705</v>
       </c>
       <c r="B21" t="n">
-        <v>78660</v>
+        <v>78762</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810368</v>
+        <v>810319</v>
       </c>
       <c r="R21" t="n">
-        <v>7171378</v>
+        <v>7171499</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3370,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122650270</v>
+        <v>122650264</v>
       </c>
       <c r="B26" t="n">
-        <v>78660</v>
+        <v>78762</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811036</v>
+        <v>811045</v>
       </c>
       <c r="R26" t="n">
-        <v>7171698</v>
+        <v>7171680</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3483,7 +3483,7 @@
         <v>122650066</v>
       </c>
       <c r="B27" t="n">
-        <v>78660</v>
+        <v>78762</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122650264</v>
+        <v>122649934</v>
       </c>
       <c r="B28" t="n">
-        <v>78660</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3606,30 +3606,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3637,10 +3638,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811045</v>
+        <v>810828</v>
       </c>
       <c r="R28" t="n">
-        <v>7171680</v>
+        <v>7171441</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,13 +3676,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3700,10 +3705,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122650339</v>
+        <v>122649921</v>
       </c>
       <c r="B29" t="n">
-        <v>57384</v>
+        <v>78762</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3716,27 +3721,30 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3744,10 +3752,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810833</v>
+        <v>810786</v>
       </c>
       <c r="R29" t="n">
-        <v>7171605</v>
+        <v>7171426</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3782,17 +3790,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3814,7 +3818,7 @@
         <v>122649892</v>
       </c>
       <c r="B30" t="n">
-        <v>78660</v>
+        <v>78762</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3921,10 +3925,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122649988</v>
+        <v>122650292</v>
       </c>
       <c r="B31" t="n">
-        <v>78660</v>
+        <v>78762</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3968,10 +3972,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810939</v>
+        <v>810931</v>
       </c>
       <c r="R31" t="n">
-        <v>7171498</v>
+        <v>7171669</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4031,10 +4035,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122650292</v>
+        <v>122650350</v>
       </c>
       <c r="B32" t="n">
-        <v>78660</v>
+        <v>78762</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4078,10 +4082,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810931</v>
+        <v>810833</v>
       </c>
       <c r="R32" t="n">
-        <v>7171669</v>
+        <v>7171605</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4141,10 +4145,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122649934</v>
+        <v>122649988</v>
       </c>
       <c r="B33" t="n">
-        <v>57384</v>
+        <v>78762</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4157,31 +4161,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4189,10 +4192,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810828</v>
+        <v>810939</v>
       </c>
       <c r="R33" t="n">
-        <v>7171441</v>
+        <v>7171498</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4227,17 +4230,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>äldre ringhack i gran</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4256,10 +4255,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122650329</v>
+        <v>122650339</v>
       </c>
       <c r="B34" t="n">
-        <v>78660</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4272,30 +4271,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4303,10 +4299,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>810886</v>
+        <v>810833</v>
       </c>
       <c r="R34" t="n">
-        <v>7171642</v>
+        <v>7171605</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4341,13 +4337,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal senvuxen gran</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122650277</v>
+        <v>122650329</v>
       </c>
       <c r="B35" t="n">
-        <v>57400</v>
+        <v>78762</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4382,31 +4382,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4414,10 +4413,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811014</v>
+        <v>810886</v>
       </c>
       <c r="R35" t="n">
-        <v>7171734</v>
+        <v>7171642</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4452,17 +4451,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>hack i gran, både äldre och färska hack</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4481,10 +4476,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122649921</v>
+        <v>122650277</v>
       </c>
       <c r="B36" t="n">
-        <v>78660</v>
+        <v>57494</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4497,30 +4492,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4528,10 +4524,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>810786</v>
+        <v>811014</v>
       </c>
       <c r="R36" t="n">
-        <v>7171426</v>
+        <v>7171734</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4566,13 +4562,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>hack i gran, både äldre och färska hack</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4591,10 +4591,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122650350</v>
+        <v>122650270</v>
       </c>
       <c r="B37" t="n">
-        <v>78660</v>
+        <v>78762</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4638,10 +4638,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810833</v>
+        <v>811036</v>
       </c>
       <c r="R37" t="n">
-        <v>7171605</v>
+        <v>7171698</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -3590,10 +3590,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122649934</v>
+        <v>122649921</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3606,31 +3606,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3638,10 +3637,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810828</v>
+        <v>810786</v>
       </c>
       <c r="R28" t="n">
-        <v>7171441</v>
+        <v>7171426</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3676,17 +3675,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack i gran</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3705,7 +3700,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122649921</v>
+        <v>122649892</v>
       </c>
       <c r="B29" t="n">
         <v>78762</v>
@@ -3752,10 +3747,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810786</v>
+        <v>810633</v>
       </c>
       <c r="R29" t="n">
-        <v>7171426</v>
+        <v>7171420</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3815,10 +3810,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122649892</v>
+        <v>122649934</v>
       </c>
       <c r="B30" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3831,30 +3826,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3862,10 +3858,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810633</v>
+        <v>810828</v>
       </c>
       <c r="R30" t="n">
-        <v>7171420</v>
+        <v>7171441</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3900,13 +3896,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645753</v>
+        <v>122645768</v>
       </c>
       <c r="B4" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,30 +925,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810433</v>
+        <v>810402</v>
       </c>
       <c r="R4" t="n">
-        <v>7171480</v>
+        <v>7171498</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,13 +995,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>påbörjat bohål?</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1019,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645804</v>
+        <v>122645753</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,31 +1040,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810405</v>
+        <v>810433</v>
       </c>
       <c r="R5" t="n">
-        <v>7171515</v>
+        <v>7171480</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,17 +1109,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122645747</v>
+        <v>122645713</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,31 +1150,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1182,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810444</v>
+        <v>810368</v>
       </c>
       <c r="R6" t="n">
-        <v>7171459</v>
+        <v>7171378</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,17 +1219,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>barksprätt på gammelgran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1249,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122645725</v>
+        <v>122645705</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810444</v>
+        <v>810319</v>
       </c>
       <c r="R7" t="n">
-        <v>7171408</v>
+        <v>7171499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122649837</v>
+        <v>122645747</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,30 +1370,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1406,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810545</v>
+        <v>810444</v>
       </c>
       <c r="R8" t="n">
-        <v>7171458</v>
+        <v>7171459</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,13 +1440,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>barksprätt på gammelgran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122650377</v>
+        <v>122645708</v>
       </c>
       <c r="B9" t="n">
-        <v>90905</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,31 +1481,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>810600</v>
+        <v>810319</v>
       </c>
       <c r="R9" t="n">
-        <v>7171604</v>
+        <v>7171477</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122649797</v>
+        <v>122649880</v>
       </c>
       <c r="B10" t="n">
-        <v>56680</v>
+        <v>57447</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,35 +1591,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>100136</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1627,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>810426</v>
+        <v>810599</v>
       </c>
       <c r="R10" t="n">
-        <v>7171539</v>
+        <v>7171453</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,12 +1653,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>satt i en gran längs vägen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122645698</v>
+        <v>122645789</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,31 +1706,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810288</v>
+        <v>810427</v>
       </c>
       <c r="R11" t="n">
-        <v>7171439</v>
+        <v>7171501</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,17 +1775,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>barksprätt på senvuxen gammelgran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1804,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122649804</v>
+        <v>122650377</v>
       </c>
       <c r="B12" t="n">
-        <v>78762</v>
+        <v>90909</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,31 +1812,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1851,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810465</v>
+        <v>810600</v>
       </c>
       <c r="R12" t="n">
-        <v>7171522</v>
+        <v>7171604</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122649813</v>
+        <v>122649804</v>
       </c>
       <c r="B13" t="n">
-        <v>78796</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,21 +1926,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1961,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810503</v>
+        <v>810465</v>
       </c>
       <c r="R13" t="n">
-        <v>7171478</v>
+        <v>7171522</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122649880</v>
+        <v>122645725</v>
       </c>
       <c r="B14" t="n">
-        <v>57447</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,31 +2032,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100136</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2068,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810599</v>
+        <v>810444</v>
       </c>
       <c r="R14" t="n">
-        <v>7171453</v>
+        <v>7171408</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2098,17 +2097,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>satt i en gran längs vägen</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,6 +2111,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2135,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122645789</v>
+        <v>122645881</v>
       </c>
       <c r="B15" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810427</v>
+        <v>810380</v>
       </c>
       <c r="R15" t="n">
-        <v>7171501</v>
+        <v>7171534</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2240,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122645768</v>
+        <v>122645698</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2293,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>810402</v>
+        <v>810288</v>
       </c>
       <c r="R16" t="n">
-        <v>7171498</v>
+        <v>7171439</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2333,7 +2328,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>påbörjat bohål?</t>
+          <t>barksprätt på senvuxen gammelgran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122645713</v>
+        <v>122649797</v>
       </c>
       <c r="B17" t="n">
-        <v>78762</v>
+        <v>56680</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,30 +2371,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2407,10 +2403,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>810368</v>
+        <v>810426</v>
       </c>
       <c r="R17" t="n">
-        <v>7171378</v>
+        <v>7171539</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2447,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2470,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122645708</v>
+        <v>122649837</v>
       </c>
       <c r="B18" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2517,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810319</v>
+        <v>810545</v>
       </c>
       <c r="R18" t="n">
-        <v>7171477</v>
+        <v>7171458</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2580,10 +2575,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122645881</v>
+        <v>122645893</v>
       </c>
       <c r="B19" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,30 +2591,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2627,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810380</v>
+        <v>810397</v>
       </c>
       <c r="R19" t="n">
-        <v>7171534</v>
+        <v>7171536</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2665,13 +2661,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>födosök på gran men kan vara från en annan hackspett</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122645893</v>
+        <v>122645804</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2706,16 +2706,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>810397</v>
+        <v>810405</v>
       </c>
       <c r="R20" t="n">
-        <v>7171536</v>
+        <v>7171515</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>födosök på gran men kan vara från en annan hackspett</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2805,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122645705</v>
+        <v>122649813</v>
       </c>
       <c r="B21" t="n">
-        <v>78762</v>
+        <v>78800</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2821,21 +2821,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810319</v>
+        <v>810503</v>
       </c>
       <c r="R21" t="n">
-        <v>7171499</v>
+        <v>7171478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3370,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122650264</v>
+        <v>122650066</v>
       </c>
       <c r="B26" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811045</v>
+        <v>810939</v>
       </c>
       <c r="R26" t="n">
-        <v>7171680</v>
+        <v>7171504</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3480,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122650066</v>
+        <v>122649988</v>
       </c>
       <c r="B27" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>810939</v>
       </c>
       <c r="R27" t="n">
-        <v>7171504</v>
+        <v>7171498</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3590,10 +3590,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122649921</v>
+        <v>122649934</v>
       </c>
       <c r="B28" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3606,30 +3606,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3637,10 +3638,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810786</v>
+        <v>810828</v>
       </c>
       <c r="R28" t="n">
-        <v>7171426</v>
+        <v>7171441</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,13 +3676,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3700,10 +3705,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122649892</v>
+        <v>122650270</v>
       </c>
       <c r="B29" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3747,10 +3752,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810633</v>
+        <v>811036</v>
       </c>
       <c r="R29" t="n">
-        <v>7171420</v>
+        <v>7171698</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3810,10 +3815,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122649934</v>
+        <v>122649921</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3826,31 +3831,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3858,10 +3862,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810828</v>
+        <v>810786</v>
       </c>
       <c r="R30" t="n">
-        <v>7171441</v>
+        <v>7171426</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3896,17 +3900,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>äldre ringhack i gran</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3925,10 +3925,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122650292</v>
+        <v>122650350</v>
       </c>
       <c r="B31" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3972,10 +3972,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810931</v>
+        <v>810833</v>
       </c>
       <c r="R31" t="n">
-        <v>7171669</v>
+        <v>7171605</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122650350</v>
+        <v>122650277</v>
       </c>
       <c r="B32" t="n">
-        <v>78762</v>
+        <v>57494</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4051,30 +4051,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4082,10 +4083,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810833</v>
+        <v>811014</v>
       </c>
       <c r="R32" t="n">
-        <v>7171605</v>
+        <v>7171734</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4120,13 +4121,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>hack i gran, både äldre och färska hack</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4145,10 +4150,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122649988</v>
+        <v>122650292</v>
       </c>
       <c r="B33" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4192,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810939</v>
+        <v>810931</v>
       </c>
       <c r="R33" t="n">
-        <v>7171498</v>
+        <v>7171669</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4369,7 +4374,7 @@
         <v>122650329</v>
       </c>
       <c r="B35" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4476,10 +4481,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122650277</v>
+        <v>122649892</v>
       </c>
       <c r="B36" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4492,31 +4497,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4524,10 +4528,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811014</v>
+        <v>810633</v>
       </c>
       <c r="R36" t="n">
-        <v>7171734</v>
+        <v>7171420</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4562,17 +4566,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>hack i gran, både äldre och färska hack</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4591,10 +4591,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122650270</v>
+        <v>122650264</v>
       </c>
       <c r="B37" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4638,10 +4638,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811036</v>
+        <v>811045</v>
       </c>
       <c r="R37" t="n">
-        <v>7171698</v>
+        <v>7171680</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645768</v>
+        <v>122645804</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810402</v>
+        <v>810405</v>
       </c>
       <c r="R4" t="n">
-        <v>7171498</v>
+        <v>7171515</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>påbörjat bohål?</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645753</v>
+        <v>122645705</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810433</v>
+        <v>810319</v>
       </c>
       <c r="R5" t="n">
-        <v>7171480</v>
+        <v>7171499</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122645713</v>
+        <v>122650377</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>90909</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,31 +1146,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810368</v>
+        <v>810600</v>
       </c>
       <c r="R6" t="n">
-        <v>7171378</v>
+        <v>7171604</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122645705</v>
+        <v>122645893</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,30 +1260,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1291,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810319</v>
+        <v>810397</v>
       </c>
       <c r="R7" t="n">
-        <v>7171499</v>
+        <v>7171536</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,13 +1330,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>födosök på gran men kan vara från en annan hackspett</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1354,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122645747</v>
+        <v>122649880</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57447</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,35 +1371,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1402,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810444</v>
+        <v>810599</v>
       </c>
       <c r="R8" t="n">
-        <v>7171459</v>
+        <v>7171453</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,17 +1433,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>barksprätt på gammelgran</t>
+          <t>satt i en gran längs vägen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1470,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122645708</v>
+        <v>122645881</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1516,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>810319</v>
+        <v>810380</v>
       </c>
       <c r="R9" t="n">
-        <v>7171477</v>
+        <v>7171534</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122649880</v>
+        <v>122649837</v>
       </c>
       <c r="B10" t="n">
-        <v>57447</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,31 +1592,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100136</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1623,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>810599</v>
+        <v>810545</v>
       </c>
       <c r="R10" t="n">
-        <v>7171453</v>
+        <v>7171458</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,17 +1657,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>satt i en gran längs vägen</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,6 +1671,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122645789</v>
+        <v>122645708</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810427</v>
+        <v>810319</v>
       </c>
       <c r="R11" t="n">
-        <v>7171501</v>
+        <v>7171477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122650377</v>
+        <v>122649804</v>
       </c>
       <c r="B12" t="n">
-        <v>90909</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,31 +1812,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810600</v>
+        <v>810465</v>
       </c>
       <c r="R12" t="n">
-        <v>7171604</v>
+        <v>7171522</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1910,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122649804</v>
+        <v>122645713</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810465</v>
+        <v>810368</v>
       </c>
       <c r="R13" t="n">
-        <v>7171522</v>
+        <v>7171378</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122645725</v>
+        <v>122645768</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,30 +2036,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2067,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810444</v>
+        <v>810402</v>
       </c>
       <c r="R14" t="n">
-        <v>7171408</v>
+        <v>7171498</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2105,13 +2106,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>påbörjat bohål?</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2130,7 +2135,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122645881</v>
+        <v>122645789</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2177,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810380</v>
+        <v>810427</v>
       </c>
       <c r="R15" t="n">
-        <v>7171534</v>
+        <v>7171501</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2355,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122649797</v>
+        <v>122645725</v>
       </c>
       <c r="B17" t="n">
-        <v>56680</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,31 +2376,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2403,10 +2407,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>810426</v>
+        <v>810444</v>
       </c>
       <c r="R17" t="n">
-        <v>7171539</v>
+        <v>7171408</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2447,6 +2451,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2465,10 +2470,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122649837</v>
+        <v>122645747</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2481,30 +2486,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2512,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810545</v>
+        <v>810444</v>
       </c>
       <c r="R18" t="n">
-        <v>7171458</v>
+        <v>7171459</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2550,13 +2556,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>barksprätt på gammelgran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2575,10 +2585,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122645893</v>
+        <v>122649797</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>56680</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,16 +2601,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2613,7 +2623,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2623,10 +2633,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810397</v>
+        <v>810426</v>
       </c>
       <c r="R19" t="n">
-        <v>7171536</v>
+        <v>7171539</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,11 +2669,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>födosök på gran men kan vara från en annan hackspett</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2690,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122645804</v>
+        <v>122649813</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>78800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2706,31 +2711,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2738,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>810405</v>
+        <v>810503</v>
       </c>
       <c r="R20" t="n">
-        <v>7171515</v>
+        <v>7171478</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,17 +2780,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2805,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122649813</v>
+        <v>122645753</v>
       </c>
       <c r="B21" t="n">
-        <v>78800</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2821,21 +2821,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810503</v>
+        <v>810433</v>
       </c>
       <c r="R21" t="n">
-        <v>7171478</v>
+        <v>7171480</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122650066</v>
+        <v>122649988</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3420,7 +3420,7 @@
         <v>810939</v>
       </c>
       <c r="R26" t="n">
-        <v>7171504</v>
+        <v>7171498</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3480,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122649988</v>
+        <v>122650277</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3496,30 +3496,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3527,10 +3528,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810939</v>
+        <v>811014</v>
       </c>
       <c r="R27" t="n">
-        <v>7171498</v>
+        <v>7171734</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3565,13 +3566,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>hack i gran, både äldre och färska hack</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3590,10 +3595,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122649934</v>
+        <v>122650329</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3606,31 +3611,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3638,10 +3642,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810828</v>
+        <v>810886</v>
       </c>
       <c r="R28" t="n">
-        <v>7171441</v>
+        <v>7171642</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3676,17 +3680,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack i gran</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122650270</v>
+        <v>122649892</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811036</v>
+        <v>810633</v>
       </c>
       <c r="R29" t="n">
-        <v>7171698</v>
+        <v>7171420</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3925,7 +3925,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122650350</v>
+        <v>122650066</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -3972,10 +3972,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810833</v>
+        <v>810939</v>
       </c>
       <c r="R31" t="n">
-        <v>7171605</v>
+        <v>7171504</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122650277</v>
+        <v>122650270</v>
       </c>
       <c r="B32" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4051,31 +4051,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4083,10 +4082,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811014</v>
+        <v>811036</v>
       </c>
       <c r="R32" t="n">
-        <v>7171734</v>
+        <v>7171698</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4121,17 +4120,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>hack i gran, både äldre och färska hack</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4260,10 +4255,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122650339</v>
+        <v>122650264</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4276,27 +4271,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4304,10 +4302,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>810833</v>
+        <v>811045</v>
       </c>
       <c r="R34" t="n">
-        <v>7171605</v>
+        <v>7171680</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4342,17 +4340,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4371,7 +4365,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122650329</v>
+        <v>122650350</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4418,10 +4412,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810886</v>
+        <v>810833</v>
       </c>
       <c r="R35" t="n">
-        <v>7171642</v>
+        <v>7171605</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4481,10 +4475,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122649892</v>
+        <v>122649934</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4497,30 +4491,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4528,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>810633</v>
+        <v>810828</v>
       </c>
       <c r="R36" t="n">
-        <v>7171420</v>
+        <v>7171441</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4566,13 +4561,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4591,10 +4590,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122650264</v>
+        <v>122650339</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4607,30 +4606,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4638,10 +4634,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811045</v>
+        <v>810833</v>
       </c>
       <c r="R37" t="n">
-        <v>7171680</v>
+        <v>7171605</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4676,13 +4672,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal senvuxen gran</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645804</v>
+        <v>122649797</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>56680</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,7 +947,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810405</v>
+        <v>810426</v>
       </c>
       <c r="R4" t="n">
-        <v>7171515</v>
+        <v>7171539</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,11 +993,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645705</v>
+        <v>122650377</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>90909</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,31 +1031,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1071,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810319</v>
+        <v>810600</v>
       </c>
       <c r="R5" t="n">
-        <v>7171499</v>
+        <v>7171604</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122650377</v>
+        <v>122645768</v>
       </c>
       <c r="B6" t="n">
-        <v>90909</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,34 +1141,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1181,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810600</v>
+        <v>810402</v>
       </c>
       <c r="R6" t="n">
-        <v>7171604</v>
+        <v>7171498</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,13 +1215,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>påbörjat bohål?</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122645893</v>
+        <v>122645705</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,31 +1260,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1292,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810397</v>
+        <v>810319</v>
       </c>
       <c r="R7" t="n">
-        <v>7171536</v>
+        <v>7171499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,17 +1329,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>födosök på gran men kan vara från en annan hackspett</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1359,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122649880</v>
+        <v>122645804</v>
       </c>
       <c r="B8" t="n">
-        <v>57447</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,31 +1366,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100136</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1403,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810599</v>
+        <v>810405</v>
       </c>
       <c r="R8" t="n">
-        <v>7171453</v>
+        <v>7171515</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,17 +1432,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>satt i en gran längs vägen</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122645881</v>
+        <v>122649880</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57447</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,34 +1481,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100136</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1517,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>810380</v>
+        <v>810599</v>
       </c>
       <c r="R9" t="n">
-        <v>7171534</v>
+        <v>7171453</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,12 +1543,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>satt i en gran längs vägen</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,7 +1562,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122649837</v>
+        <v>122645713</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>810545</v>
+        <v>810368</v>
       </c>
       <c r="R10" t="n">
-        <v>7171458</v>
+        <v>7171378</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122645708</v>
+        <v>122645747</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,30 +1706,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1737,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810319</v>
+        <v>810444</v>
       </c>
       <c r="R11" t="n">
-        <v>7171477</v>
+        <v>7171459</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,13 +1776,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>barksprätt på gammelgran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1800,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122649804</v>
+        <v>122645893</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,30 +1821,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1847,10 +1853,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810465</v>
+        <v>810397</v>
       </c>
       <c r="R12" t="n">
-        <v>7171522</v>
+        <v>7171536</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,13 +1891,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>födosök på gran men kan vara från en annan hackspett</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1910,7 +1920,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122645713</v>
+        <v>122645753</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1957,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810368</v>
+        <v>810433</v>
       </c>
       <c r="R13" t="n">
-        <v>7171378</v>
+        <v>7171480</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,10 +2030,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122645768</v>
+        <v>122649837</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,31 +2046,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2068,10 +2077,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810402</v>
+        <v>810545</v>
       </c>
       <c r="R14" t="n">
-        <v>7171498</v>
+        <v>7171458</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,17 +2115,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>påbörjat bohål?</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2245,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122645698</v>
+        <v>122645708</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,31 +2266,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2293,10 +2297,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>810288</v>
+        <v>810319</v>
       </c>
       <c r="R16" t="n">
-        <v>7171439</v>
+        <v>7171477</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,17 +2335,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>barksprätt på senvuxen gammelgran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2470,10 +2470,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122645747</v>
+        <v>122645881</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2486,31 +2486,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2518,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810444</v>
+        <v>810380</v>
       </c>
       <c r="R18" t="n">
-        <v>7171459</v>
+        <v>7171534</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,17 +2555,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>barksprätt på gammelgran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2585,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122649797</v>
+        <v>122649804</v>
       </c>
       <c r="B19" t="n">
-        <v>56680</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,31 +2596,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2633,10 +2627,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810426</v>
+        <v>810465</v>
       </c>
       <c r="R19" t="n">
-        <v>7171539</v>
+        <v>7171522</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2677,6 +2671,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2805,10 +2800,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122645753</v>
+        <v>122645698</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2821,30 +2816,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2852,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810433</v>
+        <v>810288</v>
       </c>
       <c r="R21" t="n">
-        <v>7171480</v>
+        <v>7171439</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2890,13 +2886,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>barksprätt på senvuxen gammelgran</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3370,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122649988</v>
+        <v>122649934</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3386,30 +3386,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3417,10 +3418,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810939</v>
+        <v>810828</v>
       </c>
       <c r="R26" t="n">
-        <v>7171498</v>
+        <v>7171441</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,13 +3456,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3595,7 +3600,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122650329</v>
+        <v>122649892</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -3642,10 +3647,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810886</v>
+        <v>810633</v>
       </c>
       <c r="R28" t="n">
-        <v>7171642</v>
+        <v>7171420</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3705,7 +3710,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122649892</v>
+        <v>122649988</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3752,10 +3757,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810633</v>
+        <v>810939</v>
       </c>
       <c r="R29" t="n">
-        <v>7171420</v>
+        <v>7171498</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3815,7 +3820,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122649921</v>
+        <v>122650329</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3862,10 +3867,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810786</v>
+        <v>810886</v>
       </c>
       <c r="R30" t="n">
-        <v>7171426</v>
+        <v>7171642</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3925,7 +3930,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122650066</v>
+        <v>122650270</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -3972,10 +3977,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810939</v>
+        <v>811036</v>
       </c>
       <c r="R31" t="n">
-        <v>7171504</v>
+        <v>7171698</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4035,10 +4040,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122650270</v>
+        <v>122650339</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4051,30 +4056,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4082,10 +4084,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811036</v>
+        <v>810833</v>
       </c>
       <c r="R32" t="n">
-        <v>7171698</v>
+        <v>7171605</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4120,13 +4122,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal senvuxen gran</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4145,7 +4151,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122650292</v>
+        <v>122650350</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -4192,10 +4198,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810931</v>
+        <v>810833</v>
       </c>
       <c r="R33" t="n">
-        <v>7171669</v>
+        <v>7171605</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4365,7 +4371,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122650350</v>
+        <v>122650066</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4412,10 +4418,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810833</v>
+        <v>810939</v>
       </c>
       <c r="R35" t="n">
-        <v>7171605</v>
+        <v>7171504</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4475,10 +4481,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122649934</v>
+        <v>122650292</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4491,31 +4497,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4523,10 +4528,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>810828</v>
+        <v>810931</v>
       </c>
       <c r="R36" t="n">
-        <v>7171441</v>
+        <v>7171669</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4561,17 +4566,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>äldre ringhack i gran</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4590,10 +4591,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122650339</v>
+        <v>122649921</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4606,27 +4607,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4634,10 +4638,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810833</v>
+        <v>810786</v>
       </c>
       <c r="R37" t="n">
-        <v>7171605</v>
+        <v>7171426</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4672,17 +4676,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122645705</v>
+        <v>122645804</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,30 +1260,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1291,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810319</v>
+        <v>810405</v>
       </c>
       <c r="R7" t="n">
-        <v>7171499</v>
+        <v>7171515</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,13 +1330,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1354,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122645804</v>
+        <v>122645705</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,31 +1375,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1402,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810405</v>
+        <v>810319</v>
       </c>
       <c r="R8" t="n">
-        <v>7171515</v>
+        <v>7171499</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,17 +1444,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -3370,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122649934</v>
+        <v>122650277</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3386,16 +3386,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3408,7 +3408,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3418,10 +3418,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810828</v>
+        <v>811014</v>
       </c>
       <c r="R26" t="n">
-        <v>7171441</v>
+        <v>7171734</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>äldre ringhack i gran</t>
+          <t>hack i gran, både äldre och färska hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,10 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122650277</v>
+        <v>122649934</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,16 +3501,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3523,7 +3523,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811014</v>
+        <v>810828</v>
       </c>
       <c r="R27" t="n">
-        <v>7171734</v>
+        <v>7171441</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>hack i gran, både äldre och färska hack</t>
+          <t>äldre ringhack i gran</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122645804</v>
+        <v>122645705</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,31 +1260,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1292,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810405</v>
+        <v>810319</v>
       </c>
       <c r="R7" t="n">
-        <v>7171515</v>
+        <v>7171499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,17 +1329,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1359,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122645705</v>
+        <v>122645804</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,30 +1370,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1406,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810319</v>
+        <v>810405</v>
       </c>
       <c r="R8" t="n">
-        <v>7171499</v>
+        <v>7171515</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,13 +1440,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -3370,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122650277</v>
+        <v>122649934</v>
       </c>
       <c r="B26" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3386,16 +3386,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3408,7 +3408,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3418,10 +3418,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811014</v>
+        <v>810828</v>
       </c>
       <c r="R26" t="n">
-        <v>7171734</v>
+        <v>7171441</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>hack i gran, både äldre och färska hack</t>
+          <t>äldre ringhack i gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,10 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122649934</v>
+        <v>122650277</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,16 +3501,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3523,7 +3523,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810828</v>
+        <v>811014</v>
       </c>
       <c r="R27" t="n">
-        <v>7171441</v>
+        <v>7171734</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>äldre ringhack i gran</t>
+          <t>hack i gran, både äldre och färska hack</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122649797</v>
+        <v>122645893</v>
       </c>
       <c r="B4" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,7 +947,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810426</v>
+        <v>810397</v>
       </c>
       <c r="R4" t="n">
-        <v>7171539</v>
+        <v>7171536</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,6 +993,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>födosök på gran men kan vara från en annan hackspett</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122650377</v>
+        <v>122645705</v>
       </c>
       <c r="B5" t="n">
-        <v>90909</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,31 +1036,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1066,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810600</v>
+        <v>810319</v>
       </c>
       <c r="R5" t="n">
-        <v>7171604</v>
+        <v>7171499</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122645768</v>
+        <v>122645753</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,31 +1150,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1177,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810402</v>
+        <v>810433</v>
       </c>
       <c r="R6" t="n">
-        <v>7171498</v>
+        <v>7171480</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,17 +1219,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>påbörjat bohål?</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1244,7 +1244,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122645705</v>
+        <v>122649837</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810319</v>
+        <v>810545</v>
       </c>
       <c r="R7" t="n">
-        <v>7171499</v>
+        <v>7171458</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122645804</v>
+        <v>122650377</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>90909</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,35 +1366,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1402,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810405</v>
+        <v>810600</v>
       </c>
       <c r="R8" t="n">
-        <v>7171515</v>
+        <v>7171604</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,17 +1439,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1469,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122649880</v>
+        <v>122645708</v>
       </c>
       <c r="B9" t="n">
-        <v>57447</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,31 +1476,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100136</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1513,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>810599</v>
+        <v>810319</v>
       </c>
       <c r="R9" t="n">
-        <v>7171453</v>
+        <v>7171477</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,17 +1541,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>satt i en gran längs vägen</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,6 +1555,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1580,7 +1574,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122645713</v>
+        <v>122645881</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1627,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>810368</v>
+        <v>810380</v>
       </c>
       <c r="R10" t="n">
-        <v>7171378</v>
+        <v>7171534</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,7 +1684,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122645747</v>
+        <v>122645768</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1738,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810444</v>
+        <v>810402</v>
       </c>
       <c r="R11" t="n">
-        <v>7171459</v>
+        <v>7171498</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,7 +1772,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>barksprätt på gammelgran</t>
+          <t>påbörjat bohål?</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122645893</v>
+        <v>122649880</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57447</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,35 +1811,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1853,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810397</v>
+        <v>810599</v>
       </c>
       <c r="R12" t="n">
-        <v>7171536</v>
+        <v>7171453</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,17 +1873,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>födosök på gran men kan vara från en annan hackspett</t>
+          <t>satt i en gran längs vägen</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122645753</v>
+        <v>122649813</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>78800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,21 +1926,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1967,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810433</v>
+        <v>810503</v>
       </c>
       <c r="R13" t="n">
-        <v>7171480</v>
+        <v>7171478</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122649837</v>
+        <v>122649804</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2077,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810545</v>
+        <v>810465</v>
       </c>
       <c r="R14" t="n">
-        <v>7171458</v>
+        <v>7171522</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122645789</v>
+        <v>122645804</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2156,30 +2146,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2187,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810427</v>
+        <v>810405</v>
       </c>
       <c r="R15" t="n">
-        <v>7171501</v>
+        <v>7171515</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2225,13 +2216,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2250,7 +2245,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122645708</v>
+        <v>122645725</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2297,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>810319</v>
+        <v>810444</v>
       </c>
       <c r="R16" t="n">
-        <v>7171477</v>
+        <v>7171408</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,7 +2355,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122645725</v>
+        <v>122645713</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2407,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>810444</v>
+        <v>810368</v>
       </c>
       <c r="R17" t="n">
-        <v>7171408</v>
+        <v>7171378</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2470,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122645881</v>
+        <v>122645698</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2486,30 +2481,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2517,10 +2513,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810380</v>
+        <v>810288</v>
       </c>
       <c r="R18" t="n">
-        <v>7171534</v>
+        <v>7171439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2555,13 +2551,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>barksprätt på senvuxen gammelgran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2580,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122649804</v>
+        <v>122645747</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,30 +2596,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2627,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810465</v>
+        <v>810444</v>
       </c>
       <c r="R19" t="n">
-        <v>7171522</v>
+        <v>7171459</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2665,13 +2666,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>barksprätt på gammelgran</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2690,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122649813</v>
+        <v>122649797</v>
       </c>
       <c r="B20" t="n">
-        <v>78800</v>
+        <v>56680</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2706,30 +2711,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2737,10 +2743,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>810503</v>
+        <v>810426</v>
       </c>
       <c r="R20" t="n">
-        <v>7171478</v>
+        <v>7171539</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,7 +2787,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2800,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122645698</v>
+        <v>122645789</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2816,31 +2821,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2848,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810288</v>
+        <v>810427</v>
       </c>
       <c r="R21" t="n">
-        <v>7171439</v>
+        <v>7171501</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2886,17 +2890,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>barksprätt på senvuxen gammelgran</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3370,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122649934</v>
+        <v>122649988</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3386,31 +3386,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3418,10 +3417,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810828</v>
+        <v>810939</v>
       </c>
       <c r="R26" t="n">
-        <v>7171441</v>
+        <v>7171498</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3456,17 +3455,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>äldre ringhack i gran</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3485,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122650277</v>
+        <v>122650066</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,31 +3496,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3533,10 +3527,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811014</v>
+        <v>810939</v>
       </c>
       <c r="R27" t="n">
-        <v>7171734</v>
+        <v>7171504</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3571,17 +3565,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>hack i gran, både äldre och färska hack</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3590,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122649892</v>
+        <v>122649934</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3616,30 +3606,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3647,10 +3638,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810633</v>
+        <v>810828</v>
       </c>
       <c r="R28" t="n">
-        <v>7171420</v>
+        <v>7171441</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3685,13 +3676,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3710,10 +3705,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122649988</v>
+        <v>122650277</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3726,30 +3721,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3757,10 +3753,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810939</v>
+        <v>811014</v>
       </c>
       <c r="R29" t="n">
-        <v>7171498</v>
+        <v>7171734</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3795,13 +3791,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>hack i gran, både äldre och färska hack</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122650270</v>
+        <v>122650264</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811036</v>
+        <v>811045</v>
       </c>
       <c r="R31" t="n">
-        <v>7171698</v>
+        <v>7171680</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4040,10 +4040,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122650339</v>
+        <v>122650350</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4056,27 +4056,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4122,17 +4125,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4151,10 +4150,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122650350</v>
+        <v>122650339</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4167,30 +4166,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4236,13 +4232,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal senvuxen gran</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4261,7 +4261,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122650264</v>
+        <v>122649921</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811045</v>
+        <v>810786</v>
       </c>
       <c r="R34" t="n">
-        <v>7171680</v>
+        <v>7171426</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4371,7 +4371,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122650066</v>
+        <v>122650292</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810939</v>
+        <v>810931</v>
       </c>
       <c r="R35" t="n">
-        <v>7171504</v>
+        <v>7171669</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4481,7 +4481,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122650292</v>
+        <v>122650270</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>810931</v>
+        <v>811036</v>
       </c>
       <c r="R36" t="n">
-        <v>7171669</v>
+        <v>7171698</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4591,7 +4591,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122649921</v>
+        <v>122649892</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4638,10 +4638,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810786</v>
+        <v>810633</v>
       </c>
       <c r="R37" t="n">
-        <v>7171426</v>
+        <v>7171420</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645705</v>
+        <v>122645753</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810319</v>
+        <v>810433</v>
       </c>
       <c r="R5" t="n">
-        <v>7171499</v>
+        <v>7171480</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,7 +1134,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122645753</v>
+        <v>122645705</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810433</v>
+        <v>810319</v>
       </c>
       <c r="R6" t="n">
-        <v>7171480</v>
+        <v>7171499</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122649837</v>
+        <v>122650377</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>90909</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,31 +1256,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810545</v>
+        <v>810600</v>
       </c>
       <c r="R7" t="n">
-        <v>7171458</v>
+        <v>7171604</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122650377</v>
+        <v>122649837</v>
       </c>
       <c r="B8" t="n">
-        <v>90909</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,31 +1366,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810600</v>
+        <v>810545</v>
       </c>
       <c r="R8" t="n">
-        <v>7171604</v>
+        <v>7171458</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2465,7 +2465,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122645698</v>
+        <v>122645747</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810288</v>
+        <v>810444</v>
       </c>
       <c r="R18" t="n">
-        <v>7171439</v>
+        <v>7171459</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>barksprätt på senvuxen gammelgran</t>
+          <t>barksprätt på gammelgran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2580,7 +2580,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122645747</v>
+        <v>122645698</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810444</v>
+        <v>810288</v>
       </c>
       <c r="R19" t="n">
-        <v>7171459</v>
+        <v>7171439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>barksprätt på gammelgran</t>
+          <t>barksprätt på senvuxen gammelgran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3480,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122650066</v>
+        <v>122649934</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3496,30 +3496,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3527,10 +3528,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810939</v>
+        <v>810828</v>
       </c>
       <c r="R27" t="n">
-        <v>7171504</v>
+        <v>7171441</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3565,13 +3566,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3590,10 +3595,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122649934</v>
+        <v>122650066</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3606,31 +3611,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3638,10 +3642,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810828</v>
+        <v>810939</v>
       </c>
       <c r="R28" t="n">
-        <v>7171441</v>
+        <v>7171504</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3676,17 +3680,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack i gran</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645753</v>
+        <v>122645705</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810433</v>
+        <v>810319</v>
       </c>
       <c r="R5" t="n">
-        <v>7171480</v>
+        <v>7171499</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,7 +1134,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122645705</v>
+        <v>122645753</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810319</v>
+        <v>810433</v>
       </c>
       <c r="R6" t="n">
-        <v>7171499</v>
+        <v>7171480</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>391091</v>
+        <v>123104604</v>
       </c>
       <c r="B22" t="n">
-        <v>81235</v>
+        <v>57494</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,37 +2931,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>810860.7270867341</v>
+        <v>810442</v>
       </c>
       <c r="R22" t="n">
-        <v>7171669.623737417</v>
+        <v>7171450</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2985,22 +2993,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2055139</v>
+        <v>123104657</v>
       </c>
       <c r="B23" t="n">
-        <v>78097</v>
+        <v>57494</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,37 +3046,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>810860.7270867341</v>
+        <v>810447</v>
       </c>
       <c r="R23" t="n">
-        <v>7171669.623737417</v>
+        <v>7171526</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3097,22 +3108,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3124,7 +3130,6 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AR23" t="inlineStr"/>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
@@ -3140,10 +3145,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>292476</v>
+        <v>123104581</v>
       </c>
       <c r="B24" t="n">
-        <v>79432</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3156,37 +3161,45 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tallskog Storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>810917.5546458759</v>
+        <v>810444</v>
       </c>
       <c r="R24" t="n">
-        <v>7171682.39060352</v>
+        <v>7171466</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3210,27 +3223,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2007-10-31</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>rapport från Patrik Nygren, SNF</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3245,22 +3248,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Via Jonas F Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>292265</v>
+        <v>391091</v>
       </c>
       <c r="B25" t="n">
-        <v>79432</v>
+        <v>81235</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3273,21 +3276,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3327,7 +3330,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3354,7 +3357,6 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AR25" t="inlineStr"/>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
@@ -3370,10 +3372,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122649988</v>
+        <v>2055139</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>78097</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3386,44 +3388,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storön, Vb</t>
+          <t>storön, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810939</v>
+        <v>810860.7270867341</v>
       </c>
       <c r="R26" t="n">
-        <v>7171498</v>
+        <v>7171669.623737417</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3447,12 +3442,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-12-31</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,10 +3466,10 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AR26" t="inlineStr"/>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
@@ -3480,10 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122649934</v>
+        <v>292476</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>79432</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3496,45 +3501,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Storön, Vb</t>
+          <t>Tallskog Storön, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810828</v>
+        <v>810917.5546458759</v>
       </c>
       <c r="R27" t="n">
-        <v>7171441</v>
+        <v>7171682.39060352</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3558,17 +3555,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-06-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-10-31</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>äldre ringhack i gran</t>
+          <t>rapport från Patrik Nygren, SNF</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3583,22 +3590,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Via Jonas F Grahn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122650066</v>
+        <v>292265</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>79432</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3611,44 +3618,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Storön, Vb</t>
+          <t>storön, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810939</v>
+        <v>810860.7270867341</v>
       </c>
       <c r="R28" t="n">
-        <v>7171504</v>
+        <v>7171669.623737417</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3672,12 +3672,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-12-31</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3686,10 +3696,10 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AR28" t="inlineStr"/>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
@@ -3705,10 +3715,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122650277</v>
+        <v>122649988</v>
       </c>
       <c r="B29" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3721,31 +3731,30 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3753,10 +3762,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811014</v>
+        <v>810939</v>
       </c>
       <c r="R29" t="n">
-        <v>7171734</v>
+        <v>7171498</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3791,17 +3800,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>hack i gran, både äldre och färska hack</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3820,7 +3825,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122650329</v>
+        <v>122650066</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3867,10 +3872,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810886</v>
+        <v>810939</v>
       </c>
       <c r="R30" t="n">
-        <v>7171642</v>
+        <v>7171504</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3930,10 +3935,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122650264</v>
+        <v>122649934</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3946,30 +3951,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3977,10 +3983,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811045</v>
+        <v>810828</v>
       </c>
       <c r="R31" t="n">
-        <v>7171680</v>
+        <v>7171441</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4015,13 +4021,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4040,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122650350</v>
+        <v>122650277</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4056,30 +4066,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4087,10 +4098,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810833</v>
+        <v>811014</v>
       </c>
       <c r="R32" t="n">
-        <v>7171605</v>
+        <v>7171734</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4125,13 +4136,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>hack i gran, både äldre och färska hack</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4150,10 +4165,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122650339</v>
+        <v>122650329</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4166,27 +4181,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4194,10 +4212,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810833</v>
+        <v>810886</v>
       </c>
       <c r="R33" t="n">
-        <v>7171605</v>
+        <v>7171642</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,17 +4250,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4261,7 +4275,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122649921</v>
+        <v>122650264</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4308,10 +4322,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>810786</v>
+        <v>811045</v>
       </c>
       <c r="R34" t="n">
-        <v>7171426</v>
+        <v>7171680</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4371,7 +4385,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122650292</v>
+        <v>122650350</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4418,10 +4432,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810931</v>
+        <v>810833</v>
       </c>
       <c r="R35" t="n">
-        <v>7171669</v>
+        <v>7171605</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4481,10 +4495,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122650270</v>
+        <v>122650339</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4497,30 +4511,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4528,10 +4539,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811036</v>
+        <v>810833</v>
       </c>
       <c r="R36" t="n">
-        <v>7171698</v>
+        <v>7171605</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4566,13 +4577,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal senvuxen gran</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4591,7 +4606,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122649892</v>
+        <v>122649921</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4638,10 +4653,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810633</v>
+        <v>810786</v>
       </c>
       <c r="R37" t="n">
-        <v>7171420</v>
+        <v>7171426</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4698,6 +4713,2820 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122650292</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>810931</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7171669</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122650270</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>811036</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7171698</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122649892</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>810633</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7171420</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123107511</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78792</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>811066</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7171715</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>123107409</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>811024</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7171733</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>123113174</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>810865</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7171668</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>hänglavrikt bla garnlav</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123105488</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>810824</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7171598</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>över 0,5 meter lång bål</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>123113317</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>810707</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7171592</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>hål i gammal sälg</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123107500</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>811043</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7171704</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123113205</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78800</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>185</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>810862</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7171664</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123105448</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>810833</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7171608</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>rikligt med fertil garnlav på gammal död gran</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>123107351</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>811003</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7171721</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>fertil garnlav</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>123107580</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>810886</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7171705</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>123105526</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>810798</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7171573</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>123113295</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>810851</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7171663</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>123105541</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78792</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>810786</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7171568</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>123107589</v>
+      </c>
+      <c r="B54" t="n">
+        <v>82553</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>810886</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7171705</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>123107459</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>811055</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7171672</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>123107487</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>811052</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7171679</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>rikligt med hänglavar bla garnlav</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>123107426</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>811024</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7171733</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>123113132</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>810895</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7171694</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>123107271</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>810992</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7171739</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>123113230</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>810850</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7171671</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>123107525</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78792</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>811018</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7171753</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>123107538</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78792</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>810978</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7171744</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645893</v>
+        <v>122645713</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,31 +925,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810397</v>
+        <v>810368</v>
       </c>
       <c r="R4" t="n">
-        <v>7171536</v>
+        <v>7171378</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,17 +994,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>födosök på gran men kan vara från en annan hackspett</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1024,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645705</v>
+        <v>122649880</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57447</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,34 +1031,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100136</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810319</v>
+        <v>810599</v>
       </c>
       <c r="R5" t="n">
-        <v>7171499</v>
+        <v>7171453</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,12 +1093,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>satt i en gran längs vägen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1112,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122645753</v>
+        <v>122645804</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,30 +1146,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1181,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810433</v>
+        <v>810405</v>
       </c>
       <c r="R6" t="n">
-        <v>7171480</v>
+        <v>7171515</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,13 +1216,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1244,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122650377</v>
+        <v>122645698</v>
       </c>
       <c r="B7" t="n">
-        <v>90909</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1257,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1291,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810600</v>
+        <v>810288</v>
       </c>
       <c r="R7" t="n">
-        <v>7171604</v>
+        <v>7171439</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,13 +1331,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>barksprätt på senvuxen gammelgran</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1354,7 +1360,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122649837</v>
+        <v>122645708</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1401,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810545</v>
+        <v>810319</v>
       </c>
       <c r="R8" t="n">
-        <v>7171458</v>
+        <v>7171477</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,7 +1470,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122645708</v>
+        <v>122649804</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1511,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>810319</v>
+        <v>810465</v>
       </c>
       <c r="R9" t="n">
-        <v>7171477</v>
+        <v>7171522</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1580,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122645881</v>
+        <v>122645725</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1621,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>810380</v>
+        <v>810444</v>
       </c>
       <c r="R10" t="n">
-        <v>7171534</v>
+        <v>7171408</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122645768</v>
+        <v>122645789</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,31 +1706,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1732,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810402</v>
+        <v>810427</v>
       </c>
       <c r="R11" t="n">
-        <v>7171498</v>
+        <v>7171501</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,17 +1775,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>påbörjat bohål?</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1799,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122649880</v>
+        <v>122645705</v>
       </c>
       <c r="B12" t="n">
-        <v>57447</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,31 +1812,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100136</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1843,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810599</v>
+        <v>810319</v>
       </c>
       <c r="R12" t="n">
-        <v>7171453</v>
+        <v>7171499</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,17 +1877,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>satt i en gran längs vägen</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,6 +1891,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122649813</v>
+        <v>122650377</v>
       </c>
       <c r="B13" t="n">
-        <v>78800</v>
+        <v>90917</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,31 +1922,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810503</v>
+        <v>810600</v>
       </c>
       <c r="R13" t="n">
-        <v>7171478</v>
+        <v>7171604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122649804</v>
+        <v>122649797</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>56680</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,30 +2036,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2067,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810465</v>
+        <v>810426</v>
       </c>
       <c r="R14" t="n">
-        <v>7171522</v>
+        <v>7171539</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2112,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122645804</v>
+        <v>122645881</v>
       </c>
       <c r="B15" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2146,31 +2146,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2178,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810405</v>
+        <v>810380</v>
       </c>
       <c r="R15" t="n">
-        <v>7171515</v>
+        <v>7171534</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,17 +2215,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2245,7 +2240,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122645725</v>
+        <v>122649837</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2292,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>810444</v>
+        <v>810545</v>
       </c>
       <c r="R16" t="n">
-        <v>7171408</v>
+        <v>7171458</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,7 +2350,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122645713</v>
+        <v>122645753</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2402,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>810368</v>
+        <v>810433</v>
       </c>
       <c r="R17" t="n">
-        <v>7171378</v>
+        <v>7171480</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2580,7 +2575,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122645698</v>
+        <v>122645893</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2628,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810288</v>
+        <v>810397</v>
       </c>
       <c r="R19" t="n">
-        <v>7171439</v>
+        <v>7171536</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2668,7 +2663,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>barksprätt på senvuxen gammelgran</t>
+          <t>födosök på gran men kan vara från en annan hackspett</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,10 +2690,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122649797</v>
+        <v>122649813</v>
       </c>
       <c r="B20" t="n">
-        <v>56680</v>
+        <v>78800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,31 +2706,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2743,10 +2737,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>810426</v>
+        <v>810503</v>
       </c>
       <c r="R20" t="n">
-        <v>7171539</v>
+        <v>7171478</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2787,6 +2781,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2805,10 +2800,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122645789</v>
+        <v>122645768</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2821,30 +2816,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2852,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810427</v>
+        <v>810402</v>
       </c>
       <c r="R21" t="n">
-        <v>7171501</v>
+        <v>7171498</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2890,13 +2886,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>påbörjat bohål?</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123104604</v>
+        <v>123104581</v>
       </c>
       <c r="B22" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,16 +2931,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>810442</v>
+        <v>810444</v>
       </c>
       <c r="R22" t="n">
-        <v>7171450</v>
+        <v>7171466</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3145,10 +3145,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123104581</v>
+        <v>123104604</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,16 +3161,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>810444</v>
+        <v>810442</v>
       </c>
       <c r="R24" t="n">
-        <v>7171466</v>
+        <v>7171450</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3715,10 +3715,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122649988</v>
+        <v>122650339</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3731,30 +3731,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3762,10 +3759,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810939</v>
+        <v>810833</v>
       </c>
       <c r="R29" t="n">
-        <v>7171498</v>
+        <v>7171605</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3800,13 +3797,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal senvuxen gran</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3825,7 +3826,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122650066</v>
+        <v>122649988</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3875,7 +3876,7 @@
         <v>810939</v>
       </c>
       <c r="R30" t="n">
-        <v>7171504</v>
+        <v>7171498</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3935,10 +3936,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122649934</v>
+        <v>122650350</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3951,31 +3952,30 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810828</v>
+        <v>810833</v>
       </c>
       <c r="R31" t="n">
-        <v>7171441</v>
+        <v>7171605</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4021,17 +4021,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>äldre ringhack i gran</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4050,10 +4046,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122650277</v>
+        <v>122650066</v>
       </c>
       <c r="B32" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4066,31 +4062,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4098,10 +4093,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811014</v>
+        <v>810939</v>
       </c>
       <c r="R32" t="n">
-        <v>7171734</v>
+        <v>7171504</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4136,17 +4131,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>hack i gran, både äldre och färska hack</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4165,7 +4156,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122650329</v>
+        <v>122650292</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -4212,10 +4203,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810886</v>
+        <v>810931</v>
       </c>
       <c r="R33" t="n">
-        <v>7171642</v>
+        <v>7171669</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4275,10 +4266,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122650264</v>
+        <v>122650277</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4291,30 +4282,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4322,10 +4314,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811045</v>
+        <v>811014</v>
       </c>
       <c r="R34" t="n">
-        <v>7171680</v>
+        <v>7171734</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4360,13 +4352,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>hack i gran, både äldre och färska hack</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4385,10 +4381,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122650350</v>
+        <v>122649934</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4401,30 +4397,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4432,10 +4429,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810833</v>
+        <v>810828</v>
       </c>
       <c r="R35" t="n">
-        <v>7171605</v>
+        <v>7171441</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4470,13 +4467,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4495,10 +4496,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122650339</v>
+        <v>122649892</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4511,27 +4512,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4539,10 +4543,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>810833</v>
+        <v>810633</v>
       </c>
       <c r="R36" t="n">
-        <v>7171605</v>
+        <v>7171420</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4577,17 +4581,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4606,7 +4606,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122649921</v>
+        <v>122650264</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810786</v>
+        <v>811045</v>
       </c>
       <c r="R37" t="n">
-        <v>7171426</v>
+        <v>7171680</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4716,7 +4716,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122650292</v>
+        <v>122649921</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4763,10 +4763,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>810931</v>
+        <v>810786</v>
       </c>
       <c r="R38" t="n">
-        <v>7171669</v>
+        <v>7171426</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4936,7 +4936,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122649892</v>
+        <v>122650329</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>810633</v>
+        <v>810886</v>
       </c>
       <c r="R40" t="n">
-        <v>7171420</v>
+        <v>7171642</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5046,7 +5046,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123107511</v>
+        <v>123105541</v>
       </c>
       <c r="B41" t="n">
         <v>78792</v>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811066</v>
+        <v>810786</v>
       </c>
       <c r="R41" t="n">
-        <v>7171715</v>
+        <v>7171568</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5156,10 +5156,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123107409</v>
+        <v>123107589</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5172,31 +5172,30 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5204,10 +5203,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811024</v>
+        <v>810886</v>
       </c>
       <c r="R42" t="n">
-        <v>7171733</v>
+        <v>7171705</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5242,17 +5241,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5271,10 +5266,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123113174</v>
+        <v>123113295</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5287,30 +5282,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5318,10 +5314,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810865</v>
+        <v>810851</v>
       </c>
       <c r="R43" t="n">
-        <v>7171668</v>
+        <v>7171663</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5358,7 +5354,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>hänglavrikt bla garnlav</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5367,7 +5363,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5386,10 +5381,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123105488</v>
+        <v>123107409</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5402,30 +5397,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5433,10 +5429,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>810824</v>
+        <v>811024</v>
       </c>
       <c r="R44" t="n">
-        <v>7171598</v>
+        <v>7171733</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5473,7 +5469,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>över 0,5 meter lång bål</t>
+          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5482,7 +5478,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5501,10 +5496,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123113317</v>
+        <v>123107459</v>
       </c>
       <c r="B45" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5517,16 +5512,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5539,7 +5534,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5549,10 +5544,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>810707</v>
+        <v>811055</v>
       </c>
       <c r="R45" t="n">
-        <v>7171592</v>
+        <v>7171672</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5589,7 +5584,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>hål i gammal sälg</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5616,7 +5611,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123107500</v>
+        <v>123113174</v>
       </c>
       <c r="B46" t="n">
         <v>78766</v>
@@ -5663,10 +5658,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811043</v>
+        <v>810865</v>
       </c>
       <c r="R46" t="n">
-        <v>7171704</v>
+        <v>7171668</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5699,6 +5694,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5726,10 +5726,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123113205</v>
+        <v>123107271</v>
       </c>
       <c r="B47" t="n">
-        <v>78800</v>
+        <v>57494</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5742,30 +5742,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5773,10 +5774,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810862</v>
+        <v>810992</v>
       </c>
       <c r="R47" t="n">
-        <v>7171664</v>
+        <v>7171739</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5811,13 +5812,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5836,10 +5841,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123105448</v>
+        <v>123107525</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>78792</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5848,25 +5853,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5875,11 +5880,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5887,10 +5888,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>810833</v>
+        <v>811018</v>
       </c>
       <c r="R48" t="n">
-        <v>7171608</v>
+        <v>7171753</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5923,11 +5924,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5955,10 +5951,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123107351</v>
+        <v>123107511</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>78792</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5967,25 +5963,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5994,11 +5990,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6006,10 +5998,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811003</v>
+        <v>811066</v>
       </c>
       <c r="R49" t="n">
-        <v>7171721</v>
+        <v>7171715</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6042,11 +6034,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6074,7 +6061,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123107580</v>
+        <v>123105488</v>
       </c>
       <c r="B50" t="n">
         <v>78766</v>
@@ -6121,10 +6108,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>810886</v>
+        <v>810824</v>
       </c>
       <c r="R50" t="n">
-        <v>7171705</v>
+        <v>7171598</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6157,6 +6144,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6184,7 +6176,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123105526</v>
+        <v>123107580</v>
       </c>
       <c r="B51" t="n">
         <v>78766</v>
@@ -6231,10 +6223,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>810798</v>
+        <v>810886</v>
       </c>
       <c r="R51" t="n">
-        <v>7171573</v>
+        <v>7171705</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6294,10 +6286,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123113295</v>
+        <v>123113230</v>
       </c>
       <c r="B52" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6310,31 +6302,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6342,10 +6333,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810851</v>
+        <v>810850</v>
       </c>
       <c r="R52" t="n">
-        <v>7171663</v>
+        <v>7171671</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6380,17 +6371,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>hack i död ved</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6409,10 +6396,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123105541</v>
+        <v>123107487</v>
       </c>
       <c r="B53" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6421,25 +6408,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6456,10 +6443,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810786</v>
+        <v>811052</v>
       </c>
       <c r="R53" t="n">
-        <v>7171568</v>
+        <v>7171679</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6492,6 +6479,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6519,10 +6511,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123107589</v>
+        <v>123107426</v>
       </c>
       <c r="B54" t="n">
-        <v>82553</v>
+        <v>57494</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6535,30 +6527,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6566,10 +6555,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810886</v>
+        <v>811024</v>
       </c>
       <c r="R54" t="n">
-        <v>7171705</v>
+        <v>7171733</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6604,13 +6593,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6629,10 +6622,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123107459</v>
+        <v>123107500</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6645,31 +6638,30 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6677,10 +6669,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811055</v>
+        <v>811043</v>
       </c>
       <c r="R55" t="n">
-        <v>7171672</v>
+        <v>7171704</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6715,17 +6707,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6744,7 +6732,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123107487</v>
+        <v>123105526</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -6791,10 +6779,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811052</v>
+        <v>810798</v>
       </c>
       <c r="R56" t="n">
-        <v>7171679</v>
+        <v>7171573</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6827,11 +6815,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6859,7 +6842,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123107426</v>
+        <v>123113317</v>
       </c>
       <c r="B57" t="n">
         <v>57494</v>
@@ -6895,7 +6878,11 @@
       <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6903,10 +6890,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811024</v>
+        <v>810707</v>
       </c>
       <c r="R57" t="n">
-        <v>7171733</v>
+        <v>7171592</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6943,7 +6930,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+          <t>hål i gammal sälg</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6970,10 +6957,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123113132</v>
+        <v>123113205</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>78800</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6986,31 +6973,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7018,10 +7004,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810895</v>
+        <v>810862</v>
       </c>
       <c r="R58" t="n">
-        <v>7171694</v>
+        <v>7171664</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7056,17 +7042,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7085,10 +7067,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123107271</v>
+        <v>123113132</v>
       </c>
       <c r="B59" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7101,16 +7083,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7123,7 +7105,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7133,10 +7115,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>810992</v>
+        <v>810895</v>
       </c>
       <c r="R59" t="n">
-        <v>7171739</v>
+        <v>7171694</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7173,7 +7155,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7200,10 +7182,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123113230</v>
+        <v>123107538</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>78792</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7212,25 +7194,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7247,10 +7229,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810850</v>
+        <v>810978</v>
       </c>
       <c r="R60" t="n">
-        <v>7171671</v>
+        <v>7171744</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7310,10 +7292,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123107525</v>
+        <v>123107351</v>
       </c>
       <c r="B61" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7322,25 +7304,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7349,7 +7331,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7357,10 +7343,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811018</v>
+        <v>811003</v>
       </c>
       <c r="R61" t="n">
-        <v>7171753</v>
+        <v>7171721</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7393,6 +7379,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7420,10 +7411,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123107538</v>
+        <v>123105448</v>
       </c>
       <c r="B62" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7432,25 +7423,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7459,7 +7450,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7467,10 +7462,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>810978</v>
+        <v>810833</v>
       </c>
       <c r="R62" t="n">
-        <v>7171744</v>
+        <v>7171608</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7503,6 +7498,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -3715,10 +3715,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122650339</v>
+        <v>122649988</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3731,27 +3731,30 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3759,10 +3762,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810833</v>
+        <v>810939</v>
       </c>
       <c r="R29" t="n">
-        <v>7171605</v>
+        <v>7171498</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3797,17 +3800,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3826,10 +3825,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122649988</v>
+        <v>122650339</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3842,30 +3841,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3873,10 +3869,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810939</v>
+        <v>810833</v>
       </c>
       <c r="R30" t="n">
-        <v>7171498</v>
+        <v>7171605</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3911,13 +3907,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal senvuxen gran</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -6732,10 +6732,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123105526</v>
+        <v>123113317</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6748,30 +6748,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6779,10 +6780,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810798</v>
+        <v>810707</v>
       </c>
       <c r="R56" t="n">
-        <v>7171573</v>
+        <v>7171592</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6817,13 +6818,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>hål i gammal sälg</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6842,10 +6847,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123113317</v>
+        <v>123113205</v>
       </c>
       <c r="B57" t="n">
-        <v>57494</v>
+        <v>78800</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6858,31 +6863,30 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6890,10 +6894,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810707</v>
+        <v>810862</v>
       </c>
       <c r="R57" t="n">
-        <v>7171592</v>
+        <v>7171664</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6928,17 +6932,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>hål i gammal sälg</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6957,10 +6957,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123113205</v>
+        <v>123105526</v>
       </c>
       <c r="B58" t="n">
-        <v>78800</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6973,21 +6973,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7004,10 +7004,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810862</v>
+        <v>810798</v>
       </c>
       <c r="R58" t="n">
-        <v>7171664</v>
+        <v>7171573</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122645713</v>
+        <v>122649797</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>56680</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,30 +925,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810368</v>
+        <v>810426</v>
       </c>
       <c r="R4" t="n">
-        <v>7171378</v>
+        <v>7171539</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1001,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122649880</v>
+        <v>122645747</v>
       </c>
       <c r="B5" t="n">
-        <v>57447</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,31 +1031,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100136</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810599</v>
+        <v>810444</v>
       </c>
       <c r="R5" t="n">
-        <v>7171453</v>
+        <v>7171459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,17 +1097,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>satt i en gran längs vägen</t>
+          <t>barksprätt på gammelgran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,10 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122645804</v>
+        <v>122645881</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,31 +1150,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810405</v>
+        <v>810380</v>
       </c>
       <c r="R6" t="n">
-        <v>7171515</v>
+        <v>7171534</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,17 +1219,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1245,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122645698</v>
+        <v>122645713</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,31 +1260,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1293,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810288</v>
+        <v>810368</v>
       </c>
       <c r="R7" t="n">
-        <v>7171439</v>
+        <v>7171378</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,17 +1329,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>barksprätt på senvuxen gammelgran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1580,7 +1574,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122645725</v>
+        <v>122645705</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1627,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>810444</v>
+        <v>810319</v>
       </c>
       <c r="R10" t="n">
-        <v>7171408</v>
+        <v>7171499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,10 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122645789</v>
+        <v>122650377</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>90917</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,31 +1696,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1737,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810427</v>
+        <v>810600</v>
       </c>
       <c r="R11" t="n">
-        <v>7171501</v>
+        <v>7171604</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122645705</v>
+        <v>122645768</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,30 +1810,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1847,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810319</v>
+        <v>810402</v>
       </c>
       <c r="R12" t="n">
-        <v>7171499</v>
+        <v>7171498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,13 +1880,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>påbörjat bohål?</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1910,10 +1909,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122650377</v>
+        <v>122649837</v>
       </c>
       <c r="B13" t="n">
-        <v>90917</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,31 +1921,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1957,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810600</v>
+        <v>810545</v>
       </c>
       <c r="R13" t="n">
-        <v>7171604</v>
+        <v>7171458</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122649797</v>
+        <v>122649813</v>
       </c>
       <c r="B14" t="n">
-        <v>56680</v>
+        <v>78798</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,31 +2035,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2068,10 +2066,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810426</v>
+        <v>810503</v>
       </c>
       <c r="R14" t="n">
-        <v>7171539</v>
+        <v>7171478</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2112,6 +2110,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2130,7 +2129,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122645881</v>
+        <v>122645725</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2177,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810380</v>
+        <v>810444</v>
       </c>
       <c r="R15" t="n">
-        <v>7171534</v>
+        <v>7171408</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2240,7 +2239,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122649837</v>
+        <v>122645789</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2287,10 +2286,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>810545</v>
+        <v>810427</v>
       </c>
       <c r="R16" t="n">
-        <v>7171458</v>
+        <v>7171501</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2460,7 +2459,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122645747</v>
+        <v>122645893</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2508,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810444</v>
+        <v>810397</v>
       </c>
       <c r="R18" t="n">
-        <v>7171459</v>
+        <v>7171536</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2548,7 +2547,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>barksprätt på gammelgran</t>
+          <t>födosök på gran men kan vara från en annan hackspett</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122645893</v>
+        <v>122649880</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>57447</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2587,35 +2586,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100136</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2623,10 +2618,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810397</v>
+        <v>810599</v>
       </c>
       <c r="R19" t="n">
-        <v>7171536</v>
+        <v>7171453</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2653,17 +2648,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>födosök på gran men kan vara från en annan hackspett</t>
+          <t>satt i en gran längs vägen</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2690,10 +2685,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122649813</v>
+        <v>122645804</v>
       </c>
       <c r="B20" t="n">
-        <v>78800</v>
+        <v>57494</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2706,30 +2701,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2737,10 +2733,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>810503</v>
+        <v>810405</v>
       </c>
       <c r="R20" t="n">
-        <v>7171478</v>
+        <v>7171515</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2775,13 +2771,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2800,7 +2800,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122645768</v>
+        <v>122645698</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810402</v>
+        <v>810288</v>
       </c>
       <c r="R21" t="n">
-        <v>7171498</v>
+        <v>7171439</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>påbörjat bohål?</t>
+          <t>barksprätt på senvuxen gammelgran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123104581</v>
+        <v>123104657</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,16 +2931,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>810444</v>
+        <v>810447</v>
       </c>
       <c r="R22" t="n">
-        <v>7171466</v>
+        <v>7171526</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123104657</v>
+        <v>123104581</v>
       </c>
       <c r="B23" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3046,16 +3046,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>810447</v>
+        <v>810444</v>
       </c>
       <c r="R23" t="n">
-        <v>7171526</v>
+        <v>7171466</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3715,10 +3715,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122649988</v>
+        <v>122650339</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3731,30 +3731,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3762,10 +3759,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810939</v>
+        <v>810833</v>
       </c>
       <c r="R29" t="n">
-        <v>7171498</v>
+        <v>7171605</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3800,13 +3797,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal senvuxen gran</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3825,10 +3826,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122650339</v>
+        <v>122650270</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3841,27 +3842,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3869,10 +3873,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810833</v>
+        <v>811036</v>
       </c>
       <c r="R30" t="n">
-        <v>7171605</v>
+        <v>7171698</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3907,17 +3911,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3936,7 +3936,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122650350</v>
+        <v>122650292</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810833</v>
+        <v>810931</v>
       </c>
       <c r="R31" t="n">
-        <v>7171605</v>
+        <v>7171669</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4046,7 +4046,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122650066</v>
+        <v>122650329</v>
       </c>
       <c r="B32" t="n">
         <v>78766</v>
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810939</v>
+        <v>810886</v>
       </c>
       <c r="R32" t="n">
-        <v>7171504</v>
+        <v>7171642</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4156,7 +4156,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122650292</v>
+        <v>122650350</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810931</v>
+        <v>810833</v>
       </c>
       <c r="R33" t="n">
-        <v>7171669</v>
+        <v>7171605</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4266,10 +4266,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122650277</v>
+        <v>122649988</v>
       </c>
       <c r="B34" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4282,31 +4282,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4314,10 +4313,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811014</v>
+        <v>810939</v>
       </c>
       <c r="R34" t="n">
-        <v>7171734</v>
+        <v>7171498</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4352,17 +4351,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>hack i gran, både äldre och färska hack</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4381,10 +4376,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122649934</v>
+        <v>122649921</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4397,31 +4392,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4429,10 +4423,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810828</v>
+        <v>810786</v>
       </c>
       <c r="R35" t="n">
-        <v>7171441</v>
+        <v>7171426</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4467,17 +4461,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>äldre ringhack i gran</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4496,7 +4486,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122649892</v>
+        <v>122650264</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4543,10 +4533,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>810633</v>
+        <v>811045</v>
       </c>
       <c r="R36" t="n">
-        <v>7171420</v>
+        <v>7171680</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4606,7 +4596,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122650264</v>
+        <v>122650066</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4653,10 +4643,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811045</v>
+        <v>810939</v>
       </c>
       <c r="R37" t="n">
-        <v>7171680</v>
+        <v>7171504</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4716,7 +4706,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122649921</v>
+        <v>122649892</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4763,10 +4753,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>810786</v>
+        <v>810633</v>
       </c>
       <c r="R38" t="n">
-        <v>7171426</v>
+        <v>7171420</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4826,10 +4816,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122650270</v>
+        <v>122649934</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4842,30 +4832,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4873,10 +4864,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811036</v>
+        <v>810828</v>
       </c>
       <c r="R39" t="n">
-        <v>7171698</v>
+        <v>7171441</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4911,13 +4902,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>äldre ringhack i gran</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4936,10 +4931,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122650329</v>
+        <v>122650277</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4952,30 +4947,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4983,10 +4979,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>810886</v>
+        <v>811014</v>
       </c>
       <c r="R40" t="n">
-        <v>7171642</v>
+        <v>7171734</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5021,13 +5017,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>hack i gran, både äldre och färska hack</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5046,10 +5046,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123105541</v>
+        <v>123105488</v>
       </c>
       <c r="B41" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5058,25 +5058,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>810786</v>
+        <v>810824</v>
       </c>
       <c r="R41" t="n">
-        <v>7171568</v>
+        <v>7171598</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5129,6 +5129,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5156,10 +5161,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123107589</v>
+        <v>123107271</v>
       </c>
       <c r="B42" t="n">
-        <v>82553</v>
+        <v>57494</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5172,30 +5177,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5203,10 +5209,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810886</v>
+        <v>810992</v>
       </c>
       <c r="R42" t="n">
-        <v>7171705</v>
+        <v>7171739</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5241,13 +5247,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5266,10 +5276,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123113295</v>
+        <v>123105448</v>
       </c>
       <c r="B43" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5282,29 +5292,32 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5314,10 +5327,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810851</v>
+        <v>810833</v>
       </c>
       <c r="R43" t="n">
-        <v>7171663</v>
+        <v>7171608</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5354,7 +5367,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5363,6 +5376,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5381,10 +5395,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123107409</v>
+        <v>123107500</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5397,31 +5411,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5429,10 +5442,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811024</v>
+        <v>811043</v>
       </c>
       <c r="R44" t="n">
-        <v>7171733</v>
+        <v>7171704</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5467,17 +5480,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5496,10 +5505,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123107459</v>
+        <v>123107426</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5512,16 +5521,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5532,11 +5541,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5544,10 +5549,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811055</v>
+        <v>811024</v>
       </c>
       <c r="R45" t="n">
-        <v>7171672</v>
+        <v>7171733</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5584,7 +5589,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5611,7 +5616,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123113174</v>
+        <v>123105526</v>
       </c>
       <c r="B46" t="n">
         <v>78766</v>
@@ -5658,10 +5663,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>810865</v>
+        <v>810798</v>
       </c>
       <c r="R46" t="n">
-        <v>7171668</v>
+        <v>7171573</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5694,11 +5699,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5726,10 +5726,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123107271</v>
+        <v>123113205</v>
       </c>
       <c r="B47" t="n">
-        <v>57494</v>
+        <v>78798</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5742,31 +5742,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5774,10 +5773,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810992</v>
+        <v>810862</v>
       </c>
       <c r="R47" t="n">
-        <v>7171739</v>
+        <v>7171664</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5812,17 +5811,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>hack i död ved</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5841,10 +5836,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123107525</v>
+        <v>123107511</v>
       </c>
       <c r="B48" t="n">
-        <v>78792</v>
+        <v>78790</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5888,10 +5883,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811018</v>
+        <v>811066</v>
       </c>
       <c r="R48" t="n">
-        <v>7171753</v>
+        <v>7171715</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5951,10 +5946,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123107511</v>
+        <v>123107487</v>
       </c>
       <c r="B49" t="n">
-        <v>78792</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5963,25 +5958,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5998,10 +5993,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811066</v>
+        <v>811052</v>
       </c>
       <c r="R49" t="n">
-        <v>7171715</v>
+        <v>7171679</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6034,6 +6029,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6061,7 +6061,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123105488</v>
+        <v>123107580</v>
       </c>
       <c r="B50" t="n">
         <v>78766</v>
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>810824</v>
+        <v>810886</v>
       </c>
       <c r="R50" t="n">
-        <v>7171598</v>
+        <v>7171705</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6144,11 +6144,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6176,10 +6171,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123107580</v>
+        <v>123107538</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>78790</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6188,25 +6183,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6223,10 +6218,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>810886</v>
+        <v>810978</v>
       </c>
       <c r="R51" t="n">
-        <v>7171705</v>
+        <v>7171744</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6286,10 +6281,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123113230</v>
+        <v>123107525</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>78790</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6298,25 +6293,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6333,10 +6328,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810850</v>
+        <v>811018</v>
       </c>
       <c r="R52" t="n">
-        <v>7171671</v>
+        <v>7171753</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6396,7 +6391,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123107487</v>
+        <v>123113230</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -6443,10 +6438,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811052</v>
+        <v>810850</v>
       </c>
       <c r="R53" t="n">
-        <v>7171679</v>
+        <v>7171671</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6479,11 +6474,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6511,7 +6501,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123107426</v>
+        <v>123113295</v>
       </c>
       <c r="B54" t="n">
         <v>57494</v>
@@ -6547,7 +6537,11 @@
       <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6555,10 +6549,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811024</v>
+        <v>810851</v>
       </c>
       <c r="R54" t="n">
-        <v>7171733</v>
+        <v>7171663</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6595,7 +6589,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6622,7 +6616,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123107500</v>
+        <v>123113174</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6669,10 +6663,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811043</v>
+        <v>810865</v>
       </c>
       <c r="R55" t="n">
-        <v>7171704</v>
+        <v>7171668</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6705,6 +6699,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6732,10 +6731,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123113317</v>
+        <v>123107459</v>
       </c>
       <c r="B56" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6748,16 +6747,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6770,7 +6769,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6780,10 +6779,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810707</v>
+        <v>811055</v>
       </c>
       <c r="R56" t="n">
-        <v>7171592</v>
+        <v>7171672</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6820,7 +6819,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>hål i gammal sälg</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6847,10 +6846,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123113205</v>
+        <v>123113317</v>
       </c>
       <c r="B57" t="n">
-        <v>78800</v>
+        <v>57494</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6863,30 +6862,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810862</v>
+        <v>810707</v>
       </c>
       <c r="R57" t="n">
-        <v>7171664</v>
+        <v>7171592</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6932,13 +6932,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>hål i gammal sälg</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6957,7 +6961,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123105526</v>
+        <v>123107351</v>
       </c>
       <c r="B58" t="n">
         <v>78766</v>
@@ -6996,7 +7000,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7004,10 +7012,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810798</v>
+        <v>811003</v>
       </c>
       <c r="R58" t="n">
-        <v>7171573</v>
+        <v>7171721</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7040,6 +7048,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7067,10 +7080,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123113132</v>
+        <v>123105541</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>78790</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7079,35 +7092,34 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7115,10 +7127,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>810895</v>
+        <v>810786</v>
       </c>
       <c r="R59" t="n">
-        <v>7171694</v>
+        <v>7171568</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7153,17 +7165,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7182,10 +7190,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123107538</v>
+        <v>123107589</v>
       </c>
       <c r="B60" t="n">
-        <v>78792</v>
+        <v>82553</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7194,31 +7202,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6434</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -7229,10 +7237,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810978</v>
+        <v>810886</v>
       </c>
       <c r="R60" t="n">
-        <v>7171744</v>
+        <v>7171705</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7292,10 +7300,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123107351</v>
+        <v>123107409</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7308,32 +7316,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7343,10 +7348,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811003</v>
+        <v>811024</v>
       </c>
       <c r="R61" t="n">
-        <v>7171721</v>
+        <v>7171733</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7383,7 +7388,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>fertil garnlav</t>
+          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7392,7 +7397,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7411,10 +7415,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123105448</v>
+        <v>123113132</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7427,32 +7431,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7462,10 +7463,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>810833</v>
+        <v>810895</v>
       </c>
       <c r="R62" t="n">
-        <v>7171608</v>
+        <v>7171694</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7502,7 +7503,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>rikligt med fertil garnlav på gammal död gran</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7511,7 +7512,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -5395,10 +5395,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123107500</v>
+        <v>123107426</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5411,30 +5411,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5442,10 +5439,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811043</v>
+        <v>811024</v>
       </c>
       <c r="R44" t="n">
-        <v>7171704</v>
+        <v>7171733</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5480,13 +5477,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5505,10 +5506,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123107426</v>
+        <v>123107500</v>
       </c>
       <c r="B45" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5521,27 +5522,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5549,10 +5553,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811024</v>
+        <v>811043</v>
       </c>
       <c r="R45" t="n">
-        <v>7171733</v>
+        <v>7171704</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5587,17 +5591,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -7080,10 +7080,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123105541</v>
+        <v>123107589</v>
       </c>
       <c r="B59" t="n">
-        <v>78790</v>
+        <v>82553</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7092,31 +7092,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6434</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>810786</v>
+        <v>810886</v>
       </c>
       <c r="R59" t="n">
-        <v>7171568</v>
+        <v>7171705</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7190,10 +7190,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123107589</v>
+        <v>123105541</v>
       </c>
       <c r="B60" t="n">
-        <v>82553</v>
+        <v>78790</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7202,31 +7202,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>6434</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810886</v>
+        <v>810786</v>
       </c>
       <c r="R60" t="n">
-        <v>7171705</v>
+        <v>7171568</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -5395,10 +5395,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123107426</v>
+        <v>123107500</v>
       </c>
       <c r="B44" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5411,27 +5411,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5439,10 +5442,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811024</v>
+        <v>811043</v>
       </c>
       <c r="R44" t="n">
-        <v>7171733</v>
+        <v>7171704</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5477,17 +5480,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5506,10 +5505,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123107500</v>
+        <v>123107426</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5522,30 +5521,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5553,10 +5549,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811043</v>
+        <v>811024</v>
       </c>
       <c r="R45" t="n">
-        <v>7171704</v>
+        <v>7171733</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5591,13 +5587,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6731,10 +6731,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123107459</v>
+        <v>123113317</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6747,16 +6747,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6769,7 +6769,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6779,10 +6779,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811055</v>
+        <v>810707</v>
       </c>
       <c r="R56" t="n">
-        <v>7171672</v>
+        <v>7171592</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6819,7 +6819,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hål i gammal sälg</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6846,10 +6846,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123113317</v>
+        <v>123107459</v>
       </c>
       <c r="B57" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6862,16 +6862,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6884,7 +6884,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810707</v>
+        <v>811055</v>
       </c>
       <c r="R57" t="n">
-        <v>7171592</v>
+        <v>7171672</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>hål i gammal sälg</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7080,10 +7080,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123107589</v>
+        <v>123105541</v>
       </c>
       <c r="B59" t="n">
-        <v>82553</v>
+        <v>78790</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7092,31 +7092,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>6434</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -7127,10 +7127,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>810886</v>
+        <v>810786</v>
       </c>
       <c r="R59" t="n">
-        <v>7171705</v>
+        <v>7171568</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7190,10 +7190,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123105541</v>
+        <v>123107589</v>
       </c>
       <c r="B60" t="n">
-        <v>78790</v>
+        <v>82553</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7202,31 +7202,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6434</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810786</v>
+        <v>810886</v>
       </c>
       <c r="R60" t="n">
-        <v>7171568</v>
+        <v>7171705</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122649797</v>
+        <v>122645804</v>
       </c>
       <c r="B4" t="n">
-        <v>56680</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,16 +925,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,7 +947,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810426</v>
+        <v>810405</v>
       </c>
       <c r="R4" t="n">
-        <v>7171539</v>
+        <v>7171515</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,6 +993,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122645747</v>
+        <v>122645713</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,31 +1040,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810444</v>
+        <v>810368</v>
       </c>
       <c r="R5" t="n">
-        <v>7171459</v>
+        <v>7171378</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,17 +1109,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>barksprätt på gammelgran</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1134,7 +1134,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122645881</v>
+        <v>122645705</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810380</v>
+        <v>810319</v>
       </c>
       <c r="R6" t="n">
-        <v>7171534</v>
+        <v>7171499</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122645713</v>
+        <v>122649797</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>56680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,30 +1260,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1291,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810368</v>
+        <v>810426</v>
       </c>
       <c r="R7" t="n">
-        <v>7171378</v>
+        <v>7171539</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1336,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1464,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122649804</v>
+        <v>122645881</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>810465</v>
+        <v>810380</v>
       </c>
       <c r="R9" t="n">
-        <v>7171522</v>
+        <v>7171534</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1574,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122645705</v>
+        <v>122645753</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>810319</v>
+        <v>810433</v>
       </c>
       <c r="R10" t="n">
-        <v>7171499</v>
+        <v>7171480</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122650377</v>
+        <v>122645747</v>
       </c>
       <c r="B11" t="n">
-        <v>90917</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,34 +1696,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1731,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810600</v>
+        <v>810444</v>
       </c>
       <c r="R11" t="n">
-        <v>7171604</v>
+        <v>7171459</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,13 +1770,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>barksprätt på gammelgran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1794,7 +1799,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122645768</v>
+        <v>122645893</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810402</v>
+        <v>810397</v>
       </c>
       <c r="R12" t="n">
-        <v>7171498</v>
+        <v>7171536</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1887,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>påbörjat bohål?</t>
+          <t>födosök på gran men kan vara från en annan hackspett</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122649837</v>
+        <v>122645768</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1925,30 +1930,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1956,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810545</v>
+        <v>810402</v>
       </c>
       <c r="R13" t="n">
-        <v>7171458</v>
+        <v>7171498</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1994,13 +2000,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>påbörjat bohål?</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2019,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122649813</v>
+        <v>122645725</v>
       </c>
       <c r="B14" t="n">
-        <v>78798</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2045,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2066,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810503</v>
+        <v>810444</v>
       </c>
       <c r="R14" t="n">
-        <v>7171478</v>
+        <v>7171408</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122645725</v>
+        <v>122649880</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57447</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2141,34 +2151,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100136</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2176,10 +2183,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810444</v>
+        <v>810599</v>
       </c>
       <c r="R15" t="n">
-        <v>7171408</v>
+        <v>7171453</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,12 +2213,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2014-10-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>satt i en gran längs vägen</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2220,7 +2232,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2239,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122645789</v>
+        <v>122645698</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,30 +2266,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2286,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>810427</v>
+        <v>810288</v>
       </c>
       <c r="R16" t="n">
-        <v>7171501</v>
+        <v>7171439</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2324,13 +2336,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>barksprätt på senvuxen gammelgran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2349,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122645753</v>
+        <v>122649813</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>78798</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2365,21 +2381,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2396,10 +2412,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>810433</v>
+        <v>810503</v>
       </c>
       <c r="R17" t="n">
-        <v>7171480</v>
+        <v>7171478</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2459,10 +2475,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122645893</v>
+        <v>122649804</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2475,31 +2491,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2507,10 +2522,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810397</v>
+        <v>810465</v>
       </c>
       <c r="R18" t="n">
-        <v>7171536</v>
+        <v>7171522</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2545,17 +2560,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>födosök på gran men kan vara från en annan hackspett</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2574,10 +2585,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122649880</v>
+        <v>122650377</v>
       </c>
       <c r="B19" t="n">
-        <v>57447</v>
+        <v>90917</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,31 +2597,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100136</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2618,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810599</v>
+        <v>810600</v>
       </c>
       <c r="R19" t="n">
-        <v>7171453</v>
+        <v>7171604</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2648,17 +2662,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2014-10-28</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>satt i en gran längs vägen</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,6 +2676,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2685,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122645804</v>
+        <v>122645789</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2701,31 +2711,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2733,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>810405</v>
+        <v>810427</v>
       </c>
       <c r="R20" t="n">
-        <v>7171515</v>
+        <v>7171501</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2771,17 +2780,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2800,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122645698</v>
+        <v>122649837</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2816,31 +2821,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2848,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810288</v>
+        <v>810545</v>
       </c>
       <c r="R21" t="n">
-        <v>7171439</v>
+        <v>7171458</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2886,17 +2890,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>barksprätt på senvuxen gammelgran</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3715,10 +3715,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122650339</v>
+        <v>122650329</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3731,27 +3731,30 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3759,10 +3762,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810833</v>
+        <v>810886</v>
       </c>
       <c r="R29" t="n">
-        <v>7171605</v>
+        <v>7171642</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3797,17 +3800,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3826,7 +3825,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122650270</v>
+        <v>122650264</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3873,10 +3872,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811036</v>
+        <v>811045</v>
       </c>
       <c r="R30" t="n">
-        <v>7171698</v>
+        <v>7171680</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3936,7 +3935,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122650292</v>
+        <v>122650270</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -3983,10 +3982,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810931</v>
+        <v>811036</v>
       </c>
       <c r="R31" t="n">
-        <v>7171669</v>
+        <v>7171698</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4046,7 +4045,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122650329</v>
+        <v>122650066</v>
       </c>
       <c r="B32" t="n">
         <v>78766</v>
@@ -4093,10 +4092,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810886</v>
+        <v>810939</v>
       </c>
       <c r="R32" t="n">
-        <v>7171642</v>
+        <v>7171504</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4156,7 +4155,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122650350</v>
+        <v>122649988</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -4203,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810833</v>
+        <v>810939</v>
       </c>
       <c r="R33" t="n">
-        <v>7171605</v>
+        <v>7171498</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4266,7 +4265,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122649988</v>
+        <v>122649921</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4313,10 +4312,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>810939</v>
+        <v>810786</v>
       </c>
       <c r="R34" t="n">
-        <v>7171498</v>
+        <v>7171426</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4376,10 +4375,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122649921</v>
+        <v>122650277</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4392,30 +4391,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810786</v>
+        <v>811014</v>
       </c>
       <c r="R35" t="n">
-        <v>7171426</v>
+        <v>7171734</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4461,13 +4461,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>hack i gran, både äldre och färska hack</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4486,10 +4490,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122650264</v>
+        <v>122650339</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4502,30 +4506,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4533,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811045</v>
+        <v>810833</v>
       </c>
       <c r="R36" t="n">
-        <v>7171680</v>
+        <v>7171605</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4571,13 +4572,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal senvuxen gran</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4596,7 +4601,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122650066</v>
+        <v>122649892</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4643,10 +4648,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810939</v>
+        <v>810633</v>
       </c>
       <c r="R37" t="n">
-        <v>7171504</v>
+        <v>7171420</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4706,7 +4711,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122649892</v>
+        <v>122650292</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4753,10 +4758,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>810633</v>
+        <v>810931</v>
       </c>
       <c r="R38" t="n">
-        <v>7171420</v>
+        <v>7171669</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4816,10 +4821,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122649934</v>
+        <v>122650350</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4832,31 +4837,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4864,10 +4868,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>810828</v>
+        <v>810833</v>
       </c>
       <c r="R39" t="n">
-        <v>7171441</v>
+        <v>7171605</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4902,17 +4906,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>äldre ringhack i gran</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4931,10 +4931,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122650277</v>
+        <v>122649934</v>
       </c>
       <c r="B40" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4947,16 +4947,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4969,7 +4969,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4979,10 +4979,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811014</v>
+        <v>810828</v>
       </c>
       <c r="R40" t="n">
-        <v>7171734</v>
+        <v>7171441</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>hack i gran, både äldre och färska hack</t>
+          <t>äldre ringhack i gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5046,7 +5046,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123105488</v>
+        <v>123107351</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -5085,7 +5085,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5093,10 +5097,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>810824</v>
+        <v>811003</v>
       </c>
       <c r="R41" t="n">
-        <v>7171598</v>
+        <v>7171721</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5133,7 +5137,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>över 0,5 meter lång bål</t>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5161,10 +5165,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123107271</v>
+        <v>123107580</v>
       </c>
       <c r="B42" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5177,31 +5181,30 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5209,10 +5212,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810992</v>
+        <v>810886</v>
       </c>
       <c r="R42" t="n">
-        <v>7171739</v>
+        <v>7171705</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5247,17 +5250,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>hack i död ved</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5276,7 +5275,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123105448</v>
+        <v>123105488</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -5315,11 +5314,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5327,10 +5322,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810833</v>
+        <v>810824</v>
       </c>
       <c r="R43" t="n">
-        <v>7171608</v>
+        <v>7171598</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5367,7 +5362,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>rikligt med fertil garnlav på gammal död gran</t>
+          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5395,10 +5390,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123107500</v>
+        <v>123107538</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>78790</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5407,25 +5402,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5442,10 +5437,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811043</v>
+        <v>810978</v>
       </c>
       <c r="R44" t="n">
-        <v>7171704</v>
+        <v>7171744</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5505,10 +5500,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123107426</v>
+        <v>123113174</v>
       </c>
       <c r="B45" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5521,27 +5516,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5549,10 +5547,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811024</v>
+        <v>810865</v>
       </c>
       <c r="R45" t="n">
-        <v>7171733</v>
+        <v>7171668</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5589,7 +5587,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5598,6 +5596,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5726,10 +5725,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123113205</v>
+        <v>123113230</v>
       </c>
       <c r="B47" t="n">
-        <v>78798</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5742,21 +5741,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5773,10 +5772,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810862</v>
+        <v>810850</v>
       </c>
       <c r="R47" t="n">
-        <v>7171664</v>
+        <v>7171671</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5836,10 +5835,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123107511</v>
+        <v>123107271</v>
       </c>
       <c r="B48" t="n">
-        <v>78790</v>
+        <v>57494</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5848,34 +5847,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811066</v>
+        <v>810992</v>
       </c>
       <c r="R48" t="n">
-        <v>7171715</v>
+        <v>7171739</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5921,13 +5921,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5946,10 +5950,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123107487</v>
+        <v>123107426</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5962,30 +5966,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5993,10 +5994,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811052</v>
+        <v>811024</v>
       </c>
       <c r="R49" t="n">
-        <v>7171679</v>
+        <v>7171733</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6033,7 +6034,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>rikligt med hänglavar bla garnlav</t>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6042,7 +6043,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6061,10 +6061,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123107580</v>
+        <v>123113132</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6077,30 +6077,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6108,10 +6109,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>810886</v>
+        <v>810895</v>
       </c>
       <c r="R50" t="n">
-        <v>7171705</v>
+        <v>7171694</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6146,13 +6147,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6171,7 +6176,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123107538</v>
+        <v>123105541</v>
       </c>
       <c r="B51" t="n">
         <v>78790</v>
@@ -6218,10 +6223,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>810978</v>
+        <v>810786</v>
       </c>
       <c r="R51" t="n">
-        <v>7171744</v>
+        <v>7171568</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6281,10 +6286,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123107525</v>
+        <v>123113295</v>
       </c>
       <c r="B52" t="n">
-        <v>78790</v>
+        <v>57494</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6293,34 +6298,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6328,10 +6334,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811018</v>
+        <v>810851</v>
       </c>
       <c r="R52" t="n">
-        <v>7171753</v>
+        <v>7171663</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6366,13 +6372,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6391,10 +6401,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123113230</v>
+        <v>123113317</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6407,30 +6417,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6438,10 +6449,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810850</v>
+        <v>810707</v>
       </c>
       <c r="R53" t="n">
-        <v>7171671</v>
+        <v>7171592</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6476,13 +6487,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>hål i gammal sälg</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6501,10 +6516,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123113295</v>
+        <v>123107525</v>
       </c>
       <c r="B54" t="n">
-        <v>57494</v>
+        <v>78790</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6513,35 +6528,34 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6549,10 +6563,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810851</v>
+        <v>811018</v>
       </c>
       <c r="R54" t="n">
-        <v>7171663</v>
+        <v>7171753</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6587,17 +6601,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>hack i död ved</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6616,7 +6626,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123113174</v>
+        <v>123105448</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6655,7 +6665,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6663,10 +6677,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810865</v>
+        <v>810833</v>
       </c>
       <c r="R55" t="n">
-        <v>7171668</v>
+        <v>7171608</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6703,7 +6717,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>hänglavrikt bla garnlav</t>
+          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6731,10 +6745,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123113317</v>
+        <v>123113205</v>
       </c>
       <c r="B56" t="n">
-        <v>57494</v>
+        <v>78798</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6747,31 +6761,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6779,10 +6792,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810707</v>
+        <v>810862</v>
       </c>
       <c r="R56" t="n">
-        <v>7171592</v>
+        <v>7171664</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6817,17 +6830,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>hål i gammal sälg</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6846,10 +6855,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123107459</v>
+        <v>123107589</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6862,31 +6871,30 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6894,10 +6902,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811055</v>
+        <v>810886</v>
       </c>
       <c r="R57" t="n">
-        <v>7171672</v>
+        <v>7171705</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6932,17 +6940,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6961,7 +6965,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123107351</v>
+        <v>123107500</v>
       </c>
       <c r="B58" t="n">
         <v>78766</v>
@@ -7000,11 +7004,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7012,10 +7012,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811003</v>
+        <v>811043</v>
       </c>
       <c r="R58" t="n">
-        <v>7171721</v>
+        <v>7171704</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7048,11 +7048,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7080,10 +7075,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123105541</v>
+        <v>123107409</v>
       </c>
       <c r="B59" t="n">
-        <v>78790</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7092,34 +7087,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7127,10 +7123,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>810786</v>
+        <v>811024</v>
       </c>
       <c r="R59" t="n">
-        <v>7171568</v>
+        <v>7171733</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7165,13 +7161,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7190,10 +7190,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123107589</v>
+        <v>123107511</v>
       </c>
       <c r="B60" t="n">
-        <v>82553</v>
+        <v>78790</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7202,31 +7202,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>6434</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810886</v>
+        <v>811066</v>
       </c>
       <c r="R60" t="n">
-        <v>7171705</v>
+        <v>7171715</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7300,10 +7300,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123107409</v>
+        <v>123107487</v>
       </c>
       <c r="B61" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7316,31 +7316,30 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7348,10 +7347,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811024</v>
+        <v>811052</v>
       </c>
       <c r="R61" t="n">
-        <v>7171733</v>
+        <v>7171679</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7388,7 +7387,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
+          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7397,6 +7396,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7415,7 +7415,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123113132</v>
+        <v>123107459</v>
       </c>
       <c r="B62" t="n">
         <v>57478</v>
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>810895</v>
+        <v>811055</v>
       </c>
       <c r="R62" t="n">
-        <v>7171694</v>
+        <v>7171672</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -3030,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123104581</v>
+        <v>123104604</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3046,16 +3046,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>810444</v>
+        <v>810442</v>
       </c>
       <c r="R23" t="n">
-        <v>7171466</v>
+        <v>7171450</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3145,10 +3145,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123104604</v>
+        <v>123104581</v>
       </c>
       <c r="B24" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,16 +3161,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>810442</v>
+        <v>810444</v>
       </c>
       <c r="R24" t="n">
-        <v>7171450</v>
+        <v>7171466</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5046,10 +5046,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123107351</v>
+        <v>123107525</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>78790</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5058,25 +5058,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5085,11 +5085,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5097,10 +5093,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811003</v>
+        <v>811018</v>
       </c>
       <c r="R41" t="n">
-        <v>7171721</v>
+        <v>7171753</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5133,11 +5129,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5165,10 +5156,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123107580</v>
+        <v>123107589</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5181,27 +5172,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -5275,10 +5266,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123105488</v>
+        <v>123113132</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5291,30 +5282,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5322,10 +5314,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810824</v>
+        <v>810895</v>
       </c>
       <c r="R43" t="n">
-        <v>7171598</v>
+        <v>7171694</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5362,7 +5354,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>över 0,5 meter lång bål</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5371,7 +5363,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5390,10 +5381,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123107538</v>
+        <v>123107500</v>
       </c>
       <c r="B44" t="n">
-        <v>78790</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5402,25 +5393,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5437,10 +5428,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>810978</v>
+        <v>811043</v>
       </c>
       <c r="R44" t="n">
-        <v>7171744</v>
+        <v>7171704</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5500,7 +5491,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123113174</v>
+        <v>123113230</v>
       </c>
       <c r="B45" t="n">
         <v>78766</v>
@@ -5547,10 +5538,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>810865</v>
+        <v>810850</v>
       </c>
       <c r="R45" t="n">
-        <v>7171668</v>
+        <v>7171671</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5583,11 +5574,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5725,10 +5711,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123113230</v>
+        <v>123107426</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5741,30 +5727,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5772,10 +5755,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810850</v>
+        <v>811024</v>
       </c>
       <c r="R47" t="n">
-        <v>7171671</v>
+        <v>7171733</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5810,13 +5793,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5835,10 +5822,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123107271</v>
+        <v>123113174</v>
       </c>
       <c r="B48" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5851,31 +5838,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5883,10 +5869,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>810992</v>
+        <v>810865</v>
       </c>
       <c r="R48" t="n">
-        <v>7171739</v>
+        <v>7171668</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5923,7 +5909,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5932,6 +5918,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5950,10 +5937,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123107426</v>
+        <v>123107487</v>
       </c>
       <c r="B49" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5966,27 +5953,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5994,10 +5984,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811024</v>
+        <v>811052</v>
       </c>
       <c r="R49" t="n">
-        <v>7171733</v>
+        <v>7171679</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6034,7 +6024,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6043,6 +6033,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6061,7 +6052,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123113132</v>
+        <v>123107459</v>
       </c>
       <c r="B50" t="n">
         <v>57478</v>
@@ -6109,10 +6100,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>810895</v>
+        <v>811055</v>
       </c>
       <c r="R50" t="n">
-        <v>7171694</v>
+        <v>7171672</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6149,7 +6140,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6176,10 +6167,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123105541</v>
+        <v>123113205</v>
       </c>
       <c r="B51" t="n">
-        <v>78790</v>
+        <v>78798</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6188,25 +6179,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6434</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6223,10 +6214,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>810786</v>
+        <v>810862</v>
       </c>
       <c r="R51" t="n">
-        <v>7171568</v>
+        <v>7171664</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6286,10 +6277,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123113295</v>
+        <v>123107409</v>
       </c>
       <c r="B52" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6302,16 +6293,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6324,7 +6315,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6334,10 +6325,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810851</v>
+        <v>811024</v>
       </c>
       <c r="R52" t="n">
-        <v>7171663</v>
+        <v>7171733</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6374,7 +6365,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6401,10 +6392,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123113317</v>
+        <v>123105448</v>
       </c>
       <c r="B53" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6417,29 +6408,32 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6449,10 +6443,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810707</v>
+        <v>810833</v>
       </c>
       <c r="R53" t="n">
-        <v>7171592</v>
+        <v>7171608</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6489,7 +6483,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>hål i gammal sälg</t>
+          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6498,6 +6492,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6516,10 +6511,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123107525</v>
+        <v>123107351</v>
       </c>
       <c r="B54" t="n">
-        <v>78790</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6528,25 +6523,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6555,7 +6550,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6563,10 +6562,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811018</v>
+        <v>811003</v>
       </c>
       <c r="R54" t="n">
-        <v>7171753</v>
+        <v>7171721</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6599,6 +6598,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6626,10 +6630,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123105448</v>
+        <v>123105541</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>78790</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6638,25 +6642,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6665,11 +6669,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810833</v>
+        <v>810786</v>
       </c>
       <c r="R55" t="n">
-        <v>7171608</v>
+        <v>7171568</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6713,11 +6713,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6745,10 +6740,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123113205</v>
+        <v>123107511</v>
       </c>
       <c r="B56" t="n">
-        <v>78798</v>
+        <v>78790</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6757,25 +6752,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6792,10 +6787,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810862</v>
+        <v>811066</v>
       </c>
       <c r="R56" t="n">
-        <v>7171664</v>
+        <v>7171715</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6855,10 +6850,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123107589</v>
+        <v>123107580</v>
       </c>
       <c r="B57" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6871,27 +6866,27 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -6965,7 +6960,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123107500</v>
+        <v>123105488</v>
       </c>
       <c r="B58" t="n">
         <v>78766</v>
@@ -7012,10 +7007,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811043</v>
+        <v>810824</v>
       </c>
       <c r="R58" t="n">
-        <v>7171704</v>
+        <v>7171598</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7048,6 +7043,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7075,10 +7075,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123107409</v>
+        <v>123113317</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7091,16 +7091,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7113,7 +7113,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7123,10 +7123,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811024</v>
+        <v>810707</v>
       </c>
       <c r="R59" t="n">
-        <v>7171733</v>
+        <v>7171592</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
+          <t>hål i gammal sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7190,10 +7190,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123107511</v>
+        <v>123113295</v>
       </c>
       <c r="B60" t="n">
-        <v>78790</v>
+        <v>57494</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7202,34 +7202,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7237,10 +7238,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811066</v>
+        <v>810851</v>
       </c>
       <c r="R60" t="n">
-        <v>7171715</v>
+        <v>7171663</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7275,13 +7276,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7300,10 +7305,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123107487</v>
+        <v>123107538</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>78790</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7312,25 +7317,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7347,10 +7352,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811052</v>
+        <v>810978</v>
       </c>
       <c r="R61" t="n">
-        <v>7171679</v>
+        <v>7171744</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7383,11 +7388,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7415,10 +7415,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123107459</v>
+        <v>123107271</v>
       </c>
       <c r="B62" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7431,16 +7431,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7453,7 +7453,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811055</v>
+        <v>810992</v>
       </c>
       <c r="R62" t="n">
-        <v>7171672</v>
+        <v>7171739</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123104657</v>
+        <v>123104581</v>
       </c>
       <c r="B22" t="n">
-        <v>57494</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,16 +2931,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>810447</v>
+        <v>810444</v>
       </c>
       <c r="R22" t="n">
-        <v>7171526</v>
+        <v>7171466</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123104604</v>
+        <v>123104657</v>
       </c>
       <c r="B23" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>810442</v>
+        <v>810447</v>
       </c>
       <c r="R23" t="n">
-        <v>7171450</v>
+        <v>7171526</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3145,10 +3145,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123104581</v>
+        <v>123104604</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>57497</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,16 +3161,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>810444</v>
+        <v>810442</v>
       </c>
       <c r="R24" t="n">
-        <v>7171466</v>
+        <v>7171450</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5046,10 +5046,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123107525</v>
+        <v>123107500</v>
       </c>
       <c r="B41" t="n">
-        <v>78790</v>
+        <v>78769</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5058,25 +5058,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811018</v>
+        <v>811043</v>
       </c>
       <c r="R41" t="n">
-        <v>7171753</v>
+        <v>7171704</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5156,10 +5156,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123107589</v>
+        <v>123113132</v>
       </c>
       <c r="B42" t="n">
-        <v>82553</v>
+        <v>57481</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5172,30 +5172,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5203,10 +5204,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810886</v>
+        <v>810895</v>
       </c>
       <c r="R42" t="n">
-        <v>7171705</v>
+        <v>7171694</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5241,13 +5242,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5266,10 +5271,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123113132</v>
+        <v>123113295</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>57497</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5282,16 +5287,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5304,7 +5309,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5314,10 +5319,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810895</v>
+        <v>810851</v>
       </c>
       <c r="R43" t="n">
-        <v>7171694</v>
+        <v>7171663</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5354,7 +5359,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5381,10 +5386,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123107500</v>
+        <v>123107426</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>57497</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5397,30 +5402,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5428,10 +5430,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811043</v>
+        <v>811024</v>
       </c>
       <c r="R44" t="n">
-        <v>7171704</v>
+        <v>7171733</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5466,13 +5468,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5491,10 +5497,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123113230</v>
+        <v>123107538</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>78793</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5503,25 +5509,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5538,10 +5544,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>810850</v>
+        <v>810978</v>
       </c>
       <c r="R45" t="n">
-        <v>7171671</v>
+        <v>7171744</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5601,10 +5607,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123105526</v>
+        <v>123107525</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>78793</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5613,25 +5619,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5648,10 +5654,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>810798</v>
+        <v>811018</v>
       </c>
       <c r="R46" t="n">
-        <v>7171573</v>
+        <v>7171753</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5711,10 +5717,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123107426</v>
+        <v>123113174</v>
       </c>
       <c r="B47" t="n">
-        <v>57494</v>
+        <v>78769</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5727,27 +5733,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5755,10 +5764,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811024</v>
+        <v>810865</v>
       </c>
       <c r="R47" t="n">
-        <v>7171733</v>
+        <v>7171668</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5795,7 +5804,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5804,6 +5813,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5822,10 +5832,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123113174</v>
+        <v>123107271</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>57497</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5838,30 +5848,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5869,10 +5880,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>810865</v>
+        <v>810992</v>
       </c>
       <c r="R48" t="n">
-        <v>7171668</v>
+        <v>7171739</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5909,7 +5920,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>hänglavrikt bla garnlav</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5918,7 +5929,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5937,10 +5947,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123107487</v>
+        <v>123113205</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>78801</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5953,21 +5963,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5984,10 +5994,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811052</v>
+        <v>810862</v>
       </c>
       <c r="R49" t="n">
-        <v>7171679</v>
+        <v>7171664</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6020,11 +6030,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6052,10 +6057,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123107459</v>
+        <v>123113230</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6068,31 +6073,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6100,10 +6104,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811055</v>
+        <v>810850</v>
       </c>
       <c r="R50" t="n">
-        <v>7171672</v>
+        <v>7171671</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6138,17 +6142,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6167,10 +6167,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123113205</v>
+        <v>123105526</v>
       </c>
       <c r="B51" t="n">
-        <v>78798</v>
+        <v>78769</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6183,21 +6183,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6214,10 +6214,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>810862</v>
+        <v>810798</v>
       </c>
       <c r="R51" t="n">
-        <v>7171664</v>
+        <v>7171573</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6277,10 +6277,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123107409</v>
+        <v>123105448</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6293,29 +6293,32 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6325,10 +6328,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811024</v>
+        <v>810833</v>
       </c>
       <c r="R52" t="n">
-        <v>7171733</v>
+        <v>7171608</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6365,7 +6368,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
+          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6374,6 +6377,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6392,10 +6396,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123105448</v>
+        <v>123107589</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>82556</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6408,34 +6412,30 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6443,10 +6443,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810833</v>
+        <v>810886</v>
       </c>
       <c r="R53" t="n">
-        <v>7171608</v>
+        <v>7171705</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6479,11 +6479,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6511,10 +6506,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123107351</v>
+        <v>123107511</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>78793</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6523,25 +6518,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6550,11 +6545,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6562,10 +6553,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811003</v>
+        <v>811066</v>
       </c>
       <c r="R54" t="n">
-        <v>7171721</v>
+        <v>7171715</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6598,11 +6589,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6630,10 +6616,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123105541</v>
+        <v>123107487</v>
       </c>
       <c r="B55" t="n">
-        <v>78790</v>
+        <v>78769</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6642,25 +6628,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6677,10 +6663,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810786</v>
+        <v>811052</v>
       </c>
       <c r="R55" t="n">
-        <v>7171568</v>
+        <v>7171679</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6713,6 +6699,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6740,10 +6731,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123107511</v>
+        <v>123105541</v>
       </c>
       <c r="B56" t="n">
-        <v>78790</v>
+        <v>78793</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6787,10 +6778,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811066</v>
+        <v>810786</v>
       </c>
       <c r="R56" t="n">
-        <v>7171715</v>
+        <v>7171568</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6850,10 +6841,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123107580</v>
+        <v>123105488</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6897,10 +6888,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810886</v>
+        <v>810824</v>
       </c>
       <c r="R57" t="n">
-        <v>7171705</v>
+        <v>7171598</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6933,6 +6924,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6960,10 +6956,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123105488</v>
+        <v>123107580</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7007,10 +7003,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810824</v>
+        <v>810886</v>
       </c>
       <c r="R58" t="n">
-        <v>7171598</v>
+        <v>7171705</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7043,11 +7039,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7075,10 +7066,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123113317</v>
+        <v>123107351</v>
       </c>
       <c r="B59" t="n">
-        <v>57494</v>
+        <v>78769</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7091,29 +7082,32 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7123,10 +7117,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>810707</v>
+        <v>811003</v>
       </c>
       <c r="R59" t="n">
-        <v>7171592</v>
+        <v>7171721</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7163,7 +7157,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>hål i gammal sälg</t>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7172,6 +7166,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7190,10 +7185,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123113295</v>
+        <v>123113317</v>
       </c>
       <c r="B60" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7238,10 +7233,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810851</v>
+        <v>810707</v>
       </c>
       <c r="R60" t="n">
-        <v>7171663</v>
+        <v>7171592</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7278,7 +7273,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>hål i gammal sälg</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7305,10 +7300,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123107538</v>
+        <v>123107459</v>
       </c>
       <c r="B61" t="n">
-        <v>78790</v>
+        <v>57481</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7317,34 +7312,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7352,10 +7348,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>810978</v>
+        <v>811055</v>
       </c>
       <c r="R61" t="n">
-        <v>7171744</v>
+        <v>7171672</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7390,13 +7386,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7415,10 +7415,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123107271</v>
+        <v>123107409</v>
       </c>
       <c r="B62" t="n">
-        <v>57494</v>
+        <v>57481</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7431,16 +7431,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7453,7 +7453,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>810992</v>
+        <v>811024</v>
       </c>
       <c r="R62" t="n">
-        <v>7171739</v>
+        <v>7171733</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -3030,7 +3030,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123104657</v>
+        <v>123104604</v>
       </c>
       <c r="B23" t="n">
         <v>57497</v>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>810447</v>
+        <v>810442</v>
       </c>
       <c r="R23" t="n">
-        <v>7171526</v>
+        <v>7171450</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3145,7 +3145,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123104604</v>
+        <v>123104657</v>
       </c>
       <c r="B24" t="n">
         <v>57497</v>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>810442</v>
+        <v>810447</v>
       </c>
       <c r="R24" t="n">
-        <v>7171450</v>
+        <v>7171526</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5046,10 +5046,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123107500</v>
+        <v>123105448</v>
       </c>
       <c r="B41" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5085,7 +5085,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5093,10 +5097,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811043</v>
+        <v>810833</v>
       </c>
       <c r="R41" t="n">
-        <v>7171704</v>
+        <v>7171608</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5129,6 +5133,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5156,10 +5165,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123113132</v>
+        <v>123107487</v>
       </c>
       <c r="B42" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5172,31 +5181,30 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5204,10 +5212,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810895</v>
+        <v>811052</v>
       </c>
       <c r="R42" t="n">
-        <v>7171694</v>
+        <v>7171679</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5244,7 +5252,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5253,6 +5261,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5271,7 +5280,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123113295</v>
+        <v>123113317</v>
       </c>
       <c r="B43" t="n">
         <v>57497</v>
@@ -5319,10 +5328,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810851</v>
+        <v>810707</v>
       </c>
       <c r="R43" t="n">
-        <v>7171663</v>
+        <v>7171592</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5359,7 +5368,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>hål i gammal sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5386,10 +5395,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123107426</v>
+        <v>123107589</v>
       </c>
       <c r="B44" t="n">
-        <v>57497</v>
+        <v>82558</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5402,27 +5411,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5430,10 +5442,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811024</v>
+        <v>810886</v>
       </c>
       <c r="R44" t="n">
-        <v>7171733</v>
+        <v>7171705</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5468,17 +5480,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5497,10 +5505,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123107538</v>
+        <v>123105541</v>
       </c>
       <c r="B45" t="n">
-        <v>78793</v>
+        <v>78795</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5544,10 +5552,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>810978</v>
+        <v>810786</v>
       </c>
       <c r="R45" t="n">
-        <v>7171744</v>
+        <v>7171568</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5607,10 +5615,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123107525</v>
+        <v>123107511</v>
       </c>
       <c r="B46" t="n">
-        <v>78793</v>
+        <v>78795</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5654,10 +5662,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811018</v>
+        <v>811066</v>
       </c>
       <c r="R46" t="n">
-        <v>7171753</v>
+        <v>7171715</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5717,10 +5725,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123113174</v>
+        <v>123107500</v>
       </c>
       <c r="B47" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5764,10 +5772,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810865</v>
+        <v>811043</v>
       </c>
       <c r="R47" t="n">
-        <v>7171668</v>
+        <v>7171704</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5800,11 +5808,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5832,7 +5835,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123107271</v>
+        <v>123107426</v>
       </c>
       <c r="B48" t="n">
         <v>57497</v>
@@ -5868,11 +5871,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5880,10 +5879,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>810992</v>
+        <v>811024</v>
       </c>
       <c r="R48" t="n">
-        <v>7171739</v>
+        <v>7171733</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5920,7 +5919,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5947,10 +5946,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123113205</v>
+        <v>123113295</v>
       </c>
       <c r="B49" t="n">
-        <v>78801</v>
+        <v>57497</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5963,30 +5962,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>810862</v>
+        <v>810851</v>
       </c>
       <c r="R49" t="n">
-        <v>7171664</v>
+        <v>7171663</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6032,13 +6032,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6057,10 +6061,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123113230</v>
+        <v>123107525</v>
       </c>
       <c r="B50" t="n">
-        <v>78769</v>
+        <v>78795</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6069,25 +6073,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6104,10 +6108,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>810850</v>
+        <v>811018</v>
       </c>
       <c r="R50" t="n">
-        <v>7171671</v>
+        <v>7171753</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6167,10 +6171,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123105526</v>
+        <v>123107459</v>
       </c>
       <c r="B51" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6183,30 +6187,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6214,10 +6219,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>810798</v>
+        <v>811055</v>
       </c>
       <c r="R51" t="n">
-        <v>7171573</v>
+        <v>7171672</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6252,13 +6257,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6277,10 +6286,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123105448</v>
+        <v>123113132</v>
       </c>
       <c r="B52" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6293,32 +6302,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6328,10 +6334,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810833</v>
+        <v>810895</v>
       </c>
       <c r="R52" t="n">
-        <v>7171608</v>
+        <v>7171694</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6368,7 +6374,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>rikligt med fertil garnlav på gammal död gran</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6377,7 +6383,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6396,10 +6401,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123107589</v>
+        <v>123105488</v>
       </c>
       <c r="B53" t="n">
-        <v>82556</v>
+        <v>78771</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6412,27 +6417,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -6443,10 +6448,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810886</v>
+        <v>810824</v>
       </c>
       <c r="R53" t="n">
-        <v>7171705</v>
+        <v>7171598</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6479,6 +6484,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6506,10 +6516,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123107511</v>
+        <v>123105526</v>
       </c>
       <c r="B54" t="n">
-        <v>78793</v>
+        <v>78771</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6518,25 +6528,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6553,10 +6563,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811066</v>
+        <v>810798</v>
       </c>
       <c r="R54" t="n">
-        <v>7171715</v>
+        <v>7171573</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6616,10 +6626,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123107487</v>
+        <v>123113230</v>
       </c>
       <c r="B55" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6663,10 +6673,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811052</v>
+        <v>810850</v>
       </c>
       <c r="R55" t="n">
-        <v>7171679</v>
+        <v>7171671</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6699,11 +6709,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6731,10 +6736,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123105541</v>
+        <v>123107538</v>
       </c>
       <c r="B56" t="n">
-        <v>78793</v>
+        <v>78795</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6778,10 +6783,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810786</v>
+        <v>810978</v>
       </c>
       <c r="R56" t="n">
-        <v>7171568</v>
+        <v>7171744</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6841,10 +6846,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123105488</v>
+        <v>123107580</v>
       </c>
       <c r="B57" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6888,10 +6893,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810824</v>
+        <v>810886</v>
       </c>
       <c r="R57" t="n">
-        <v>7171598</v>
+        <v>7171705</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6924,11 +6929,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6956,10 +6956,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123107580</v>
+        <v>123107271</v>
       </c>
       <c r="B58" t="n">
-        <v>78769</v>
+        <v>57497</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6972,30 +6972,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7003,10 +7004,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810886</v>
+        <v>810992</v>
       </c>
       <c r="R58" t="n">
-        <v>7171705</v>
+        <v>7171739</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7041,13 +7042,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7066,10 +7071,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123107351</v>
+        <v>123113205</v>
       </c>
       <c r="B59" t="n">
-        <v>78769</v>
+        <v>78803</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7082,21 +7087,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7105,11 +7110,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7117,10 +7118,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811003</v>
+        <v>810862</v>
       </c>
       <c r="R59" t="n">
-        <v>7171721</v>
+        <v>7171664</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7153,11 +7154,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7185,10 +7181,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123113317</v>
+        <v>123113174</v>
       </c>
       <c r="B60" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7201,31 +7197,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7233,10 +7228,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810707</v>
+        <v>810865</v>
       </c>
       <c r="R60" t="n">
-        <v>7171592</v>
+        <v>7171668</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7273,7 +7268,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>hål i gammal sälg</t>
+          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7282,6 +7277,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7300,7 +7296,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123107459</v>
+        <v>123107409</v>
       </c>
       <c r="B61" t="n">
         <v>57481</v>
@@ -7348,10 +7344,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811055</v>
+        <v>811024</v>
       </c>
       <c r="R61" t="n">
-        <v>7171672</v>
+        <v>7171733</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7388,7 +7384,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7415,10 +7411,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123107409</v>
+        <v>123107351</v>
       </c>
       <c r="B62" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7431,29 +7427,32 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7463,10 +7462,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811024</v>
+        <v>811003</v>
       </c>
       <c r="R62" t="n">
-        <v>7171733</v>
+        <v>7171721</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7503,7 +7502,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7512,6 +7511,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -3030,7 +3030,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123104604</v>
+        <v>123104657</v>
       </c>
       <c r="B23" t="n">
         <v>57497</v>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>810442</v>
+        <v>810447</v>
       </c>
       <c r="R23" t="n">
-        <v>7171450</v>
+        <v>7171526</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3145,7 +3145,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123104657</v>
+        <v>123104604</v>
       </c>
       <c r="B24" t="n">
         <v>57497</v>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>810447</v>
+        <v>810442</v>
       </c>
       <c r="R24" t="n">
-        <v>7171526</v>
+        <v>7171450</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5046,10 +5046,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123105448</v>
+        <v>123107525</v>
       </c>
       <c r="B41" t="n">
-        <v>78771</v>
+        <v>78796</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5058,25 +5058,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5085,11 +5085,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5097,10 +5093,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>810833</v>
+        <v>811018</v>
       </c>
       <c r="R41" t="n">
-        <v>7171608</v>
+        <v>7171753</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5133,11 +5129,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5165,10 +5156,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123107487</v>
+        <v>123113317</v>
       </c>
       <c r="B42" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5181,30 +5172,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5212,10 +5204,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811052</v>
+        <v>810707</v>
       </c>
       <c r="R42" t="n">
-        <v>7171679</v>
+        <v>7171592</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5252,7 +5244,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>rikligt med hänglavar bla garnlav</t>
+          <t>hål i gammal sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5261,7 +5253,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5280,10 +5271,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123113317</v>
+        <v>123105541</v>
       </c>
       <c r="B43" t="n">
-        <v>57497</v>
+        <v>78796</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5292,35 +5283,34 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5328,10 +5318,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810707</v>
+        <v>810786</v>
       </c>
       <c r="R43" t="n">
-        <v>7171592</v>
+        <v>7171568</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5366,17 +5356,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>hål i gammal sälg</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5395,10 +5381,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123107589</v>
+        <v>123113230</v>
       </c>
       <c r="B44" t="n">
-        <v>82558</v>
+        <v>78772</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5411,27 +5397,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -5442,10 +5428,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>810886</v>
+        <v>810850</v>
       </c>
       <c r="R44" t="n">
-        <v>7171705</v>
+        <v>7171671</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5505,10 +5491,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123105541</v>
+        <v>123107426</v>
       </c>
       <c r="B45" t="n">
-        <v>78795</v>
+        <v>57497</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5517,34 +5503,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5552,10 +5535,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>810786</v>
+        <v>811024</v>
       </c>
       <c r="R45" t="n">
-        <v>7171568</v>
+        <v>7171733</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5590,13 +5573,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5615,10 +5602,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123107511</v>
+        <v>123107500</v>
       </c>
       <c r="B46" t="n">
-        <v>78795</v>
+        <v>78772</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5627,25 +5614,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5662,10 +5649,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811066</v>
+        <v>811043</v>
       </c>
       <c r="R46" t="n">
-        <v>7171715</v>
+        <v>7171704</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5725,10 +5712,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123107500</v>
+        <v>123107459</v>
       </c>
       <c r="B47" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5741,30 +5728,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5772,10 +5760,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811043</v>
+        <v>811055</v>
       </c>
       <c r="R47" t="n">
-        <v>7171704</v>
+        <v>7171672</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5810,13 +5798,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5835,10 +5827,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123107426</v>
+        <v>123107589</v>
       </c>
       <c r="B48" t="n">
-        <v>57497</v>
+        <v>82559</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5851,27 +5843,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5879,10 +5874,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811024</v>
+        <v>810886</v>
       </c>
       <c r="R48" t="n">
-        <v>7171733</v>
+        <v>7171705</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5917,17 +5912,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5946,10 +5937,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123113295</v>
+        <v>123107351</v>
       </c>
       <c r="B49" t="n">
-        <v>57497</v>
+        <v>78772</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5962,29 +5953,32 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5994,10 +5988,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>810851</v>
+        <v>811003</v>
       </c>
       <c r="R49" t="n">
-        <v>7171663</v>
+        <v>7171721</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6034,7 +6028,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6043,6 +6037,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6061,10 +6056,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123107525</v>
+        <v>123113295</v>
       </c>
       <c r="B50" t="n">
-        <v>78795</v>
+        <v>57497</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6073,34 +6068,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6108,10 +6104,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811018</v>
+        <v>810851</v>
       </c>
       <c r="R50" t="n">
-        <v>7171753</v>
+        <v>7171663</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6146,13 +6142,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6171,10 +6171,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123107459</v>
+        <v>123105526</v>
       </c>
       <c r="B51" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6187,31 +6187,30 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6219,10 +6218,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811055</v>
+        <v>810798</v>
       </c>
       <c r="R51" t="n">
-        <v>7171672</v>
+        <v>7171573</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6257,17 +6256,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6286,10 +6281,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123113132</v>
+        <v>123113174</v>
       </c>
       <c r="B52" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6302,31 +6297,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6334,10 +6328,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810895</v>
+        <v>810865</v>
       </c>
       <c r="R52" t="n">
-        <v>7171694</v>
+        <v>7171668</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6374,7 +6368,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6383,6 +6377,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6401,10 +6396,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123105488</v>
+        <v>123107271</v>
       </c>
       <c r="B53" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6417,30 +6412,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6448,10 +6444,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810824</v>
+        <v>810992</v>
       </c>
       <c r="R53" t="n">
-        <v>7171598</v>
+        <v>7171739</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6488,7 +6484,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>över 0,5 meter lång bål</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6497,7 +6493,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6516,10 +6511,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123105526</v>
+        <v>123107487</v>
       </c>
       <c r="B54" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6563,10 +6558,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810798</v>
+        <v>811052</v>
       </c>
       <c r="R54" t="n">
-        <v>7171573</v>
+        <v>7171679</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6599,6 +6594,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6626,10 +6626,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123113230</v>
+        <v>123107580</v>
       </c>
       <c r="B55" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810850</v>
+        <v>810886</v>
       </c>
       <c r="R55" t="n">
-        <v>7171671</v>
+        <v>7171705</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6736,10 +6736,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123107538</v>
+        <v>123113132</v>
       </c>
       <c r="B56" t="n">
-        <v>78795</v>
+        <v>57481</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6748,34 +6748,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6783,10 +6784,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810978</v>
+        <v>810895</v>
       </c>
       <c r="R56" t="n">
-        <v>7171744</v>
+        <v>7171694</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6821,13 +6822,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6846,10 +6851,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123107580</v>
+        <v>123107538</v>
       </c>
       <c r="B57" t="n">
-        <v>78771</v>
+        <v>78796</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6858,25 +6863,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6893,10 +6898,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810886</v>
+        <v>810978</v>
       </c>
       <c r="R57" t="n">
-        <v>7171705</v>
+        <v>7171744</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6956,10 +6961,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123107271</v>
+        <v>123105488</v>
       </c>
       <c r="B58" t="n">
-        <v>57497</v>
+        <v>78772</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6972,31 +6977,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7004,10 +7008,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810992</v>
+        <v>810824</v>
       </c>
       <c r="R58" t="n">
-        <v>7171739</v>
+        <v>7171598</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7044,7 +7048,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7053,6 +7057,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7074,7 +7079,7 @@
         <v>123113205</v>
       </c>
       <c r="B59" t="n">
-        <v>78803</v>
+        <v>78804</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7181,10 +7186,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123113174</v>
+        <v>123107409</v>
       </c>
       <c r="B60" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7197,30 +7202,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7228,10 +7234,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810865</v>
+        <v>811024</v>
       </c>
       <c r="R60" t="n">
-        <v>7171668</v>
+        <v>7171733</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7268,7 +7274,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>hänglavrikt bla garnlav</t>
+          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7277,7 +7283,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7296,10 +7301,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123107409</v>
+        <v>123107511</v>
       </c>
       <c r="B61" t="n">
-        <v>57481</v>
+        <v>78796</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7308,35 +7313,34 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7344,10 +7348,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811024</v>
+        <v>811066</v>
       </c>
       <c r="R61" t="n">
-        <v>7171733</v>
+        <v>7171715</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7382,17 +7386,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7411,10 +7411,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123107351</v>
+        <v>123105448</v>
       </c>
       <c r="B62" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7462,10 +7462,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811003</v>
+        <v>810833</v>
       </c>
       <c r="R62" t="n">
-        <v>7171721</v>
+        <v>7171608</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>fertil garnlav</t>
+          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -3030,7 +3030,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123104657</v>
+        <v>123104604</v>
       </c>
       <c r="B23" t="n">
         <v>57497</v>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>810447</v>
+        <v>810442</v>
       </c>
       <c r="R23" t="n">
-        <v>7171526</v>
+        <v>7171450</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3145,7 +3145,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123104604</v>
+        <v>123104657</v>
       </c>
       <c r="B24" t="n">
         <v>57497</v>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>810442</v>
+        <v>810447</v>
       </c>
       <c r="R24" t="n">
-        <v>7171450</v>
+        <v>7171526</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5046,10 +5046,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123107525</v>
+        <v>123113230</v>
       </c>
       <c r="B41" t="n">
-        <v>78796</v>
+        <v>78775</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5058,25 +5058,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811018</v>
+        <v>810850</v>
       </c>
       <c r="R41" t="n">
-        <v>7171753</v>
+        <v>7171671</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5156,7 +5156,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123113317</v>
+        <v>123107271</v>
       </c>
       <c r="B42" t="n">
         <v>57497</v>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810707</v>
+        <v>810992</v>
       </c>
       <c r="R42" t="n">
-        <v>7171592</v>
+        <v>7171739</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>hål i gammal sälg</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5271,10 +5271,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123105541</v>
+        <v>123107580</v>
       </c>
       <c r="B43" t="n">
-        <v>78796</v>
+        <v>78775</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5283,25 +5283,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810786</v>
+        <v>810886</v>
       </c>
       <c r="R43" t="n">
-        <v>7171568</v>
+        <v>7171705</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123113230</v>
+        <v>123107409</v>
       </c>
       <c r="B44" t="n">
-        <v>78772</v>
+        <v>57481</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5397,30 +5397,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5428,10 +5429,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>810850</v>
+        <v>811024</v>
       </c>
       <c r="R44" t="n">
-        <v>7171671</v>
+        <v>7171733</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5466,13 +5467,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5491,10 +5496,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123107426</v>
+        <v>123107538</v>
       </c>
       <c r="B45" t="n">
-        <v>57497</v>
+        <v>78799</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5503,31 +5508,34 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5535,10 +5543,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811024</v>
+        <v>810978</v>
       </c>
       <c r="R45" t="n">
-        <v>7171733</v>
+        <v>7171744</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5573,17 +5581,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5602,10 +5606,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123107500</v>
+        <v>123113174</v>
       </c>
       <c r="B46" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5649,10 +5653,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811043</v>
+        <v>810865</v>
       </c>
       <c r="R46" t="n">
-        <v>7171704</v>
+        <v>7171668</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5685,6 +5689,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5712,10 +5721,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123107459</v>
+        <v>123105448</v>
       </c>
       <c r="B47" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5728,29 +5737,32 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5760,10 +5772,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811055</v>
+        <v>810833</v>
       </c>
       <c r="R47" t="n">
-        <v>7171672</v>
+        <v>7171608</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5800,7 +5812,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5809,6 +5821,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5827,10 +5840,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123107589</v>
+        <v>123107487</v>
       </c>
       <c r="B48" t="n">
-        <v>82559</v>
+        <v>78775</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5843,27 +5856,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -5874,10 +5887,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>810886</v>
+        <v>811052</v>
       </c>
       <c r="R48" t="n">
-        <v>7171705</v>
+        <v>7171679</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5910,6 +5923,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5937,10 +5955,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123107351</v>
+        <v>123113205</v>
       </c>
       <c r="B49" t="n">
-        <v>78772</v>
+        <v>78807</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5953,21 +5971,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5976,11 +5994,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5988,10 +6002,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811003</v>
+        <v>810862</v>
       </c>
       <c r="R49" t="n">
-        <v>7171721</v>
+        <v>7171664</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6024,11 +6038,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6056,10 +6065,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123113295</v>
+        <v>123107511</v>
       </c>
       <c r="B50" t="n">
-        <v>57497</v>
+        <v>78799</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6068,35 +6077,34 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6104,10 +6112,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>810851</v>
+        <v>811066</v>
       </c>
       <c r="R50" t="n">
-        <v>7171663</v>
+        <v>7171715</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6142,17 +6150,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>hack i död ved</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6171,10 +6175,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123105526</v>
+        <v>123113295</v>
       </c>
       <c r="B51" t="n">
-        <v>78772</v>
+        <v>57497</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6187,30 +6191,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6218,10 +6223,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>810798</v>
+        <v>810851</v>
       </c>
       <c r="R51" t="n">
-        <v>7171573</v>
+        <v>7171663</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6256,13 +6261,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6281,10 +6290,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123113174</v>
+        <v>123107351</v>
       </c>
       <c r="B52" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6320,7 +6329,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6328,10 +6341,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810865</v>
+        <v>811003</v>
       </c>
       <c r="R52" t="n">
-        <v>7171668</v>
+        <v>7171721</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6368,7 +6381,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>hänglavrikt bla garnlav</t>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6396,10 +6409,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123107271</v>
+        <v>123105541</v>
       </c>
       <c r="B53" t="n">
-        <v>57497</v>
+        <v>78799</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6408,35 +6421,34 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6444,10 +6456,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810992</v>
+        <v>810786</v>
       </c>
       <c r="R53" t="n">
-        <v>7171739</v>
+        <v>7171568</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6482,17 +6494,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>hack i död ved</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6511,10 +6519,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123107487</v>
+        <v>123107525</v>
       </c>
       <c r="B54" t="n">
-        <v>78772</v>
+        <v>78799</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6523,25 +6531,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6558,10 +6566,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811052</v>
+        <v>811018</v>
       </c>
       <c r="R54" t="n">
-        <v>7171679</v>
+        <v>7171753</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6594,11 +6602,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6626,10 +6629,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123107580</v>
+        <v>123107459</v>
       </c>
       <c r="B55" t="n">
-        <v>78772</v>
+        <v>57481</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6642,30 +6645,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6673,10 +6677,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810886</v>
+        <v>811055</v>
       </c>
       <c r="R55" t="n">
-        <v>7171705</v>
+        <v>7171672</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6711,13 +6715,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6736,10 +6744,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123113132</v>
+        <v>123113317</v>
       </c>
       <c r="B56" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6752,16 +6760,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6774,7 +6782,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6784,10 +6792,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810895</v>
+        <v>810707</v>
       </c>
       <c r="R56" t="n">
-        <v>7171694</v>
+        <v>7171592</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6824,7 +6832,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>hål i gammal sälg</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6851,10 +6859,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123107538</v>
+        <v>123107500</v>
       </c>
       <c r="B57" t="n">
-        <v>78796</v>
+        <v>78775</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6863,25 +6871,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6898,10 +6906,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810978</v>
+        <v>811043</v>
       </c>
       <c r="R57" t="n">
-        <v>7171744</v>
+        <v>7171704</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6961,10 +6969,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123105488</v>
+        <v>123113132</v>
       </c>
       <c r="B58" t="n">
-        <v>78772</v>
+        <v>57481</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6977,30 +6985,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7008,10 +7017,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810824</v>
+        <v>810895</v>
       </c>
       <c r="R58" t="n">
-        <v>7171598</v>
+        <v>7171694</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7048,7 +7057,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>över 0,5 meter lång bål</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7057,7 +7066,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7076,10 +7084,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123113205</v>
+        <v>123105488</v>
       </c>
       <c r="B59" t="n">
-        <v>78804</v>
+        <v>78775</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7092,21 +7100,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7123,10 +7131,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>810862</v>
+        <v>810824</v>
       </c>
       <c r="R59" t="n">
-        <v>7171664</v>
+        <v>7171598</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7159,6 +7167,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7186,10 +7199,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123107409</v>
+        <v>123105526</v>
       </c>
       <c r="B60" t="n">
-        <v>57481</v>
+        <v>78775</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7202,31 +7215,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7234,10 +7246,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811024</v>
+        <v>810798</v>
       </c>
       <c r="R60" t="n">
-        <v>7171733</v>
+        <v>7171573</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7272,17 +7284,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7301,10 +7309,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123107511</v>
+        <v>123107589</v>
       </c>
       <c r="B61" t="n">
-        <v>78796</v>
+        <v>82562</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7313,31 +7321,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6434</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -7348,10 +7356,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811066</v>
+        <v>810886</v>
       </c>
       <c r="R61" t="n">
-        <v>7171715</v>
+        <v>7171705</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7411,10 +7419,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123105448</v>
+        <v>123107426</v>
       </c>
       <c r="B62" t="n">
-        <v>78772</v>
+        <v>57497</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7427,34 +7435,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7462,10 +7463,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>810833</v>
+        <v>811024</v>
       </c>
       <c r="R62" t="n">
-        <v>7171608</v>
+        <v>7171733</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7502,7 +7503,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>rikligt med fertil garnlav på gammal död gran</t>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7511,7 +7512,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -5840,10 +5840,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123113205</v>
+        <v>123107487</v>
       </c>
       <c r="B48" t="n">
-        <v>78807</v>
+        <v>78775</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5856,21 +5856,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>810862</v>
+        <v>811052</v>
       </c>
       <c r="R48" t="n">
-        <v>7171664</v>
+        <v>7171679</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5923,6 +5923,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5950,10 +5955,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123107487</v>
+        <v>123113205</v>
       </c>
       <c r="B49" t="n">
-        <v>78775</v>
+        <v>78807</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5966,21 +5971,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5997,10 +6002,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811052</v>
+        <v>810862</v>
       </c>
       <c r="R49" t="n">
-        <v>7171679</v>
+        <v>7171664</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6033,11 +6038,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6409,10 +6409,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123107459</v>
+        <v>123105541</v>
       </c>
       <c r="B53" t="n">
-        <v>57481</v>
+        <v>78799</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6421,35 +6421,34 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6457,10 +6456,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811055</v>
+        <v>810786</v>
       </c>
       <c r="R53" t="n">
-        <v>7171672</v>
+        <v>7171568</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6495,17 +6494,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6524,7 +6519,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123105541</v>
+        <v>123107525</v>
       </c>
       <c r="B54" t="n">
         <v>78799</v>
@@ -6571,10 +6566,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810786</v>
+        <v>811018</v>
       </c>
       <c r="R54" t="n">
-        <v>7171568</v>
+        <v>7171753</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6634,10 +6629,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123107525</v>
+        <v>123107459</v>
       </c>
       <c r="B55" t="n">
-        <v>78799</v>
+        <v>57481</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6646,34 +6641,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6681,10 +6677,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811018</v>
+        <v>811055</v>
       </c>
       <c r="R55" t="n">
-        <v>7171753</v>
+        <v>7171672</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6719,13 +6715,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123104581</v>
+        <v>123104657</v>
       </c>
       <c r="B22" t="n">
-        <v>57481</v>
+        <v>57503</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,16 +2931,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>810444</v>
+        <v>810447</v>
       </c>
       <c r="R22" t="n">
-        <v>7171466</v>
+        <v>7171526</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3033,7 +3033,7 @@
         <v>123104604</v>
       </c>
       <c r="B23" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3145,10 +3145,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123104657</v>
+        <v>123104581</v>
       </c>
       <c r="B24" t="n">
-        <v>57497</v>
+        <v>57487</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,16 +3161,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>810447</v>
+        <v>810444</v>
       </c>
       <c r="R24" t="n">
-        <v>7171526</v>
+        <v>7171466</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5046,10 +5046,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123113230</v>
+        <v>123107589</v>
       </c>
       <c r="B41" t="n">
-        <v>78775</v>
+        <v>82568</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5062,27 +5062,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>810850</v>
+        <v>810886</v>
       </c>
       <c r="R41" t="n">
-        <v>7171671</v>
+        <v>7171705</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5156,10 +5156,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123107271</v>
+        <v>123105448</v>
       </c>
       <c r="B42" t="n">
-        <v>57497</v>
+        <v>78781</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5172,29 +5172,32 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5204,10 +5207,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810992</v>
+        <v>810833</v>
       </c>
       <c r="R42" t="n">
-        <v>7171739</v>
+        <v>7171608</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5244,7 +5247,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5253,6 +5256,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5271,10 +5275,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123107580</v>
+        <v>123113230</v>
       </c>
       <c r="B43" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5318,10 +5322,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810886</v>
+        <v>810850</v>
       </c>
       <c r="R43" t="n">
-        <v>7171705</v>
+        <v>7171671</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5381,10 +5385,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123107409</v>
+        <v>123113295</v>
       </c>
       <c r="B44" t="n">
-        <v>57481</v>
+        <v>57503</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5397,16 +5401,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5419,7 +5423,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5429,10 +5433,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811024</v>
+        <v>810851</v>
       </c>
       <c r="R44" t="n">
-        <v>7171733</v>
+        <v>7171663</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5469,7 +5473,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5496,10 +5500,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123107538</v>
+        <v>123107409</v>
       </c>
       <c r="B45" t="n">
-        <v>78799</v>
+        <v>57487</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5508,34 +5512,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5543,10 +5548,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>810978</v>
+        <v>811024</v>
       </c>
       <c r="R45" t="n">
-        <v>7171744</v>
+        <v>7171733</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5581,13 +5586,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5606,10 +5615,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123113174</v>
+        <v>123107525</v>
       </c>
       <c r="B46" t="n">
-        <v>78775</v>
+        <v>78805</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5618,25 +5627,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5653,10 +5662,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>810865</v>
+        <v>811018</v>
       </c>
       <c r="R46" t="n">
-        <v>7171668</v>
+        <v>7171753</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5689,11 +5698,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5721,10 +5725,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123105448</v>
+        <v>123113205</v>
       </c>
       <c r="B47" t="n">
-        <v>78775</v>
+        <v>78813</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5737,21 +5741,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5760,11 +5764,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810833</v>
+        <v>810862</v>
       </c>
       <c r="R47" t="n">
-        <v>7171608</v>
+        <v>7171664</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5808,11 +5808,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5840,10 +5835,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123107487</v>
+        <v>123107511</v>
       </c>
       <c r="B48" t="n">
-        <v>78775</v>
+        <v>78805</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5852,25 +5847,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5887,10 +5882,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811052</v>
+        <v>811066</v>
       </c>
       <c r="R48" t="n">
-        <v>7171679</v>
+        <v>7171715</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5923,11 +5918,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5955,10 +5945,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123113205</v>
+        <v>123105526</v>
       </c>
       <c r="B49" t="n">
-        <v>78807</v>
+        <v>78781</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5971,21 +5961,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6002,10 +5992,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>810862</v>
+        <v>810798</v>
       </c>
       <c r="R49" t="n">
-        <v>7171664</v>
+        <v>7171573</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6065,10 +6055,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123107511</v>
+        <v>123107271</v>
       </c>
       <c r="B50" t="n">
-        <v>78799</v>
+        <v>57503</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6077,34 +6067,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6112,10 +6103,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811066</v>
+        <v>810992</v>
       </c>
       <c r="R50" t="n">
-        <v>7171715</v>
+        <v>7171739</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6150,13 +6141,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6175,10 +6170,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123113295</v>
+        <v>123105488</v>
       </c>
       <c r="B51" t="n">
-        <v>57497</v>
+        <v>78781</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6191,31 +6186,30 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6223,10 +6217,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>810851</v>
+        <v>810824</v>
       </c>
       <c r="R51" t="n">
-        <v>7171663</v>
+        <v>7171598</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6263,7 +6257,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6272,6 +6266,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6290,10 +6285,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123107351</v>
+        <v>123113317</v>
       </c>
       <c r="B52" t="n">
-        <v>78775</v>
+        <v>57503</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6306,32 +6301,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6341,10 +6333,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811003</v>
+        <v>810707</v>
       </c>
       <c r="R52" t="n">
-        <v>7171721</v>
+        <v>7171592</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6381,7 +6373,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>fertil garnlav</t>
+          <t>hål i gammal sälg</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6390,7 +6382,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6412,7 +6403,7 @@
         <v>123105541</v>
       </c>
       <c r="B53" t="n">
-        <v>78799</v>
+        <v>78805</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6519,10 +6510,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123107525</v>
+        <v>123107351</v>
       </c>
       <c r="B54" t="n">
-        <v>78799</v>
+        <v>78781</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6531,25 +6522,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6558,7 +6549,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6566,10 +6561,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811018</v>
+        <v>811003</v>
       </c>
       <c r="R54" t="n">
-        <v>7171753</v>
+        <v>7171721</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6602,6 +6597,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6629,10 +6629,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123107459</v>
+        <v>123107580</v>
       </c>
       <c r="B55" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6645,31 +6645,30 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6677,10 +6676,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811055</v>
+        <v>810886</v>
       </c>
       <c r="R55" t="n">
-        <v>7171672</v>
+        <v>7171705</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6715,17 +6714,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6744,10 +6739,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123113317</v>
+        <v>123107487</v>
       </c>
       <c r="B56" t="n">
-        <v>57497</v>
+        <v>78781</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6760,31 +6755,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6792,10 +6786,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810707</v>
+        <v>811052</v>
       </c>
       <c r="R56" t="n">
-        <v>7171592</v>
+        <v>7171679</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6832,7 +6826,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>hål i gammal sälg</t>
+          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6841,6 +6835,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6859,10 +6854,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123107500</v>
+        <v>123113174</v>
       </c>
       <c r="B57" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6906,10 +6901,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811043</v>
+        <v>810865</v>
       </c>
       <c r="R57" t="n">
-        <v>7171704</v>
+        <v>7171668</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6942,6 +6937,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6969,10 +6969,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123105488</v>
+        <v>123107538</v>
       </c>
       <c r="B58" t="n">
-        <v>78775</v>
+        <v>78805</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6981,25 +6981,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7016,10 +7016,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810824</v>
+        <v>810978</v>
       </c>
       <c r="R58" t="n">
-        <v>7171598</v>
+        <v>7171744</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7052,11 +7052,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7084,10 +7079,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123113132</v>
+        <v>123107500</v>
       </c>
       <c r="B59" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7100,31 +7095,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7132,10 +7126,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>810895</v>
+        <v>811043</v>
       </c>
       <c r="R59" t="n">
-        <v>7171694</v>
+        <v>7171704</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7170,17 +7164,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7199,10 +7189,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123105526</v>
+        <v>123107426</v>
       </c>
       <c r="B60" t="n">
-        <v>78775</v>
+        <v>57503</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7215,30 +7205,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7246,10 +7233,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810798</v>
+        <v>811024</v>
       </c>
       <c r="R60" t="n">
-        <v>7171573</v>
+        <v>7171733</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7284,13 +7271,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7309,10 +7300,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123107589</v>
+        <v>123107459</v>
       </c>
       <c r="B61" t="n">
-        <v>82562</v>
+        <v>57487</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7325,30 +7316,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7356,10 +7348,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>810886</v>
+        <v>811055</v>
       </c>
       <c r="R61" t="n">
-        <v>7171705</v>
+        <v>7171672</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7394,13 +7386,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7419,10 +7415,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123107426</v>
+        <v>123113132</v>
       </c>
       <c r="B62" t="n">
-        <v>57497</v>
+        <v>57487</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7435,16 +7431,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7455,7 +7451,11 @@
       <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7463,10 +7463,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811024</v>
+        <v>810895</v>
       </c>
       <c r="R62" t="n">
-        <v>7171733</v>
+        <v>7171694</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -5725,10 +5725,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123113205</v>
+        <v>123107271</v>
       </c>
       <c r="B47" t="n">
-        <v>78813</v>
+        <v>57503</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5741,30 +5741,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5772,10 +5773,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810862</v>
+        <v>810992</v>
       </c>
       <c r="R47" t="n">
-        <v>7171664</v>
+        <v>7171739</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5810,13 +5811,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5835,10 +5840,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123107511</v>
+        <v>123113205</v>
       </c>
       <c r="B48" t="n">
-        <v>78805</v>
+        <v>78813</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5847,25 +5852,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6434</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5882,10 +5887,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811066</v>
+        <v>810862</v>
       </c>
       <c r="R48" t="n">
-        <v>7171715</v>
+        <v>7171664</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5945,10 +5950,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123105526</v>
+        <v>123107511</v>
       </c>
       <c r="B49" t="n">
-        <v>78781</v>
+        <v>78805</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5957,25 +5962,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5992,10 +5997,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>810798</v>
+        <v>811066</v>
       </c>
       <c r="R49" t="n">
-        <v>7171573</v>
+        <v>7171715</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6055,10 +6060,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123107271</v>
+        <v>123105526</v>
       </c>
       <c r="B50" t="n">
-        <v>57503</v>
+        <v>78781</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6071,31 +6076,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6103,10 +6107,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>810992</v>
+        <v>810798</v>
       </c>
       <c r="R50" t="n">
-        <v>7171739</v>
+        <v>7171573</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6141,17 +6145,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>hack i död ved</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -5725,10 +5725,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123107271</v>
+        <v>123113205</v>
       </c>
       <c r="B47" t="n">
-        <v>57503</v>
+        <v>78813</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5741,31 +5741,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5773,10 +5772,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810992</v>
+        <v>810862</v>
       </c>
       <c r="R47" t="n">
-        <v>7171739</v>
+        <v>7171664</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5811,17 +5810,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>hack i död ved</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5840,10 +5835,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123113205</v>
+        <v>123107511</v>
       </c>
       <c r="B48" t="n">
-        <v>78813</v>
+        <v>78805</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5852,25 +5847,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5887,10 +5882,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>810862</v>
+        <v>811066</v>
       </c>
       <c r="R48" t="n">
-        <v>7171664</v>
+        <v>7171715</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5950,10 +5945,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123107511</v>
+        <v>123105526</v>
       </c>
       <c r="B49" t="n">
-        <v>78805</v>
+        <v>78781</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5962,25 +5957,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5997,10 +5992,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811066</v>
+        <v>810798</v>
       </c>
       <c r="R49" t="n">
-        <v>7171715</v>
+        <v>7171573</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6060,10 +6055,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123105526</v>
+        <v>123107271</v>
       </c>
       <c r="B50" t="n">
-        <v>78781</v>
+        <v>57503</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6076,30 +6071,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6107,10 +6103,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>810798</v>
+        <v>810992</v>
       </c>
       <c r="R50" t="n">
-        <v>7171573</v>
+        <v>7171739</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6145,13 +6141,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123104657</v>
+        <v>123104604</v>
       </c>
       <c r="B22" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>810447</v>
+        <v>810442</v>
       </c>
       <c r="R22" t="n">
-        <v>7171526</v>
+        <v>7171450</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123104604</v>
+        <v>123104581</v>
       </c>
       <c r="B23" t="n">
-        <v>57503</v>
+        <v>57490</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3046,16 +3046,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>810442</v>
+        <v>810444</v>
       </c>
       <c r="R23" t="n">
-        <v>7171450</v>
+        <v>7171466</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3145,10 +3145,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123104581</v>
+        <v>123104657</v>
       </c>
       <c r="B24" t="n">
-        <v>57487</v>
+        <v>57506</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,16 +3161,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>810444</v>
+        <v>810447</v>
       </c>
       <c r="R24" t="n">
-        <v>7171466</v>
+        <v>7171526</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5046,10 +5046,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123107589</v>
+        <v>123107500</v>
       </c>
       <c r="B41" t="n">
-        <v>82568</v>
+        <v>78786</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5062,27 +5062,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>810886</v>
+        <v>811043</v>
       </c>
       <c r="R41" t="n">
-        <v>7171705</v>
+        <v>7171704</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5156,10 +5156,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123105448</v>
+        <v>123105541</v>
       </c>
       <c r="B42" t="n">
-        <v>78781</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5168,25 +5168,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5195,11 +5195,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5207,10 +5203,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810833</v>
+        <v>810786</v>
       </c>
       <c r="R42" t="n">
-        <v>7171608</v>
+        <v>7171568</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5243,11 +5239,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5275,10 +5266,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123113230</v>
+        <v>123107589</v>
       </c>
       <c r="B43" t="n">
-        <v>78781</v>
+        <v>82573</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5291,27 +5282,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -5322,10 +5313,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810850</v>
+        <v>810886</v>
       </c>
       <c r="R43" t="n">
-        <v>7171671</v>
+        <v>7171705</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5385,10 +5376,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123113295</v>
+        <v>123113205</v>
       </c>
       <c r="B44" t="n">
-        <v>57503</v>
+        <v>78818</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5401,31 +5392,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5433,10 +5423,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>810851</v>
+        <v>810862</v>
       </c>
       <c r="R44" t="n">
-        <v>7171663</v>
+        <v>7171664</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5471,17 +5461,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>hack i död ved</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5500,10 +5486,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123107409</v>
+        <v>123107580</v>
       </c>
       <c r="B45" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5516,31 +5502,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5548,10 +5533,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811024</v>
+        <v>810886</v>
       </c>
       <c r="R45" t="n">
-        <v>7171733</v>
+        <v>7171705</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5586,17 +5571,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5618,7 +5599,7 @@
         <v>123107525</v>
       </c>
       <c r="B46" t="n">
-        <v>78805</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5725,10 +5706,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123113205</v>
+        <v>123107538</v>
       </c>
       <c r="B47" t="n">
-        <v>78813</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5737,25 +5718,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5772,10 +5753,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810862</v>
+        <v>810978</v>
       </c>
       <c r="R47" t="n">
-        <v>7171664</v>
+        <v>7171744</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5835,10 +5816,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123107511</v>
+        <v>123107351</v>
       </c>
       <c r="B48" t="n">
-        <v>78805</v>
+        <v>78786</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5847,25 +5828,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5874,7 +5855,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5882,10 +5867,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811066</v>
+        <v>811003</v>
       </c>
       <c r="R48" t="n">
-        <v>7171715</v>
+        <v>7171721</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5918,6 +5903,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5945,10 +5935,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123105526</v>
+        <v>123107271</v>
       </c>
       <c r="B49" t="n">
-        <v>78781</v>
+        <v>57506</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5961,30 +5951,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5992,10 +5983,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>810798</v>
+        <v>810992</v>
       </c>
       <c r="R49" t="n">
-        <v>7171573</v>
+        <v>7171739</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6030,13 +6021,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6055,10 +6050,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123107271</v>
+        <v>123107409</v>
       </c>
       <c r="B50" t="n">
-        <v>57503</v>
+        <v>57490</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6071,16 +6066,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6093,7 +6088,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6103,10 +6098,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>810992</v>
+        <v>811024</v>
       </c>
       <c r="R50" t="n">
-        <v>7171739</v>
+        <v>7171733</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6143,7 +6138,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6170,10 +6165,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123105488</v>
+        <v>123105448</v>
       </c>
       <c r="B51" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6209,7 +6204,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6217,10 +6216,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>810824</v>
+        <v>810833</v>
       </c>
       <c r="R51" t="n">
-        <v>7171598</v>
+        <v>7171608</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6257,7 +6256,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>över 0,5 meter lång bål</t>
+          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6288,7 +6287,7 @@
         <v>123113317</v>
       </c>
       <c r="B52" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6400,10 +6399,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123105541</v>
+        <v>123107487</v>
       </c>
       <c r="B53" t="n">
-        <v>78805</v>
+        <v>78786</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6412,25 +6411,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6447,10 +6446,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810786</v>
+        <v>811052</v>
       </c>
       <c r="R53" t="n">
-        <v>7171568</v>
+        <v>7171679</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6483,6 +6482,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6510,10 +6514,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123107351</v>
+        <v>123113295</v>
       </c>
       <c r="B54" t="n">
-        <v>78781</v>
+        <v>57506</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6526,32 +6530,29 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6561,10 +6562,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811003</v>
+        <v>810851</v>
       </c>
       <c r="R54" t="n">
-        <v>7171721</v>
+        <v>7171663</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6601,7 +6602,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>fertil garnlav</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6610,7 +6611,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6629,10 +6629,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123107580</v>
+        <v>123113132</v>
       </c>
       <c r="B55" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6645,30 +6645,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6676,10 +6677,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810886</v>
+        <v>810895</v>
       </c>
       <c r="R55" t="n">
-        <v>7171705</v>
+        <v>7171694</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6714,13 +6715,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6739,10 +6744,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123107487</v>
+        <v>123105526</v>
       </c>
       <c r="B56" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6786,10 +6791,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811052</v>
+        <v>810798</v>
       </c>
       <c r="R56" t="n">
-        <v>7171679</v>
+        <v>7171573</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6822,11 +6827,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6854,10 +6854,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123113174</v>
+        <v>123107511</v>
       </c>
       <c r="B57" t="n">
-        <v>78781</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6866,25 +6866,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810865</v>
+        <v>811066</v>
       </c>
       <c r="R57" t="n">
-        <v>7171668</v>
+        <v>7171715</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6937,11 +6937,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6969,10 +6964,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123107538</v>
+        <v>123113230</v>
       </c>
       <c r="B58" t="n">
-        <v>78805</v>
+        <v>78786</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6981,25 +6976,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7016,10 +7011,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810978</v>
+        <v>810850</v>
       </c>
       <c r="R58" t="n">
-        <v>7171744</v>
+        <v>7171671</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7079,10 +7074,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123107500</v>
+        <v>123107426</v>
       </c>
       <c r="B59" t="n">
-        <v>78781</v>
+        <v>57506</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7095,30 +7090,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7126,10 +7118,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811043</v>
+        <v>811024</v>
       </c>
       <c r="R59" t="n">
-        <v>7171704</v>
+        <v>7171733</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7164,13 +7156,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7189,10 +7185,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123107426</v>
+        <v>123113174</v>
       </c>
       <c r="B60" t="n">
-        <v>57503</v>
+        <v>78786</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7205,27 +7201,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7233,10 +7232,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811024</v>
+        <v>810865</v>
       </c>
       <c r="R60" t="n">
-        <v>7171733</v>
+        <v>7171668</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7273,7 +7272,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7282,6 +7281,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7303,7 +7303,7 @@
         <v>123107459</v>
       </c>
       <c r="B61" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7415,10 +7415,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123113132</v>
+        <v>123105488</v>
       </c>
       <c r="B62" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7431,31 +7431,30 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7463,10 +7462,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>810895</v>
+        <v>810824</v>
       </c>
       <c r="R62" t="n">
-        <v>7171694</v>
+        <v>7171598</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7503,7 +7502,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7512,6 +7511,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123104604</v>
+        <v>123104657</v>
       </c>
       <c r="B22" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>810442</v>
+        <v>810447</v>
       </c>
       <c r="R22" t="n">
-        <v>7171450</v>
+        <v>7171526</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>hack i torraka</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123104581</v>
+        <v>123104604</v>
       </c>
       <c r="B23" t="n">
-        <v>57490</v>
+        <v>57507</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3046,16 +3046,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>810444</v>
+        <v>810442</v>
       </c>
       <c r="R23" t="n">
-        <v>7171466</v>
+        <v>7171450</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>äldre ringhack på tall</t>
+          <t>hack i torraka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3145,10 +3145,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123104657</v>
+        <v>123104581</v>
       </c>
       <c r="B24" t="n">
-        <v>57506</v>
+        <v>57491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,16 +3161,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>810447</v>
+        <v>810444</v>
       </c>
       <c r="R24" t="n">
-        <v>7171526</v>
+        <v>7171466</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5046,10 +5046,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123107500</v>
+        <v>123105448</v>
       </c>
       <c r="B41" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5085,7 +5085,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5093,10 +5097,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811043</v>
+        <v>810833</v>
       </c>
       <c r="R41" t="n">
-        <v>7171704</v>
+        <v>7171608</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5129,6 +5133,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5156,10 +5165,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123105541</v>
+        <v>123107459</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>57491</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5168,34 +5177,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5203,10 +5213,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810786</v>
+        <v>811055</v>
       </c>
       <c r="R42" t="n">
-        <v>7171568</v>
+        <v>7171672</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5241,13 +5251,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5266,10 +5280,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123107589</v>
+        <v>123105526</v>
       </c>
       <c r="B43" t="n">
-        <v>82573</v>
+        <v>78788</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5282,27 +5296,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -5313,10 +5327,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810886</v>
+        <v>810798</v>
       </c>
       <c r="R43" t="n">
-        <v>7171705</v>
+        <v>7171573</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5376,10 +5390,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123113205</v>
+        <v>123107351</v>
       </c>
       <c r="B44" t="n">
-        <v>78818</v>
+        <v>78788</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5392,21 +5406,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5415,7 +5429,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5423,10 +5441,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>810862</v>
+        <v>811003</v>
       </c>
       <c r="R44" t="n">
-        <v>7171664</v>
+        <v>7171721</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5459,6 +5477,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5486,10 +5509,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123107580</v>
+        <v>123113230</v>
       </c>
       <c r="B45" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5533,10 +5556,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>810886</v>
+        <v>810850</v>
       </c>
       <c r="R45" t="n">
-        <v>7171705</v>
+        <v>7171671</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5596,10 +5619,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123107525</v>
+        <v>123113132</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>57491</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5608,34 +5631,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5643,10 +5667,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811018</v>
+        <v>810895</v>
       </c>
       <c r="R46" t="n">
-        <v>7171753</v>
+        <v>7171694</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5681,13 +5705,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5706,10 +5734,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123107538</v>
+        <v>123113205</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>78820</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5718,25 +5746,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6434</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5753,10 +5781,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810978</v>
+        <v>810862</v>
       </c>
       <c r="R47" t="n">
-        <v>7171744</v>
+        <v>7171664</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5816,10 +5844,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123107351</v>
+        <v>123113317</v>
       </c>
       <c r="B48" t="n">
-        <v>78786</v>
+        <v>57507</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5832,32 +5860,29 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5867,10 +5892,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811003</v>
+        <v>810707</v>
       </c>
       <c r="R48" t="n">
-        <v>7171721</v>
+        <v>7171592</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5907,7 +5932,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>fertil garnlav</t>
+          <t>hål i gammal sälg</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5916,7 +5941,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5935,10 +5959,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123107271</v>
+        <v>123107500</v>
       </c>
       <c r="B49" t="n">
-        <v>57506</v>
+        <v>78788</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5951,31 +5975,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5983,10 +6006,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>810992</v>
+        <v>811043</v>
       </c>
       <c r="R49" t="n">
-        <v>7171739</v>
+        <v>7171704</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6021,17 +6044,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>hack i död ved</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6050,10 +6069,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123107409</v>
+        <v>123107487</v>
       </c>
       <c r="B50" t="n">
-        <v>57490</v>
+        <v>78788</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6066,31 +6085,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6098,10 +6116,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811024</v>
+        <v>811052</v>
       </c>
       <c r="R50" t="n">
-        <v>7171733</v>
+        <v>7171679</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6138,7 +6156,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
+          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6147,6 +6165,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6165,10 +6184,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123105448</v>
+        <v>123113174</v>
       </c>
       <c r="B51" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6204,11 +6223,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6216,10 +6231,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>810833</v>
+        <v>810865</v>
       </c>
       <c r="R51" t="n">
-        <v>7171608</v>
+        <v>7171668</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6256,7 +6271,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>rikligt med fertil garnlav på gammal död gran</t>
+          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6284,10 +6299,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123113317</v>
+        <v>123105541</v>
       </c>
       <c r="B52" t="n">
-        <v>57506</v>
+        <v>78812</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6296,35 +6311,34 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6332,10 +6346,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810707</v>
+        <v>810786</v>
       </c>
       <c r="R52" t="n">
-        <v>7171592</v>
+        <v>7171568</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6370,17 +6384,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>hål i gammal sälg</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6399,10 +6409,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123107487</v>
+        <v>123107426</v>
       </c>
       <c r="B53" t="n">
-        <v>78786</v>
+        <v>57507</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6415,30 +6425,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6446,10 +6453,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811052</v>
+        <v>811024</v>
       </c>
       <c r="R53" t="n">
-        <v>7171679</v>
+        <v>7171733</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6486,7 +6493,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>rikligt med hänglavar bla garnlav</t>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6495,7 +6502,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6514,10 +6520,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123113295</v>
+        <v>123107409</v>
       </c>
       <c r="B54" t="n">
-        <v>57506</v>
+        <v>57491</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6530,16 +6536,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6552,7 +6558,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6562,10 +6568,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810851</v>
+        <v>811024</v>
       </c>
       <c r="R54" t="n">
-        <v>7171663</v>
+        <v>7171733</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6602,7 +6608,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6629,10 +6635,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123113132</v>
+        <v>123107511</v>
       </c>
       <c r="B55" t="n">
-        <v>57490</v>
+        <v>78812</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6641,35 +6647,34 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6677,10 +6682,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810895</v>
+        <v>811066</v>
       </c>
       <c r="R55" t="n">
-        <v>7171694</v>
+        <v>7171715</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6715,17 +6720,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6744,10 +6745,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123105526</v>
+        <v>123107538</v>
       </c>
       <c r="B56" t="n">
-        <v>78786</v>
+        <v>78812</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6756,25 +6757,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6791,10 +6792,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810798</v>
+        <v>810978</v>
       </c>
       <c r="R56" t="n">
-        <v>7171573</v>
+        <v>7171744</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6854,10 +6855,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123107511</v>
+        <v>123107589</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>82575</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6866,31 +6867,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6434</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -6901,10 +6902,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811066</v>
+        <v>810886</v>
       </c>
       <c r="R57" t="n">
-        <v>7171715</v>
+        <v>7171705</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6964,10 +6965,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123113230</v>
+        <v>123113295</v>
       </c>
       <c r="B58" t="n">
-        <v>78786</v>
+        <v>57507</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6980,30 +6981,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7011,10 +7013,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810850</v>
+        <v>810851</v>
       </c>
       <c r="R58" t="n">
-        <v>7171671</v>
+        <v>7171663</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7049,13 +7051,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7074,10 +7080,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123107426</v>
+        <v>123107525</v>
       </c>
       <c r="B59" t="n">
-        <v>57506</v>
+        <v>78812</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7086,31 +7092,34 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7118,10 +7127,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811024</v>
+        <v>811018</v>
       </c>
       <c r="R59" t="n">
-        <v>7171733</v>
+        <v>7171753</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7156,17 +7165,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7185,10 +7190,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123113174</v>
+        <v>123105488</v>
       </c>
       <c r="B60" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7232,10 +7237,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810865</v>
+        <v>810824</v>
       </c>
       <c r="R60" t="n">
-        <v>7171668</v>
+        <v>7171598</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7272,7 +7277,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>hänglavrikt bla garnlav</t>
+          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7300,10 +7305,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123107459</v>
+        <v>123107271</v>
       </c>
       <c r="B61" t="n">
-        <v>57490</v>
+        <v>57507</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7316,16 +7321,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7338,7 +7343,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7348,10 +7353,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811055</v>
+        <v>810992</v>
       </c>
       <c r="R61" t="n">
-        <v>7171672</v>
+        <v>7171739</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7388,7 +7393,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7415,10 +7420,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123105488</v>
+        <v>123107580</v>
       </c>
       <c r="B62" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7462,10 +7467,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>810824</v>
+        <v>810886</v>
       </c>
       <c r="R62" t="n">
-        <v>7171598</v>
+        <v>7171705</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7498,11 +7503,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -5844,10 +5844,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123113317</v>
+        <v>123107500</v>
       </c>
       <c r="B48" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5860,31 +5860,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5892,10 +5891,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>810707</v>
+        <v>811043</v>
       </c>
       <c r="R48" t="n">
-        <v>7171592</v>
+        <v>7171704</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5930,17 +5929,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>hål i gammal sälg</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5959,10 +5954,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123107500</v>
+        <v>123113317</v>
       </c>
       <c r="B49" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5975,30 +5970,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6006,10 +6002,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811043</v>
+        <v>810707</v>
       </c>
       <c r="R49" t="n">
-        <v>7171704</v>
+        <v>7171592</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6044,13 +6040,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>hål i gammal sälg</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6855,10 +6855,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123107589</v>
+        <v>123113295</v>
       </c>
       <c r="B57" t="n">
-        <v>82575</v>
+        <v>57507</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6871,30 +6871,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6902,10 +6903,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810886</v>
+        <v>810851</v>
       </c>
       <c r="R57" t="n">
-        <v>7171705</v>
+        <v>7171663</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6940,13 +6941,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6965,10 +6970,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123113295</v>
+        <v>123107589</v>
       </c>
       <c r="B58" t="n">
-        <v>57507</v>
+        <v>82575</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6981,31 +6986,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7013,10 +7017,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810851</v>
+        <v>810886</v>
       </c>
       <c r="R58" t="n">
-        <v>7171663</v>
+        <v>7171705</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7051,17 +7055,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>hack i död ved</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -1687,7 +1687,7 @@
         <v>122645747</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>122645698</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>122650339</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>123107459</v>
       </c>
       <c r="B42" t="n">
-        <v>57491</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>123113132</v>
       </c>
       <c r="B46" t="n">
-        <v>57491</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3260,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>391091</v>
+        <v>125014705</v>
       </c>
       <c r="B25" t="n">
-        <v>81235</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3272,41 +3272,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810860.7270867341</v>
+        <v>810458</v>
       </c>
       <c r="R25" t="n">
-        <v>7171669.623737417</v>
+        <v>7171462</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3330,22 +3338,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,6 +3352,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3372,10 +3371,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2055139</v>
+        <v>125014666</v>
       </c>
       <c r="B26" t="n">
-        <v>78097</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3384,41 +3383,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810860.7270867341</v>
+        <v>810442</v>
       </c>
       <c r="R26" t="n">
-        <v>7171669.623737417</v>
+        <v>7171466</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3442,22 +3449,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3466,10 +3463,10 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AR26" t="inlineStr"/>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
@@ -3478,17 +3475,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>292476</v>
+        <v>125014750</v>
       </c>
       <c r="B27" t="n">
-        <v>79432</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3497,41 +3494,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tallskog Storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810917.5546458759</v>
+        <v>810464</v>
       </c>
       <c r="R27" t="n">
-        <v>7171682.39060352</v>
+        <v>7171463</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3555,27 +3560,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2007-10-31</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>rapport från Patrik Nygren, SNF</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3584,28 +3574,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Jonas F Grahn</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>292265</v>
+        <v>125014622</v>
       </c>
       <c r="B28" t="n">
-        <v>79432</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3614,41 +3605,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>storön, Vb</t>
+          <t>Storön, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810860.7270867341</v>
+        <v>810448</v>
       </c>
       <c r="R28" t="n">
-        <v>7171669.623737417</v>
+        <v>7171471</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3672,22 +3671,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3696,10 +3690,10 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AR28" t="inlineStr"/>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
@@ -3708,17 +3702,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122650329</v>
+        <v>391091</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>81235</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3731,44 +3725,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storön, Vb</t>
+          <t>storön, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810886</v>
+        <v>810860.7270867341</v>
       </c>
       <c r="R29" t="n">
-        <v>7171642</v>
+        <v>7171669.623737417</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3792,12 +3779,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-12-31</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3806,7 +3803,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3825,10 +3821,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122650264</v>
+        <v>2055139</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>78097</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3841,44 +3837,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storön, Vb</t>
+          <t>storön, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811045</v>
+        <v>810860.7270867341</v>
       </c>
       <c r="R30" t="n">
-        <v>7171680</v>
+        <v>7171669.623737417</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3902,12 +3891,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-12-31</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3916,10 +3915,10 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AR30" t="inlineStr"/>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
@@ -3935,10 +3934,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122650270</v>
+        <v>292476</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>79432</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3951,44 +3950,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storön, Vb</t>
+          <t>Tallskog Storön, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811036</v>
+        <v>810917.5546458759</v>
       </c>
       <c r="R31" t="n">
-        <v>7171698</v>
+        <v>7171682.39060352</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4012,12 +4004,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-06-01</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-10-31</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>rapport från Patrik Nygren, SNF</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4026,29 +4033,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Via Jonas F Grahn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122650066</v>
+        <v>292265</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>79432</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4061,44 +4067,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storön, Vb</t>
+          <t>storön, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810939</v>
+        <v>810860.7270867341</v>
       </c>
       <c r="R32" t="n">
-        <v>7171504</v>
+        <v>7171669.623737417</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4122,12 +4121,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2007-12-31</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4136,10 +4145,10 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AR32" t="inlineStr"/>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
@@ -4155,7 +4164,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122649988</v>
+        <v>122650329</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -4202,10 +4211,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810939</v>
+        <v>810886</v>
       </c>
       <c r="R33" t="n">
-        <v>7171498</v>
+        <v>7171642</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4265,7 +4274,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122649921</v>
+        <v>122650264</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4312,10 +4321,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>810786</v>
+        <v>811045</v>
       </c>
       <c r="R34" t="n">
-        <v>7171426</v>
+        <v>7171680</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4375,10 +4384,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122650277</v>
+        <v>122650270</v>
       </c>
       <c r="B35" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4391,31 +4400,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4423,10 +4431,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811014</v>
+        <v>811036</v>
       </c>
       <c r="R35" t="n">
-        <v>7171734</v>
+        <v>7171698</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4461,17 +4469,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>hack i gran, både äldre och färska hack</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4490,10 +4494,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122650339</v>
+        <v>122650066</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4506,27 +4510,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4534,10 +4541,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>810833</v>
+        <v>810939</v>
       </c>
       <c r="R36" t="n">
-        <v>7171605</v>
+        <v>7171504</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4572,17 +4579,13 @@
           <t>2025-02-13</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4601,7 +4604,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122649892</v>
+        <v>122649988</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4648,10 +4651,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810633</v>
+        <v>810939</v>
       </c>
       <c r="R37" t="n">
-        <v>7171420</v>
+        <v>7171498</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4711,7 +4714,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122650292</v>
+        <v>122649921</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -4758,10 +4761,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>810931</v>
+        <v>810786</v>
       </c>
       <c r="R38" t="n">
-        <v>7171669</v>
+        <v>7171426</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4821,10 +4824,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122650350</v>
+        <v>122650277</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4837,30 +4840,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4868,10 +4872,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>810833</v>
+        <v>811014</v>
       </c>
       <c r="R39" t="n">
-        <v>7171605</v>
+        <v>7171734</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4906,13 +4910,17 @@
           <t>2025-02-13</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>hack i gran, både äldre och färska hack</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4931,10 +4939,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122649934</v>
+        <v>122650339</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4967,11 +4975,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4979,10 +4983,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>810828</v>
+        <v>810833</v>
       </c>
       <c r="R40" t="n">
-        <v>7171441</v>
+        <v>7171605</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5019,7 +5023,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>äldre ringhack i gran</t>
+          <t>barksprätt på gammal senvuxen gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5046,10 +5050,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123105448</v>
+        <v>122649892</v>
       </c>
       <c r="B41" t="n">
-        <v>78788</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5085,11 +5089,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>810833</v>
+        <v>810633</v>
       </c>
       <c r="R41" t="n">
-        <v>7171608</v>
+        <v>7171420</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5127,17 +5127,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>rikligt med fertil garnlav på gammal död gran</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5165,10 +5160,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123107459</v>
+        <v>122650292</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5181,31 +5176,30 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5213,10 +5207,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811055</v>
+        <v>810931</v>
       </c>
       <c r="R42" t="n">
-        <v>7171672</v>
+        <v>7171669</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5243,17 +5237,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5262,6 +5251,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5280,10 +5270,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123105526</v>
+        <v>122650350</v>
       </c>
       <c r="B43" t="n">
-        <v>78788</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5327,10 +5317,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810798</v>
+        <v>810833</v>
       </c>
       <c r="R43" t="n">
-        <v>7171573</v>
+        <v>7171605</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5357,12 +5347,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5390,10 +5380,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123107351</v>
+        <v>122649934</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5406,32 +5396,29 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5441,10 +5428,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811003</v>
+        <v>810828</v>
       </c>
       <c r="R44" t="n">
-        <v>7171721</v>
+        <v>7171441</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5471,17 +5458,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>fertil garnlav</t>
+          <t>äldre ringhack i gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5490,7 +5477,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5509,7 +5495,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123113230</v>
+        <v>123105448</v>
       </c>
       <c r="B45" t="n">
         <v>78788</v>
@@ -5548,7 +5534,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5556,10 +5546,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>810850</v>
+        <v>810833</v>
       </c>
       <c r="R45" t="n">
-        <v>7171671</v>
+        <v>7171608</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5592,6 +5582,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>rikligt med fertil garnlav på gammal död gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5619,7 +5614,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123113132</v>
+        <v>123107459</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -5667,10 +5662,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>810895</v>
+        <v>811055</v>
       </c>
       <c r="R46" t="n">
-        <v>7171694</v>
+        <v>7171672</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5707,7 +5702,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>barksprätt på gammal gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5734,10 +5729,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123113205</v>
+        <v>123105526</v>
       </c>
       <c r="B47" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5750,21 +5745,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5781,10 +5776,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810862</v>
+        <v>810798</v>
       </c>
       <c r="R47" t="n">
-        <v>7171664</v>
+        <v>7171573</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5844,7 +5839,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123107500</v>
+        <v>123107351</v>
       </c>
       <c r="B48" t="n">
         <v>78788</v>
@@ -5883,7 +5878,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5891,10 +5890,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811043</v>
+        <v>811003</v>
       </c>
       <c r="R48" t="n">
-        <v>7171704</v>
+        <v>7171721</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5927,6 +5926,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5954,10 +5958,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123113317</v>
+        <v>123113230</v>
       </c>
       <c r="B49" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5970,31 +5974,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6002,10 +6005,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>810707</v>
+        <v>810850</v>
       </c>
       <c r="R49" t="n">
-        <v>7171592</v>
+        <v>7171671</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6040,17 +6043,13 @@
           <t>2025-03-11</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>hål i gammal sälg</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6069,10 +6068,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123107487</v>
+        <v>123113132</v>
       </c>
       <c r="B50" t="n">
-        <v>78788</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6085,30 +6084,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811052</v>
+        <v>810895</v>
       </c>
       <c r="R50" t="n">
-        <v>7171679</v>
+        <v>7171694</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>rikligt med hänglavar bla garnlav</t>
+          <t>barksprätt på gammal gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6165,7 +6165,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6184,10 +6183,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123113174</v>
+        <v>123113205</v>
       </c>
       <c r="B51" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6200,21 +6199,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6231,10 +6230,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>810865</v>
+        <v>810862</v>
       </c>
       <c r="R51" t="n">
-        <v>7171668</v>
+        <v>7171664</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6267,11 +6266,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6299,10 +6293,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123105541</v>
+        <v>123107500</v>
       </c>
       <c r="B52" t="n">
-        <v>78812</v>
+        <v>78788</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6311,25 +6305,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6346,10 +6340,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810786</v>
+        <v>811043</v>
       </c>
       <c r="R52" t="n">
-        <v>7171568</v>
+        <v>7171704</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6409,7 +6403,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123107426</v>
+        <v>123113317</v>
       </c>
       <c r="B53" t="n">
         <v>57507</v>
@@ -6445,7 +6439,11 @@
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6453,10 +6451,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811024</v>
+        <v>810707</v>
       </c>
       <c r="R53" t="n">
-        <v>7171733</v>
+        <v>7171592</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6493,7 +6491,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
+          <t>hål i gammal sälg</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6520,10 +6518,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123107409</v>
+        <v>123107487</v>
       </c>
       <c r="B54" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6536,31 +6534,30 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6568,10 +6565,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811024</v>
+        <v>811052</v>
       </c>
       <c r="R54" t="n">
-        <v>7171733</v>
+        <v>7171679</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6608,7 +6605,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
+          <t>rikligt med hänglavar bla garnlav</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6617,6 +6614,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6635,10 +6633,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123107511</v>
+        <v>123113174</v>
       </c>
       <c r="B55" t="n">
-        <v>78812</v>
+        <v>78788</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6647,25 +6645,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6682,10 +6680,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811066</v>
+        <v>810865</v>
       </c>
       <c r="R55" t="n">
-        <v>7171715</v>
+        <v>7171668</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6718,6 +6716,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>hänglavrikt bla garnlav</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6745,7 +6748,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123107538</v>
+        <v>123105541</v>
       </c>
       <c r="B56" t="n">
         <v>78812</v>
@@ -6792,10 +6795,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810978</v>
+        <v>810786</v>
       </c>
       <c r="R56" t="n">
-        <v>7171744</v>
+        <v>7171568</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6855,7 +6858,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123113295</v>
+        <v>123107426</v>
       </c>
       <c r="B57" t="n">
         <v>57507</v>
@@ -6891,11 +6894,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6903,10 +6902,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810851</v>
+        <v>811024</v>
       </c>
       <c r="R57" t="n">
-        <v>7171663</v>
+        <v>7171733</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6943,7 +6942,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>hack i högstubbe av gammelgran, samma gran som eventuellt bohål av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6970,10 +6969,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123107589</v>
+        <v>123107409</v>
       </c>
       <c r="B58" t="n">
-        <v>82575</v>
+        <v>57491</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6986,30 +6985,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7017,10 +7017,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810886</v>
+        <v>811024</v>
       </c>
       <c r="R58" t="n">
-        <v>7171705</v>
+        <v>7171733</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7055,13 +7055,17 @@
           <t>2025-03-11</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>påbörjat bohål? i samma högstubbe av gammal gran som spillkråkehack men detta är mindre och rundare</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7080,7 +7084,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123107525</v>
+        <v>123107511</v>
       </c>
       <c r="B59" t="n">
         <v>78812</v>
@@ -7127,10 +7131,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811018</v>
+        <v>811066</v>
       </c>
       <c r="R59" t="n">
-        <v>7171753</v>
+        <v>7171715</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7190,10 +7194,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123105488</v>
+        <v>123107538</v>
       </c>
       <c r="B60" t="n">
-        <v>78788</v>
+        <v>78812</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7202,25 +7206,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7237,10 +7241,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810824</v>
+        <v>810978</v>
       </c>
       <c r="R60" t="n">
-        <v>7171598</v>
+        <v>7171744</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7273,11 +7277,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-11</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>över 0,5 meter lång bål</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7305,7 +7304,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123107271</v>
+        <v>123113295</v>
       </c>
       <c r="B61" t="n">
         <v>57507</v>
@@ -7353,10 +7352,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>810992</v>
+        <v>810851</v>
       </c>
       <c r="R61" t="n">
-        <v>7171739</v>
+        <v>7171663</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7420,10 +7419,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123107580</v>
+        <v>123107589</v>
       </c>
       <c r="B62" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7436,27 +7435,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -7527,6 +7526,572 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>123107525</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78812</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>811018</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7171753</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>123105488</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>810824</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7171598</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>över 0,5 meter lång bål</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>123107271</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>810992</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7171739</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>hack i död ved</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>123107580</v>
+      </c>
+      <c r="B66" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>810886</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7171705</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>125014301</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Storön, Vb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>810839</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7171616</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ca 50 ggr 50cm yta med ca 40 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Patrik Nygren, Sirirat Chanon</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014705</v>
+        <v>125014750</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810458</v>
+        <v>810464</v>
       </c>
       <c r="R25" t="n">
-        <v>7171462</v>
+        <v>7171463</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014666</v>
+        <v>125014622</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810442</v>
+        <v>810448</v>
       </c>
       <c r="R26" t="n">
-        <v>7171466</v>
+        <v>7171471</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,6 +3455,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3482,7 +3487,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014750</v>
+        <v>125014666</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3530,10 +3535,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810464</v>
+        <v>810442</v>
       </c>
       <c r="R27" t="n">
-        <v>7171463</v>
+        <v>7171466</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3586,14 +3591,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014622</v>
+        <v>125014705</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3641,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810448</v>
+        <v>810458</v>
       </c>
       <c r="R28" t="n">
-        <v>7171471</v>
+        <v>7171462</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3679,11 +3684,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014750</v>
+        <v>125014666</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810464</v>
+        <v>810442</v>
       </c>
       <c r="R25" t="n">
-        <v>7171463</v>
+        <v>7171466</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3487,7 +3487,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014666</v>
+        <v>125014705</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810442</v>
+        <v>810458</v>
       </c>
       <c r="R27" t="n">
-        <v>7171466</v>
+        <v>7171462</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3591,14 +3591,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014705</v>
+        <v>125014750</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810458</v>
+        <v>810464</v>
       </c>
       <c r="R28" t="n">
-        <v>7171462</v>
+        <v>7171463</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -3371,7 +3371,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014622</v>
+        <v>125014750</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810448</v>
+        <v>810464</v>
       </c>
       <c r="R26" t="n">
-        <v>7171471</v>
+        <v>7171463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,11 +3457,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3480,14 +3475,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014705</v>
+        <v>125014622</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3535,10 +3530,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810458</v>
+        <v>810448</v>
       </c>
       <c r="R27" t="n">
-        <v>7171462</v>
+        <v>7171471</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,6 +3568,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3591,14 +3591,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014750</v>
+        <v>125014705</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810464</v>
+        <v>810458</v>
       </c>
       <c r="R28" t="n">
-        <v>7171463</v>
+        <v>7171462</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014666</v>
+        <v>125014705</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810442</v>
+        <v>810458</v>
       </c>
       <c r="R25" t="n">
-        <v>7171466</v>
+        <v>7171462</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3364,14 +3364,14 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014750</v>
+        <v>125014666</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810464</v>
+        <v>810442</v>
       </c>
       <c r="R26" t="n">
-        <v>7171463</v>
+        <v>7171466</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,14 +3475,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014622</v>
+        <v>125014750</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3530,10 +3530,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810448</v>
+        <v>810464</v>
       </c>
       <c r="R27" t="n">
-        <v>7171471</v>
+        <v>7171463</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3568,11 +3568,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3591,14 +3586,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014705</v>
+        <v>125014622</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3646,10 +3641,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810458</v>
+        <v>810448</v>
       </c>
       <c r="R28" t="n">
-        <v>7171462</v>
+        <v>7171471</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3684,6 +3679,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014705</v>
+        <v>125014666</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810458</v>
+        <v>810442</v>
       </c>
       <c r="R25" t="n">
-        <v>7171462</v>
+        <v>7171466</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3364,14 +3364,14 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014666</v>
+        <v>125014750</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810442</v>
+        <v>810464</v>
       </c>
       <c r="R26" t="n">
-        <v>7171466</v>
+        <v>7171463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,14 +3475,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014750</v>
+        <v>125014705</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3530,10 +3530,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810464</v>
+        <v>810458</v>
       </c>
       <c r="R27" t="n">
-        <v>7171463</v>
+        <v>7171462</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014666</v>
+        <v>125014622</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810442</v>
+        <v>810448</v>
       </c>
       <c r="R25" t="n">
-        <v>7171466</v>
+        <v>7171471</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,6 +3344,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,7 +3376,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014750</v>
+        <v>125014705</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3419,10 +3424,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810464</v>
+        <v>810458</v>
       </c>
       <c r="R26" t="n">
-        <v>7171463</v>
+        <v>7171462</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3482,7 +3487,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014705</v>
+        <v>125014666</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3530,10 +3535,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810458</v>
+        <v>810442</v>
       </c>
       <c r="R27" t="n">
-        <v>7171462</v>
+        <v>7171466</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3586,14 +3591,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014622</v>
+        <v>125014750</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3641,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810448</v>
+        <v>810464</v>
       </c>
       <c r="R28" t="n">
-        <v>7171471</v>
+        <v>7171463</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3679,11 +3684,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014622</v>
+        <v>125014705</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810448</v>
+        <v>810458</v>
       </c>
       <c r="R25" t="n">
-        <v>7171471</v>
+        <v>7171462</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3346,11 +3346,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3369,14 +3364,14 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014705</v>
+        <v>125014622</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3424,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810458</v>
+        <v>810448</v>
       </c>
       <c r="R26" t="n">
-        <v>7171462</v>
+        <v>7171471</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3462,6 +3457,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014705</v>
+        <v>125014622</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810458</v>
+        <v>810448</v>
       </c>
       <c r="R25" t="n">
-        <v>7171462</v>
+        <v>7171471</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3346,6 +3346,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3364,14 +3369,14 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014622</v>
+        <v>125014750</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3419,10 +3424,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810448</v>
+        <v>810464</v>
       </c>
       <c r="R26" t="n">
-        <v>7171471</v>
+        <v>7171463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,11 +3462,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3598,7 +3598,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014750</v>
+        <v>125014705</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810464</v>
+        <v>810458</v>
       </c>
       <c r="R28" t="n">
-        <v>7171463</v>
+        <v>7171462</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014622</v>
+        <v>125014666</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810448</v>
+        <v>810442</v>
       </c>
       <c r="R25" t="n">
-        <v>7171471</v>
+        <v>7171466</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,11 +3344,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3376,7 +3371,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014750</v>
+        <v>125014622</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3424,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810464</v>
+        <v>810448</v>
       </c>
       <c r="R26" t="n">
-        <v>7171463</v>
+        <v>7171471</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3462,6 +3457,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3480,14 +3480,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014666</v>
+        <v>125014705</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810442</v>
+        <v>810458</v>
       </c>
       <c r="R27" t="n">
-        <v>7171466</v>
+        <v>7171462</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3591,14 +3591,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014705</v>
+        <v>125014750</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810458</v>
+        <v>810464</v>
       </c>
       <c r="R28" t="n">
-        <v>7171462</v>
+        <v>7171463</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -1687,7 +1687,7 @@
         <v>122645747</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>122645698</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3260,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014666</v>
+        <v>125014750</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810442</v>
+        <v>810464</v>
       </c>
       <c r="R25" t="n">
-        <v>7171466</v>
+        <v>7171463</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3364,17 +3364,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014622</v>
+        <v>125014705</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810448</v>
+        <v>810458</v>
       </c>
       <c r="R26" t="n">
-        <v>7171471</v>
+        <v>7171462</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,11 +3457,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3480,17 +3475,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014705</v>
+        <v>125014622</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3535,10 +3530,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810458</v>
+        <v>810448</v>
       </c>
       <c r="R27" t="n">
-        <v>7171462</v>
+        <v>7171471</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3573,6 +3568,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3591,17 +3591,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014750</v>
+        <v>125014666</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810464</v>
+        <v>810442</v>
       </c>
       <c r="R28" t="n">
-        <v>7171463</v>
+        <v>7171466</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4942,7 +4942,7 @@
         <v>122650339</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>123107459</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>123113132</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>125014301</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -3260,7 +3260,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014750</v>
+        <v>125014622</v>
       </c>
       <c r="B25" t="n">
         <v>98269</v>
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810464</v>
+        <v>810448</v>
       </c>
       <c r="R25" t="n">
-        <v>7171463</v>
+        <v>7171471</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3346,6 +3346,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3364,14 +3369,14 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014705</v>
+        <v>125014750</v>
       </c>
       <c r="B26" t="n">
         <v>98269</v>
@@ -3419,10 +3424,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810458</v>
+        <v>810464</v>
       </c>
       <c r="R26" t="n">
-        <v>7171462</v>
+        <v>7171463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3482,7 +3487,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014622</v>
+        <v>125014705</v>
       </c>
       <c r="B27" t="n">
         <v>98269</v>
@@ -3530,10 +3535,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810448</v>
+        <v>810458</v>
       </c>
       <c r="R27" t="n">
-        <v>7171471</v>
+        <v>7171462</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3568,11 +3573,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 4874-2025 artfynd.xlsx
+++ b/artfynd/A 4874-2025 artfynd.xlsx
@@ -1689,11 +1689,6 @@
       <c r="B11" t="n">
         <v>57635</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2255,11 +2250,6 @@
       <c r="B16" t="n">
         <v>57635</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>NT</t>
@@ -3260,15 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014622</v>
+        <v>125014750</v>
       </c>
       <c r="B25" t="n">
         <v>98269</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3308,10 +3293,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810448</v>
+        <v>810464</v>
       </c>
       <c r="R25" t="n">
-        <v>7171471</v>
+        <v>7171463</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3346,11 +3331,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>flera kvadratmeter med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3369,22 +3349,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014750</v>
+        <v>125014622</v>
       </c>
       <c r="B26" t="n">
         <v>98269</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3424,10 +3399,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810464</v>
+        <v>810448</v>
       </c>
       <c r="R26" t="n">
-        <v>7171463</v>
+        <v>7171471</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3462,6 +3437,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>flera kvadratmeter med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3480,7 +3460,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3492,11 +3472,6 @@
       <c r="B27" t="n">
         <v>98269</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>VU</t>
@@ -3603,11 +3578,6 @@
       <c r="B28" t="n">
         <v>98269</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>VU</t>
@@ -4943,11 +4913,6 @@
       </c>
       <c r="B40" t="n">
         <v>57635</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5619,11 +5584,6 @@
       <c r="B46" t="n">
         <v>57635</v>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>NT</t>
@@ -6072,11 +6032,6 @@
       </c>
       <c r="B50" t="n">
         <v>57635</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7984,11 +7939,6 @@
       <c r="B67" t="n">
         <v>98269</v>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>VU</t>
